--- a/database/BHIA3.xlsx
+++ b/database/BHIA3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3688"/>
+  <dimension ref="A1:F3689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36528</v>
       </c>
       <c r="B2" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="C2" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="D2" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="E2" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="F2" t="n">
         <v>319</v>
@@ -472,16 +472,16 @@
         <v>36529</v>
       </c>
       <c r="B3" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="C3" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="D3" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="E3" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="F3" t="n">
         <v>745</v>
@@ -492,16 +492,16 @@
         <v>36530</v>
       </c>
       <c r="B4" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="C4" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="D4" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="E4" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="F4" t="n">
         <v>745</v>
@@ -512,16 +512,16 @@
         <v>36531</v>
       </c>
       <c r="B5" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="C5" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="D5" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="E5" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="F5" t="n">
         <v>4615</v>
@@ -532,16 +532,16 @@
         <v>36532</v>
       </c>
       <c r="B6" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="C6" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="D6" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="E6" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="F6" t="n">
         <v>35</v>
@@ -552,16 +552,16 @@
         <v>36535</v>
       </c>
       <c r="B7" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="C7" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="D7" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="E7" t="n">
-        <v>21.8005542755127</v>
+        <v>21.80055809020996</v>
       </c>
       <c r="F7" t="n">
         <v>4260</v>
@@ -692,16 +692,16 @@
         <v>36692</v>
       </c>
       <c r="B14" t="n">
-        <v>44.12017822265625</v>
+        <v>44.12017440795898</v>
       </c>
       <c r="C14" t="n">
-        <v>44.12017822265625</v>
+        <v>44.12017440795898</v>
       </c>
       <c r="D14" t="n">
-        <v>44.12017822265625</v>
+        <v>44.12017440795898</v>
       </c>
       <c r="E14" t="n">
-        <v>44.12017822265625</v>
+        <v>44.12017440795898</v>
       </c>
       <c r="F14" t="n">
         <v>35</v>
@@ -712,16 +712,16 @@
         <v>36756</v>
       </c>
       <c r="B15" t="n">
-        <v>43.86064910888672</v>
+        <v>43.86064529418945</v>
       </c>
       <c r="C15" t="n">
-        <v>43.86064910888672</v>
+        <v>43.86064529418945</v>
       </c>
       <c r="D15" t="n">
-        <v>43.86064910888672</v>
+        <v>43.86064529418945</v>
       </c>
       <c r="E15" t="n">
-        <v>43.86064910888672</v>
+        <v>43.86064529418945</v>
       </c>
       <c r="F15" t="n">
         <v>142</v>
@@ -852,16 +852,16 @@
         <v>38140</v>
       </c>
       <c r="B22" t="n">
-        <v>32.78959274291992</v>
+        <v>32.78959655761719</v>
       </c>
       <c r="C22" t="n">
-        <v>32.78959274291992</v>
+        <v>32.78959655761719</v>
       </c>
       <c r="D22" t="n">
-        <v>27.17892816620879</v>
+        <v>27.17893132816886</v>
       </c>
       <c r="E22" t="n">
-        <v>27.17892816620879</v>
+        <v>27.17893132816886</v>
       </c>
       <c r="F22" t="n">
         <v>354</v>
@@ -872,16 +872,16 @@
         <v>38152</v>
       </c>
       <c r="B23" t="n">
-        <v>32.78959274291992</v>
+        <v>32.78959655761719</v>
       </c>
       <c r="C23" t="n">
-        <v>32.82602483086042</v>
+        <v>32.82602864979614</v>
       </c>
       <c r="D23" t="n">
-        <v>30.23929034302818</v>
+        <v>30.23929386102668</v>
       </c>
       <c r="E23" t="n">
-        <v>30.96794967810592</v>
+        <v>30.96795328087567</v>
       </c>
       <c r="F23" t="n">
         <v>784</v>
@@ -892,16 +892,16 @@
         <v>38153</v>
       </c>
       <c r="B24" t="n">
-        <v>32.78959274291992</v>
+        <v>32.78959655761719</v>
       </c>
       <c r="C24" t="n">
-        <v>32.78959274291992</v>
+        <v>32.78959655761719</v>
       </c>
       <c r="D24" t="n">
-        <v>32.78959274291992</v>
+        <v>32.78959655761719</v>
       </c>
       <c r="E24" t="n">
-        <v>32.78959274291992</v>
+        <v>32.78959655761719</v>
       </c>
       <c r="F24" t="n">
         <v>252</v>
@@ -912,16 +912,16 @@
         <v>38170</v>
       </c>
       <c r="B25" t="n">
-        <v>32.78959274291992</v>
+        <v>32.78959655761719</v>
       </c>
       <c r="C25" t="n">
-        <v>32.78959274291992</v>
+        <v>32.78959655761719</v>
       </c>
       <c r="D25" t="n">
-        <v>32.78959274291992</v>
+        <v>32.78959655761719</v>
       </c>
       <c r="E25" t="n">
-        <v>32.78959274291992</v>
+        <v>32.78959655761719</v>
       </c>
       <c r="F25" t="n">
         <v>303</v>
@@ -952,16 +952,16 @@
         <v>38819</v>
       </c>
       <c r="B27" t="n">
-        <v>61.89946746826172</v>
+        <v>61.89947128295898</v>
       </c>
       <c r="C27" t="n">
-        <v>61.89946746826172</v>
+        <v>61.89947128295898</v>
       </c>
       <c r="D27" t="n">
-        <v>61.89946746826172</v>
+        <v>61.89947128295898</v>
       </c>
       <c r="E27" t="n">
-        <v>61.89946746826172</v>
+        <v>61.89947128295898</v>
       </c>
       <c r="F27" t="n">
         <v>25</v>
@@ -992,16 +992,16 @@
         <v>38832</v>
       </c>
       <c r="B29" t="n">
-        <v>76.50905609130859</v>
+        <v>76.50906372070312</v>
       </c>
       <c r="C29" t="n">
-        <v>76.50905609130859</v>
+        <v>76.50906372070312</v>
       </c>
       <c r="D29" t="n">
-        <v>62.66455942368046</v>
+        <v>62.6645656725178</v>
       </c>
       <c r="E29" t="n">
-        <v>62.66455942368046</v>
+        <v>62.6645656725178</v>
       </c>
       <c r="F29" t="n">
         <v>50</v>
@@ -1052,16 +1052,16 @@
         <v>39078</v>
       </c>
       <c r="B32" t="n">
-        <v>65.57918548583984</v>
+        <v>65.57919311523438</v>
       </c>
       <c r="C32" t="n">
-        <v>65.57918548583984</v>
+        <v>65.57919311523438</v>
       </c>
       <c r="D32" t="n">
-        <v>65.57918548583984</v>
+        <v>65.57919311523438</v>
       </c>
       <c r="E32" t="n">
-        <v>65.57918548583984</v>
+        <v>65.57919311523438</v>
       </c>
       <c r="F32" t="n">
         <v>25</v>
@@ -1072,16 +1072,16 @@
         <v>39091</v>
       </c>
       <c r="B33" t="n">
-        <v>68.31166076660156</v>
+        <v>68.31166839599609</v>
       </c>
       <c r="C33" t="n">
-        <v>68.34809286117721</v>
+        <v>68.34810049464066</v>
       </c>
       <c r="D33" t="n">
-        <v>68.31166076660156</v>
+        <v>68.31166839599609</v>
       </c>
       <c r="E33" t="n">
-        <v>68.34809286117721</v>
+        <v>68.34810049464066</v>
       </c>
       <c r="F33" t="n">
         <v>75</v>
@@ -1092,16 +1092,16 @@
         <v>39094</v>
       </c>
       <c r="B34" t="n">
-        <v>68.71241760253906</v>
+        <v>68.71242523193359</v>
       </c>
       <c r="C34" t="n">
-        <v>68.71241760253906</v>
+        <v>68.71242523193359</v>
       </c>
       <c r="D34" t="n">
-        <v>65.57918763204418</v>
+        <v>65.57919491354457</v>
       </c>
       <c r="E34" t="n">
-        <v>65.57918763204418</v>
+        <v>65.57919491354457</v>
       </c>
       <c r="F34" t="n">
         <v>101</v>
@@ -1172,16 +1172,16 @@
         <v>39112</v>
       </c>
       <c r="B38" t="n">
-        <v>67.40084075927734</v>
+        <v>67.40083312988281</v>
       </c>
       <c r="C38" t="n">
-        <v>67.47371198266552</v>
+        <v>67.47370434502237</v>
       </c>
       <c r="D38" t="n">
-        <v>67.40084075927734</v>
+        <v>67.40083312988281</v>
       </c>
       <c r="E38" t="n">
-        <v>67.47371198266552</v>
+        <v>67.47370434502237</v>
       </c>
       <c r="F38" t="n">
         <v>151</v>
@@ -1192,16 +1192,16 @@
         <v>39121</v>
       </c>
       <c r="B39" t="n">
-        <v>67.40084075927734</v>
+        <v>67.40083312988281</v>
       </c>
       <c r="C39" t="n">
-        <v>67.40084075927734</v>
+        <v>67.40083312988281</v>
       </c>
       <c r="D39" t="n">
-        <v>67.40084075927734</v>
+        <v>67.40083312988281</v>
       </c>
       <c r="E39" t="n">
-        <v>67.40084075927734</v>
+        <v>67.40083312988281</v>
       </c>
       <c r="F39" t="n">
         <v>151</v>
@@ -1212,16 +1212,16 @@
         <v>39122</v>
       </c>
       <c r="B40" t="n">
-        <v>67.40084075927734</v>
+        <v>67.40083312988281</v>
       </c>
       <c r="C40" t="n">
-        <v>67.40084075927734</v>
+        <v>67.40083312988281</v>
       </c>
       <c r="D40" t="n">
-        <v>67.40084075927734</v>
+        <v>67.40083312988281</v>
       </c>
       <c r="E40" t="n">
-        <v>67.40084075927734</v>
+        <v>67.40083312988281</v>
       </c>
       <c r="F40" t="n">
         <v>151</v>
@@ -1292,16 +1292,16 @@
         <v>39188</v>
       </c>
       <c r="B44" t="n">
-        <v>91.08221435546875</v>
+        <v>91.08222198486328</v>
       </c>
       <c r="C44" t="n">
-        <v>91.08221435546875</v>
+        <v>91.08222198486328</v>
       </c>
       <c r="D44" t="n">
-        <v>91.08221435546875</v>
+        <v>91.08222198486328</v>
       </c>
       <c r="E44" t="n">
-        <v>91.08221435546875</v>
+        <v>91.08222198486328</v>
       </c>
       <c r="F44" t="n">
         <v>25</v>
@@ -1352,16 +1352,16 @@
         <v>39204</v>
       </c>
       <c r="B47" t="n">
-        <v>131.19482421875</v>
+        <v>131.1948394775391</v>
       </c>
       <c r="C47" t="n">
-        <v>131.19482421875</v>
+        <v>131.1948394775391</v>
       </c>
       <c r="D47" t="n">
-        <v>131.1583921249337</v>
+        <v>131.1584073794855</v>
       </c>
       <c r="E47" t="n">
-        <v>131.1583921249337</v>
+        <v>131.1584073794855</v>
       </c>
       <c r="F47" t="n">
         <v>682</v>
@@ -1372,16 +1372,16 @@
         <v>39218</v>
       </c>
       <c r="B48" t="n">
-        <v>134.8016967773438</v>
+        <v>134.8016815185547</v>
       </c>
       <c r="C48" t="n">
-        <v>134.8016967773438</v>
+        <v>134.8016815185547</v>
       </c>
       <c r="D48" t="n">
-        <v>134.8016967773438</v>
+        <v>134.8016815185547</v>
       </c>
       <c r="E48" t="n">
-        <v>134.8016967773438</v>
+        <v>134.8016815185547</v>
       </c>
       <c r="F48" t="n">
         <v>758</v>
@@ -1392,16 +1392,16 @@
         <v>39219</v>
       </c>
       <c r="B49" t="n">
-        <v>138.4449615478516</v>
+        <v>138.4449768066406</v>
       </c>
       <c r="C49" t="n">
-        <v>138.4449615478516</v>
+        <v>138.4449768066406</v>
       </c>
       <c r="D49" t="n">
-        <v>134.8016819667077</v>
+        <v>134.8016968239507</v>
       </c>
       <c r="E49" t="n">
-        <v>134.8016819667077</v>
+        <v>134.8016968239507</v>
       </c>
       <c r="F49" t="n">
         <v>328</v>
@@ -1512,16 +1512,16 @@
         <v>39274</v>
       </c>
       <c r="B55" t="n">
-        <v>164.6401977539062</v>
+        <v>164.6402282714844</v>
       </c>
       <c r="C55" t="n">
-        <v>164.6401977539062</v>
+        <v>164.6402282714844</v>
       </c>
       <c r="D55" t="n">
-        <v>164.6037656644627</v>
+        <v>164.6037961752879</v>
       </c>
       <c r="E55" t="n">
-        <v>164.6037656644627</v>
+        <v>164.6037961752879</v>
       </c>
       <c r="F55" t="n">
         <v>531</v>
@@ -1532,16 +1532,16 @@
         <v>39286</v>
       </c>
       <c r="B56" t="n">
-        <v>182.1644287109375</v>
+        <v>182.1644439697266</v>
       </c>
       <c r="C56" t="n">
-        <v>182.1644287109375</v>
+        <v>182.1644439697266</v>
       </c>
       <c r="D56" t="n">
-        <v>182.1644287109375</v>
+        <v>182.1644439697266</v>
       </c>
       <c r="E56" t="n">
-        <v>182.1644287109375</v>
+        <v>182.1644439697266</v>
       </c>
       <c r="F56" t="n">
         <v>50</v>
@@ -1552,16 +1552,16 @@
         <v>39295</v>
       </c>
       <c r="B57" t="n">
-        <v>182.1279754638672</v>
+        <v>182.1279907226562</v>
       </c>
       <c r="C57" t="n">
-        <v>182.1279754638672</v>
+        <v>182.1279907226562</v>
       </c>
       <c r="D57" t="n">
-        <v>182.1279754638672</v>
+        <v>182.1279907226562</v>
       </c>
       <c r="E57" t="n">
-        <v>182.1279754638672</v>
+        <v>182.1279907226562</v>
       </c>
       <c r="F57" t="n">
         <v>25</v>
@@ -1592,16 +1592,16 @@
         <v>39330</v>
       </c>
       <c r="B59" t="n">
-        <v>149.7755889892578</v>
+        <v>149.7756042480469</v>
       </c>
       <c r="C59" t="n">
-        <v>149.7755889892578</v>
+        <v>149.7756042480469</v>
       </c>
       <c r="D59" t="n">
-        <v>149.7755889892578</v>
+        <v>149.7756042480469</v>
       </c>
       <c r="E59" t="n">
-        <v>149.7755889892578</v>
+        <v>149.7756042480469</v>
       </c>
       <c r="F59" t="n">
         <v>50</v>
@@ -1612,16 +1612,16 @@
         <v>39345</v>
       </c>
       <c r="B60" t="n">
-        <v>153.0181121826172</v>
+        <v>153.0181274414062</v>
       </c>
       <c r="C60" t="n">
-        <v>153.0181121826172</v>
+        <v>153.0181274414062</v>
       </c>
       <c r="D60" t="n">
-        <v>153.0181121826172</v>
+        <v>153.0181274414062</v>
       </c>
       <c r="E60" t="n">
-        <v>153.0181121826172</v>
+        <v>153.0181274414062</v>
       </c>
       <c r="F60" t="n">
         <v>25</v>
@@ -1672,16 +1672,16 @@
         <v>39423</v>
       </c>
       <c r="B63" t="n">
-        <v>156.6614227294922</v>
+        <v>156.6614074707031</v>
       </c>
       <c r="C63" t="n">
-        <v>163.9480109948773</v>
+        <v>163.9479950263761</v>
       </c>
       <c r="D63" t="n">
-        <v>156.6614227294922</v>
+        <v>156.6614074707031</v>
       </c>
       <c r="E63" t="n">
-        <v>163.9480109948773</v>
+        <v>163.9479950263761</v>
       </c>
       <c r="F63" t="n">
         <v>75</v>
@@ -1692,16 +1692,16 @@
         <v>39455</v>
       </c>
       <c r="B64" t="n">
-        <v>196.3206939697266</v>
+        <v>196.3207092285156</v>
       </c>
       <c r="C64" t="n">
-        <v>196.5222586352784</v>
+        <v>196.5222739097339</v>
       </c>
       <c r="D64" t="n">
-        <v>196.3206939697266</v>
+        <v>196.3207092285156</v>
       </c>
       <c r="E64" t="n">
-        <v>196.5222586352784</v>
+        <v>196.5222739097339</v>
       </c>
       <c r="F64" t="n">
         <v>219</v>
@@ -1712,16 +1712,16 @@
         <v>39456</v>
       </c>
       <c r="B65" t="n">
-        <v>196.5222473144531</v>
+        <v>196.5222625732422</v>
       </c>
       <c r="C65" t="n">
-        <v>196.5222473144531</v>
+        <v>196.5222625732422</v>
       </c>
       <c r="D65" t="n">
-        <v>196.5222473144531</v>
+        <v>196.5222625732422</v>
       </c>
       <c r="E65" t="n">
-        <v>196.5222473144531</v>
+        <v>196.5222625732422</v>
       </c>
       <c r="F65" t="n">
         <v>73</v>
@@ -1792,16 +1792,16 @@
         <v>39471</v>
       </c>
       <c r="B69" t="n">
-        <v>156.7643127441406</v>
+        <v>156.7642822265625</v>
       </c>
       <c r="C69" t="n">
-        <v>156.7643127441406</v>
+        <v>156.7642822265625</v>
       </c>
       <c r="D69" t="n">
-        <v>156.7139180583274</v>
+        <v>156.7138875505597</v>
       </c>
       <c r="E69" t="n">
-        <v>156.7139180583274</v>
+        <v>156.7138875505597</v>
       </c>
       <c r="F69" t="n">
         <v>493</v>
@@ -1812,16 +1812,16 @@
         <v>39476</v>
       </c>
       <c r="B70" t="n">
-        <v>157.7217254638672</v>
+        <v>157.7217102050781</v>
       </c>
       <c r="C70" t="n">
-        <v>161.2490440849197</v>
+        <v>161.2490284848802</v>
       </c>
       <c r="D70" t="n">
-        <v>156.2100114572659</v>
+        <v>156.2099963447277</v>
       </c>
       <c r="E70" t="n">
-        <v>161.2490440849197</v>
+        <v>161.2490284848802</v>
       </c>
       <c r="F70" t="n">
         <v>146</v>
@@ -1872,16 +1872,16 @@
         <v>39486</v>
       </c>
       <c r="B73" t="n">
-        <v>156.1595916748047</v>
+        <v>156.1596069335938</v>
       </c>
       <c r="C73" t="n">
-        <v>156.2099863518973</v>
+        <v>156.2100016156106</v>
       </c>
       <c r="D73" t="n">
-        <v>156.1595916748047</v>
+        <v>156.1596069335938</v>
       </c>
       <c r="E73" t="n">
-        <v>156.2099863518973</v>
+        <v>156.2100016156106</v>
       </c>
       <c r="F73" t="n">
         <v>512</v>
@@ -1892,16 +1892,16 @@
         <v>39490</v>
       </c>
       <c r="B74" t="n">
-        <v>156.1092224121094</v>
+        <v>156.1092071533203</v>
       </c>
       <c r="C74" t="n">
-        <v>156.1092224121094</v>
+        <v>156.1092071533203</v>
       </c>
       <c r="D74" t="n">
-        <v>156.1092224121094</v>
+        <v>156.1092071533203</v>
       </c>
       <c r="E74" t="n">
-        <v>156.1092224121094</v>
+        <v>156.1092071533203</v>
       </c>
       <c r="F74" t="n">
         <v>91</v>
@@ -1912,16 +1912,16 @@
         <v>39491</v>
       </c>
       <c r="B75" t="n">
-        <v>156.1092224121094</v>
+        <v>156.1092071533203</v>
       </c>
       <c r="C75" t="n">
-        <v>156.1092224121094</v>
+        <v>156.1092071533203</v>
       </c>
       <c r="D75" t="n">
-        <v>156.1092224121094</v>
+        <v>156.1092071533203</v>
       </c>
       <c r="E75" t="n">
-        <v>156.1092224121094</v>
+        <v>156.1092071533203</v>
       </c>
       <c r="F75" t="n">
         <v>54</v>
@@ -1932,16 +1932,16 @@
         <v>39493</v>
       </c>
       <c r="B76" t="n">
-        <v>156.1092224121094</v>
+        <v>156.1092071533203</v>
       </c>
       <c r="C76" t="n">
-        <v>156.1596030318512</v>
+        <v>156.1595877681377</v>
       </c>
       <c r="D76" t="n">
-        <v>138.3214327553723</v>
+        <v>138.3214192352385</v>
       </c>
       <c r="E76" t="n">
-        <v>138.3214327553723</v>
+        <v>138.3214192352385</v>
       </c>
       <c r="F76" t="n">
         <v>219</v>
@@ -1952,16 +1952,16 @@
         <v>39496</v>
       </c>
       <c r="B77" t="n">
-        <v>156.1092224121094</v>
+        <v>156.1092071533203</v>
       </c>
       <c r="C77" t="n">
-        <v>156.1596030318512</v>
+        <v>156.1595877681377</v>
       </c>
       <c r="D77" t="n">
-        <v>156.1092224121094</v>
+        <v>156.1092071533203</v>
       </c>
       <c r="E77" t="n">
-        <v>156.1596030318512</v>
+        <v>156.1595877681377</v>
       </c>
       <c r="F77" t="n">
         <v>256</v>
@@ -1972,16 +1972,16 @@
         <v>39497</v>
       </c>
       <c r="B78" t="n">
-        <v>153.6401062011719</v>
+        <v>153.6400909423828</v>
       </c>
       <c r="C78" t="n">
-        <v>153.6401062011719</v>
+        <v>153.6400909423828</v>
       </c>
       <c r="D78" t="n">
-        <v>153.6401062011719</v>
+        <v>153.6400909423828</v>
       </c>
       <c r="E78" t="n">
-        <v>153.6401062011719</v>
+        <v>153.6400909423828</v>
       </c>
       <c r="F78" t="n">
         <v>438</v>
@@ -1992,16 +1992,16 @@
         <v>39498</v>
       </c>
       <c r="B79" t="n">
-        <v>156.1595916748047</v>
+        <v>156.1596069335938</v>
       </c>
       <c r="C79" t="n">
-        <v>156.2099863518973</v>
+        <v>156.2100016156106</v>
       </c>
       <c r="D79" t="n">
-        <v>153.5896881193179</v>
+        <v>153.5897031269945</v>
       </c>
       <c r="E79" t="n">
-        <v>153.5896881193179</v>
+        <v>153.5897031269945</v>
       </c>
       <c r="F79" t="n">
         <v>1133</v>
@@ -2012,16 +2012,16 @@
         <v>39499</v>
       </c>
       <c r="B80" t="n">
-        <v>161.2490234375</v>
+        <v>161.2490386962891</v>
       </c>
       <c r="C80" t="n">
-        <v>171.3270874023438</v>
+        <v>171.3271036148071</v>
       </c>
       <c r="D80" t="n">
-        <v>155.2021822463907</v>
+        <v>155.2021969329749</v>
       </c>
       <c r="E80" t="n">
-        <v>156.2099914550781</v>
+        <v>156.21000623703</v>
       </c>
       <c r="F80" t="n">
         <v>1243</v>
@@ -2032,16 +2032,16 @@
         <v>39500</v>
       </c>
       <c r="B81" t="n">
-        <v>168.3036956787109</v>
+        <v>168.3036804199219</v>
       </c>
       <c r="C81" t="n">
-        <v>171.3271096361179</v>
+        <v>171.3270941032194</v>
       </c>
       <c r="D81" t="n">
-        <v>156.2604064123276</v>
+        <v>156.26039224541</v>
       </c>
       <c r="E81" t="n">
-        <v>171.3271096361179</v>
+        <v>171.3270941032194</v>
       </c>
       <c r="F81" t="n">
         <v>530</v>
@@ -2052,16 +2052,16 @@
         <v>39503</v>
       </c>
       <c r="B82" t="n">
-        <v>170.8231811523438</v>
+        <v>170.8231964111328</v>
       </c>
       <c r="C82" t="n">
-        <v>171.1255210998343</v>
+        <v>171.1255363856299</v>
       </c>
       <c r="D82" t="n">
-        <v>163.7685448815244</v>
+        <v>163.7685595101577</v>
       </c>
       <c r="E82" t="n">
-        <v>171.1255210998343</v>
+        <v>171.1255363856299</v>
       </c>
       <c r="F82" t="n">
         <v>256</v>
@@ -2092,16 +2092,16 @@
         <v>39505</v>
       </c>
       <c r="B84" t="n">
-        <v>158.7295074462891</v>
+        <v>158.7295227050781</v>
       </c>
       <c r="C84" t="n">
-        <v>159.6869219338314</v>
+        <v>159.6869372846574</v>
       </c>
       <c r="D84" t="n">
-        <v>156.2099845361662</v>
+        <v>156.2099995527516</v>
       </c>
       <c r="E84" t="n">
-        <v>156.2099845361662</v>
+        <v>156.2099995527516</v>
       </c>
       <c r="F84" t="n">
         <v>91</v>
@@ -2112,16 +2112,16 @@
         <v>39506</v>
       </c>
       <c r="B85" t="n">
-        <v>158.4775695800781</v>
+        <v>158.4775543212891</v>
       </c>
       <c r="C85" t="n">
-        <v>161.2490381259182</v>
+        <v>161.2490226002822</v>
       </c>
       <c r="D85" t="n">
-        <v>154.1943870835026</v>
+        <v>154.1943722371138</v>
       </c>
       <c r="E85" t="n">
-        <v>158.729528935709</v>
+        <v>158.7295136526604</v>
       </c>
       <c r="F85" t="n">
         <v>237</v>
@@ -2132,16 +2132,16 @@
         <v>39507</v>
       </c>
       <c r="B86" t="n">
-        <v>158.7295074462891</v>
+        <v>158.7295227050781</v>
       </c>
       <c r="C86" t="n">
-        <v>158.7295074462891</v>
+        <v>158.7295227050781</v>
       </c>
       <c r="D86" t="n">
-        <v>126.026188657286</v>
+        <v>126.02620077228</v>
       </c>
       <c r="E86" t="n">
-        <v>153.7408563025501</v>
+        <v>153.7408710817763</v>
       </c>
       <c r="F86" t="n">
         <v>2688</v>
@@ -2212,16 +2212,16 @@
         <v>39513</v>
       </c>
       <c r="B90" t="n">
-        <v>156.1092224121094</v>
+        <v>156.1092071533203</v>
       </c>
       <c r="C90" t="n">
-        <v>156.7139023371383</v>
+        <v>156.7138870192452</v>
       </c>
       <c r="D90" t="n">
-        <v>148.6514564667003</v>
+        <v>148.6514419368654</v>
       </c>
       <c r="E90" t="n">
-        <v>156.2099977126089</v>
+        <v>156.2099824439696</v>
       </c>
       <c r="F90" t="n">
         <v>640</v>
@@ -2232,16 +2232,16 @@
         <v>39514</v>
       </c>
       <c r="B91" t="n">
-        <v>157.7217254638672</v>
+        <v>157.7217102050781</v>
       </c>
       <c r="C91" t="n">
-        <v>158.0744601381759</v>
+        <v>158.0744448452615</v>
       </c>
       <c r="D91" t="n">
-        <v>151.1709788296122</v>
+        <v>151.1709642045751</v>
       </c>
       <c r="E91" t="n">
-        <v>158.0744601381759</v>
+        <v>158.0744448452615</v>
       </c>
       <c r="F91" t="n">
         <v>91</v>
@@ -2252,16 +2252,16 @@
         <v>39517</v>
       </c>
       <c r="B92" t="n">
-        <v>161.2490234375</v>
+        <v>161.2490386962891</v>
       </c>
       <c r="C92" t="n">
-        <v>161.2490234375</v>
+        <v>161.2490386962891</v>
       </c>
       <c r="D92" t="n">
-        <v>161.2490234375</v>
+        <v>161.2490386962891</v>
       </c>
       <c r="E92" t="n">
-        <v>161.2490234375</v>
+        <v>161.2490386962891</v>
       </c>
       <c r="F92" t="n">
         <v>18</v>
@@ -2272,16 +2272,16 @@
         <v>39518</v>
       </c>
       <c r="B93" t="n">
-        <v>166.2880554199219</v>
+        <v>166.2880706787109</v>
       </c>
       <c r="C93" t="n">
-        <v>166.2880554199219</v>
+        <v>166.2880706787109</v>
       </c>
       <c r="D93" t="n">
-        <v>161.198628758761</v>
+        <v>161.1986435505383</v>
       </c>
       <c r="E93" t="n">
-        <v>161.2490234375</v>
+        <v>161.2490382339015</v>
       </c>
       <c r="F93" t="n">
         <v>128</v>
@@ -2312,16 +2312,16 @@
         <v>39520</v>
       </c>
       <c r="B95" t="n">
-        <v>165.7337951660156</v>
+        <v>165.7337799072266</v>
       </c>
       <c r="C95" t="n">
-        <v>165.7337951660156</v>
+        <v>165.7337799072266</v>
       </c>
       <c r="D95" t="n">
-        <v>162.7103670844672</v>
+        <v>162.7103521040393</v>
       </c>
       <c r="E95" t="n">
-        <v>162.7103670844672</v>
+        <v>162.7103521040393</v>
       </c>
       <c r="F95" t="n">
         <v>109</v>
@@ -2332,16 +2332,16 @@
         <v>39521</v>
       </c>
       <c r="B96" t="n">
-        <v>164.7763519287109</v>
+        <v>164.7763366699219</v>
       </c>
       <c r="C96" t="n">
-        <v>165.2298759437404</v>
+        <v>165.2298606429536</v>
       </c>
       <c r="D96" t="n">
-        <v>163.7685567179091</v>
+        <v>163.7685415524449</v>
       </c>
       <c r="E96" t="n">
-        <v>165.2298759437404</v>
+        <v>165.2298606429536</v>
       </c>
       <c r="F96" t="n">
         <v>329</v>
@@ -2372,16 +2372,16 @@
         <v>39526</v>
       </c>
       <c r="B98" t="n">
-        <v>161.2490234375</v>
+        <v>161.2490386962891</v>
       </c>
       <c r="C98" t="n">
-        <v>163.7685464592186</v>
+        <v>163.7685619564269</v>
       </c>
       <c r="D98" t="n">
-        <v>151.4229188053357</v>
+        <v>151.4229331342931</v>
       </c>
       <c r="E98" t="n">
-        <v>163.7685464592186</v>
+        <v>163.7685619564269</v>
       </c>
       <c r="F98" t="n">
         <v>54</v>
@@ -2412,16 +2412,16 @@
         <v>39531</v>
       </c>
       <c r="B100" t="n">
-        <v>157.7217254638672</v>
+        <v>157.7217102050781</v>
       </c>
       <c r="C100" t="n">
-        <v>160.2412347471855</v>
+        <v>160.2412192446465</v>
       </c>
       <c r="D100" t="n">
-        <v>151.4229381945543</v>
+        <v>151.4229235451414</v>
       </c>
       <c r="E100" t="n">
-        <v>160.2412347471855</v>
+        <v>160.2412192446465</v>
       </c>
       <c r="F100" t="n">
         <v>146</v>
@@ -2452,16 +2452,16 @@
         <v>39533</v>
       </c>
       <c r="B102" t="n">
-        <v>155.1014099121094</v>
+        <v>155.1014251708984</v>
       </c>
       <c r="C102" t="n">
-        <v>156.2099944384316</v>
+        <v>156.2100098062826</v>
       </c>
       <c r="D102" t="n">
-        <v>155.1014099121094</v>
+        <v>155.1014251708984</v>
       </c>
       <c r="E102" t="n">
-        <v>156.2099944384316</v>
+        <v>156.2100098062826</v>
       </c>
       <c r="F102" t="n">
         <v>438</v>
@@ -2472,16 +2472,16 @@
         <v>39534</v>
       </c>
       <c r="B103" t="n">
-        <v>132.5265655517578</v>
+        <v>132.5265502929688</v>
       </c>
       <c r="C103" t="n">
-        <v>152.1283971854909</v>
+        <v>152.1283796697942</v>
       </c>
       <c r="D103" t="n">
-        <v>132.5265655517578</v>
+        <v>132.5265502929688</v>
       </c>
       <c r="E103" t="n">
-        <v>137.0616936209453</v>
+        <v>137.0616778399926</v>
       </c>
       <c r="F103" t="n">
         <v>6199</v>
@@ -2512,16 +2512,16 @@
         <v>39538</v>
       </c>
       <c r="B105" t="n">
-        <v>123.4058990478516</v>
+        <v>123.4059143066406</v>
       </c>
       <c r="C105" t="n">
-        <v>128.4953258379637</v>
+        <v>128.4953417260459</v>
       </c>
       <c r="D105" t="n">
-        <v>115.8977385322151</v>
+        <v>115.8977528626414</v>
       </c>
       <c r="E105" t="n">
-        <v>128.4953258379637</v>
+        <v>128.4953417260459</v>
       </c>
       <c r="F105" t="n">
         <v>4078</v>
@@ -2532,16 +2532,16 @@
         <v>39539</v>
       </c>
       <c r="B106" t="n">
-        <v>123.4563064575195</v>
+        <v>123.456298828125</v>
       </c>
       <c r="C106" t="n">
-        <v>125.975815741848</v>
+        <v>125.9758079567519</v>
       </c>
       <c r="D106" t="n">
-        <v>117.4094644897074</v>
+        <v>117.4094572339977</v>
       </c>
       <c r="E106" t="n">
-        <v>119.4250691049667</v>
+        <v>119.425061724696</v>
       </c>
       <c r="F106" t="n">
         <v>4644</v>
@@ -2552,16 +2552,16 @@
         <v>39540</v>
       </c>
       <c r="B107" t="n">
-        <v>120.936767578125</v>
+        <v>120.9367599487305</v>
       </c>
       <c r="C107" t="n">
-        <v>125.9757995605469</v>
+        <v>125.9757916132609</v>
       </c>
       <c r="D107" t="n">
-        <v>119.9289583694376</v>
+        <v>119.9289508036215</v>
       </c>
       <c r="E107" t="n">
-        <v>125.9757995605469</v>
+        <v>125.9757916132609</v>
       </c>
       <c r="F107" t="n">
         <v>5193</v>
@@ -2572,16 +2572,16 @@
         <v>39541</v>
       </c>
       <c r="B108" t="n">
-        <v>120.936767578125</v>
+        <v>120.9367599487305</v>
       </c>
       <c r="C108" t="n">
-        <v>120.936767578125</v>
+        <v>120.9367599487305</v>
       </c>
       <c r="D108" t="n">
-        <v>118.4172586174217</v>
+        <v>118.4172511469724</v>
       </c>
       <c r="E108" t="n">
-        <v>119.3242784686312</v>
+        <v>119.3242709409619</v>
       </c>
       <c r="F108" t="n">
         <v>8064</v>
@@ -2592,16 +2592,16 @@
         <v>39542</v>
       </c>
       <c r="B109" t="n">
-        <v>118.4172592163086</v>
+        <v>118.4172744750977</v>
       </c>
       <c r="C109" t="n">
-        <v>120.3824689038681</v>
+        <v>120.3824844158865</v>
       </c>
       <c r="D109" t="n">
-        <v>115.8977361818477</v>
+        <v>115.8977511159808</v>
       </c>
       <c r="E109" t="n">
-        <v>120.3824689038681</v>
+        <v>120.3824844158865</v>
       </c>
       <c r="F109" t="n">
         <v>17409</v>
@@ -2612,16 +2612,16 @@
         <v>39545</v>
       </c>
       <c r="B110" t="n">
-        <v>120.936767578125</v>
+        <v>120.9367599487305</v>
       </c>
       <c r="C110" t="n">
-        <v>122.3980867124172</v>
+        <v>122.3980789908342</v>
       </c>
       <c r="D110" t="n">
-        <v>120.936767578125</v>
+        <v>120.9367599487305</v>
       </c>
       <c r="E110" t="n">
-        <v>120.936767578125</v>
+        <v>120.9367599487305</v>
       </c>
       <c r="F110" t="n">
         <v>91</v>
@@ -2632,16 +2632,16 @@
         <v>39546</v>
       </c>
       <c r="B111" t="n">
-        <v>120.936767578125</v>
+        <v>120.9367599487305</v>
       </c>
       <c r="C111" t="n">
-        <v>120.936767578125</v>
+        <v>120.9367599487305</v>
       </c>
       <c r="D111" t="n">
-        <v>115.8977355957031</v>
+        <v>115.8977282842</v>
       </c>
       <c r="E111" t="n">
-        <v>120.936767578125</v>
+        <v>120.9367599487305</v>
       </c>
       <c r="F111" t="n">
         <v>1481</v>
@@ -2652,16 +2652,16 @@
         <v>39547</v>
       </c>
       <c r="B112" t="n">
-        <v>120.936767578125</v>
+        <v>120.9367599487305</v>
       </c>
       <c r="C112" t="n">
-        <v>125.9757995605469</v>
+        <v>125.9757916132609</v>
       </c>
       <c r="D112" t="n">
-        <v>118.4172586174217</v>
+        <v>118.4172511469724</v>
       </c>
       <c r="E112" t="n">
-        <v>125.9757995605469</v>
+        <v>125.9757916132609</v>
       </c>
       <c r="F112" t="n">
         <v>475</v>
@@ -2692,16 +2692,16 @@
         <v>39549</v>
       </c>
       <c r="B114" t="n">
-        <v>125.169563293457</v>
+        <v>125.1695785522461</v>
       </c>
       <c r="C114" t="n">
-        <v>125.9758079015865</v>
+        <v>125.9758232586608</v>
       </c>
       <c r="D114" t="n">
-        <v>118.4172664579994</v>
+        <v>118.4172808936501</v>
       </c>
       <c r="E114" t="n">
-        <v>125.9758079015865</v>
+        <v>125.9758232586608</v>
       </c>
       <c r="F114" t="n">
         <v>54</v>
@@ -2712,16 +2712,16 @@
         <v>39552</v>
       </c>
       <c r="B115" t="n">
-        <v>124.9679718017578</v>
+        <v>124.9679870605469</v>
       </c>
       <c r="C115" t="n">
-        <v>124.9679718017578</v>
+        <v>124.9679870605469</v>
       </c>
       <c r="D115" t="n">
-        <v>124.4640672722131</v>
+        <v>124.4640824694746</v>
       </c>
       <c r="E115" t="n">
-        <v>124.9679718017578</v>
+        <v>124.9679870605469</v>
       </c>
       <c r="F115" t="n">
         <v>1901</v>
@@ -2732,16 +2732,16 @@
         <v>39553</v>
       </c>
       <c r="B116" t="n">
-        <v>125.9253921508789</v>
+        <v>125.925422668457</v>
       </c>
       <c r="C116" t="n">
-        <v>125.9253921508789</v>
+        <v>125.925422668457</v>
       </c>
       <c r="D116" t="n">
-        <v>121.4406599049416</v>
+        <v>121.4406893356605</v>
       </c>
       <c r="E116" t="n">
-        <v>125.1191476776425</v>
+        <v>125.1191779998301</v>
       </c>
       <c r="F116" t="n">
         <v>54</v>
@@ -2752,16 +2752,16 @@
         <v>39554</v>
       </c>
       <c r="B117" t="n">
-        <v>129.9566345214844</v>
+        <v>129.9566497802734</v>
       </c>
       <c r="C117" t="n">
-        <v>131.0148242893086</v>
+        <v>131.0148396723445</v>
       </c>
       <c r="D117" t="n">
-        <v>125.9253979099248</v>
+        <v>125.9254126953884</v>
       </c>
       <c r="E117" t="n">
-        <v>131.0148242893086</v>
+        <v>131.0148396723445</v>
       </c>
       <c r="F117" t="n">
         <v>164</v>
@@ -2772,16 +2772,16 @@
         <v>39555</v>
       </c>
       <c r="B118" t="n">
-        <v>126.9835891723633</v>
+        <v>126.9836044311523</v>
       </c>
       <c r="C118" t="n">
-        <v>132.0226203771315</v>
+        <v>132.0226362414281</v>
       </c>
       <c r="D118" t="n">
-        <v>126.9835891723633</v>
+        <v>126.9836044311523</v>
       </c>
       <c r="E118" t="n">
-        <v>132.0226203771315</v>
+        <v>132.0226362414281</v>
       </c>
       <c r="F118" t="n">
         <v>347</v>
@@ -2792,16 +2792,16 @@
         <v>39556</v>
       </c>
       <c r="B119" t="n">
-        <v>125.9758148193359</v>
+        <v>125.9757995605469</v>
       </c>
       <c r="C119" t="n">
-        <v>126.479719484715</v>
+        <v>126.4797041648906</v>
       </c>
       <c r="D119" t="n">
-        <v>125.9758148193359</v>
+        <v>125.9757995605469</v>
       </c>
       <c r="E119" t="n">
-        <v>126.479719484715</v>
+        <v>126.4797041648906</v>
       </c>
       <c r="F119" t="n">
         <v>36</v>
@@ -2872,16 +2872,16 @@
         <v>39563</v>
       </c>
       <c r="B123" t="n">
-        <v>123.4563064575195</v>
+        <v>123.456298828125</v>
       </c>
       <c r="C123" t="n">
-        <v>128.4953390871935</v>
+        <v>128.4953311463951</v>
       </c>
       <c r="D123" t="n">
-        <v>120.936783112174</v>
+        <v>120.9367756384818</v>
       </c>
       <c r="E123" t="n">
-        <v>120.936783112174</v>
+        <v>120.9367756384818</v>
       </c>
       <c r="F123" t="n">
         <v>9180</v>
@@ -2892,16 +2892,16 @@
         <v>39566</v>
       </c>
       <c r="B124" t="n">
-        <v>123.4563064575195</v>
+        <v>123.456298828125</v>
       </c>
       <c r="C124" t="n">
-        <v>127.9914344181243</v>
+        <v>127.9914265084664</v>
       </c>
       <c r="D124" t="n">
-        <v>120.936783112174</v>
+        <v>120.9367756384818</v>
       </c>
       <c r="E124" t="n">
-        <v>123.4563064575195</v>
+        <v>123.456298828125</v>
       </c>
       <c r="F124" t="n">
         <v>11941</v>
@@ -3072,16 +3072,16 @@
         <v>39581</v>
       </c>
       <c r="B133" t="n">
-        <v>135.1990356445312</v>
+        <v>135.1990203857422</v>
       </c>
       <c r="C133" t="n">
-        <v>135.1990356445312</v>
+        <v>135.1990203857422</v>
       </c>
       <c r="D133" t="n">
-        <v>127.7873689581211</v>
+        <v>127.7873545358251</v>
       </c>
       <c r="E133" t="n">
-        <v>128.0429515408066</v>
+        <v>128.0429370896651</v>
       </c>
       <c r="F133" t="n">
         <v>640</v>
@@ -3212,16 +3212,16 @@
         <v>39594</v>
       </c>
       <c r="B140" t="n">
-        <v>127.7362442016602</v>
+        <v>127.7362594604492</v>
       </c>
       <c r="C140" t="n">
-        <v>127.7362442016602</v>
+        <v>127.7362594604492</v>
       </c>
       <c r="D140" t="n">
-        <v>125.4871917376092</v>
+        <v>125.4872067277367</v>
       </c>
       <c r="E140" t="n">
-        <v>127.5317952599946</v>
+        <v>127.5318104943611</v>
       </c>
       <c r="F140" t="n">
         <v>274</v>
@@ -3232,16 +3232,16 @@
         <v>39595</v>
       </c>
       <c r="B141" t="n">
-        <v>128.8096618652344</v>
+        <v>128.8096771240234</v>
       </c>
       <c r="C141" t="n">
-        <v>128.8096618652344</v>
+        <v>128.8096771240234</v>
       </c>
       <c r="D141" t="n">
-        <v>122.6758657262773</v>
+        <v>122.6758802584571</v>
       </c>
       <c r="E141" t="n">
-        <v>123.1870165931251</v>
+        <v>123.1870311858557</v>
       </c>
       <c r="F141" t="n">
         <v>676</v>
@@ -3372,16 +3372,16 @@
         <v>39605</v>
       </c>
       <c r="B148" t="n">
-        <v>126.7139587402344</v>
+        <v>126.7139739990234</v>
       </c>
       <c r="C148" t="n">
-        <v>126.7139587402344</v>
+        <v>126.7139739990234</v>
       </c>
       <c r="D148" t="n">
-        <v>126.7139587402344</v>
+        <v>126.7139739990234</v>
       </c>
       <c r="E148" t="n">
-        <v>126.7139587402344</v>
+        <v>126.7139739990234</v>
       </c>
       <c r="F148" t="n">
         <v>18</v>
@@ -3432,16 +3432,16 @@
         <v>39610</v>
       </c>
       <c r="B151" t="n">
-        <v>127.7362442016602</v>
+        <v>127.7362594604492</v>
       </c>
       <c r="C151" t="n">
-        <v>127.7873635686847</v>
+        <v>127.7873788335802</v>
       </c>
       <c r="D151" t="n">
-        <v>118.5866762443826</v>
+        <v>118.586690410206</v>
       </c>
       <c r="E151" t="n">
-        <v>127.7873635686847</v>
+        <v>127.7873788335802</v>
       </c>
       <c r="F151" t="n">
         <v>14867</v>
@@ -3452,16 +3452,16 @@
         <v>39611</v>
       </c>
       <c r="B152" t="n">
-        <v>127.7873764038086</v>
+        <v>127.7873611450195</v>
       </c>
       <c r="C152" t="n">
-        <v>131.8765695960869</v>
+        <v>131.876553849017</v>
       </c>
       <c r="D152" t="n">
-        <v>126.5095062055749</v>
+        <v>126.5094910993733</v>
       </c>
       <c r="E152" t="n">
-        <v>129.8319801315566</v>
+        <v>129.8319646286262</v>
       </c>
       <c r="F152" t="n">
         <v>14940</v>
@@ -3492,16 +3492,16 @@
         <v>39616</v>
       </c>
       <c r="B154" t="n">
-        <v>127.7362442016602</v>
+        <v>127.7362594604492</v>
       </c>
       <c r="C154" t="n">
-        <v>127.7362442016602</v>
+        <v>127.7362594604492</v>
       </c>
       <c r="D154" t="n">
-        <v>120.3756971948618</v>
+        <v>120.3757115743935</v>
       </c>
       <c r="E154" t="n">
-        <v>120.3756971948618</v>
+        <v>120.3757115743935</v>
       </c>
       <c r="F154" t="n">
         <v>274</v>
@@ -3512,16 +3512,16 @@
         <v>39617</v>
       </c>
       <c r="B155" t="n">
-        <v>126.25390625</v>
+        <v>126.2538909912109</v>
       </c>
       <c r="C155" t="n">
-        <v>126.25390625</v>
+        <v>126.2538909912109</v>
       </c>
       <c r="D155" t="n">
-        <v>125.2316187898927</v>
+        <v>125.2316036546552</v>
       </c>
       <c r="E155" t="n">
-        <v>125.2316187898927</v>
+        <v>125.2316036546552</v>
       </c>
       <c r="F155" t="n">
         <v>22182</v>
@@ -3552,16 +3552,16 @@
         <v>39623</v>
       </c>
       <c r="B157" t="n">
-        <v>118.5867004394531</v>
+        <v>118.5866928100586</v>
       </c>
       <c r="C157" t="n">
-        <v>121.3980237247152</v>
+        <v>121.3980159144513</v>
       </c>
       <c r="D157" t="n">
-        <v>107.341407298405</v>
+        <v>107.3414003924877</v>
       </c>
       <c r="E157" t="n">
-        <v>120.3757217549437</v>
+        <v>120.3757140104507</v>
       </c>
       <c r="F157" t="n">
         <v>2925</v>
@@ -3612,16 +3612,16 @@
         <v>39626</v>
       </c>
       <c r="B160" t="n">
-        <v>111.9417343139648</v>
+        <v>111.9417419433594</v>
       </c>
       <c r="C160" t="n">
-        <v>113.9863379323162</v>
+        <v>113.9863457010608</v>
       </c>
       <c r="D160" t="n">
-        <v>107.3413904358912</v>
+        <v>107.3413977517491</v>
       </c>
       <c r="E160" t="n">
-        <v>107.3413904358912</v>
+        <v>107.3413977517491</v>
       </c>
       <c r="F160" t="n">
         <v>621</v>
@@ -3632,16 +3632,16 @@
         <v>39629</v>
       </c>
       <c r="B161" t="n">
-        <v>105.552375793457</v>
+        <v>105.5523681640625</v>
       </c>
       <c r="C161" t="n">
-        <v>117.5643871206494</v>
+        <v>117.5643786230189</v>
       </c>
       <c r="D161" t="n">
-        <v>97.11840675184081</v>
+        <v>97.11839973205907</v>
       </c>
       <c r="E161" t="n">
-        <v>117.5643871206494</v>
+        <v>117.5643786230189</v>
       </c>
       <c r="F161" t="n">
         <v>1865</v>
@@ -3652,16 +3652,16 @@
         <v>39630</v>
       </c>
       <c r="B162" t="n">
-        <v>104.78564453125</v>
+        <v>104.7856521606445</v>
       </c>
       <c r="C162" t="n">
-        <v>107.3413919588415</v>
+        <v>107.3413997743188</v>
       </c>
       <c r="D162" t="n">
-        <v>102.2298971036585</v>
+        <v>102.2299045469703</v>
       </c>
       <c r="E162" t="n">
-        <v>107.3413919588415</v>
+        <v>107.3413997743188</v>
       </c>
       <c r="F162" t="n">
         <v>146</v>
@@ -3672,16 +3672,16 @@
         <v>39631</v>
       </c>
       <c r="B163" t="n">
-        <v>104.5300674438477</v>
+        <v>104.5300750732422</v>
       </c>
       <c r="C163" t="n">
-        <v>107.3413902834806</v>
+        <v>107.3413981180667</v>
       </c>
       <c r="D163" t="n">
-        <v>99.67414812037485</v>
+        <v>99.67415539534768</v>
       </c>
       <c r="E163" t="n">
-        <v>107.3413902834806</v>
+        <v>107.3413981180667</v>
       </c>
       <c r="F163" t="n">
         <v>256</v>
@@ -3832,16 +3832,16 @@
         <v>39647</v>
       </c>
       <c r="B171" t="n">
-        <v>101.1053771972656</v>
+        <v>101.1053848266602</v>
       </c>
       <c r="C171" t="n">
-        <v>102.229903569147</v>
+        <v>102.2299112833981</v>
       </c>
       <c r="D171" t="n">
-        <v>92.00691321223229</v>
+        <v>92.00692015505828</v>
       </c>
       <c r="E171" t="n">
-        <v>92.00691321223229</v>
+        <v>92.00692015505828</v>
       </c>
       <c r="F171" t="n">
         <v>438</v>
@@ -3932,16 +3932,16 @@
         <v>39658</v>
       </c>
       <c r="B176" t="n">
-        <v>84.33966064453125</v>
+        <v>84.33966827392578</v>
       </c>
       <c r="C176" t="n">
-        <v>87.66213426394978</v>
+        <v>87.66214219389641</v>
       </c>
       <c r="D176" t="n">
-        <v>79.2281660600142</v>
+        <v>79.22817322702119</v>
       </c>
       <c r="E176" t="n">
-        <v>79.48374150240087</v>
+        <v>79.4837486925273</v>
       </c>
       <c r="F176" t="n">
         <v>89717</v>
@@ -4112,16 +4112,16 @@
         <v>39673</v>
       </c>
       <c r="B185" t="n">
-        <v>84.33966064453125</v>
+        <v>84.33966827392578</v>
       </c>
       <c r="C185" t="n">
-        <v>84.33966064453125</v>
+        <v>84.33966827392578</v>
       </c>
       <c r="D185" t="n">
-        <v>81.78391335227273</v>
+        <v>81.78392075047348</v>
       </c>
       <c r="E185" t="n">
-        <v>81.78391335227273</v>
+        <v>81.78392075047348</v>
       </c>
       <c r="F185" t="n">
         <v>402</v>
@@ -4172,16 +4172,16 @@
         <v>39679</v>
       </c>
       <c r="B188" t="n">
-        <v>80.65940093994141</v>
+        <v>80.65939331054688</v>
       </c>
       <c r="C188" t="n">
-        <v>80.65940093994141</v>
+        <v>80.65939331054688</v>
       </c>
       <c r="D188" t="n">
-        <v>80.50605707454056</v>
+        <v>80.50604945965048</v>
       </c>
       <c r="E188" t="n">
-        <v>80.50605707454056</v>
+        <v>80.50604945965048</v>
       </c>
       <c r="F188" t="n">
         <v>36</v>
@@ -4212,16 +4212,16 @@
         <v>39681</v>
       </c>
       <c r="B190" t="n">
-        <v>80.65940093994141</v>
+        <v>80.65939331054688</v>
       </c>
       <c r="C190" t="n">
-        <v>80.65940093994141</v>
+        <v>80.65939331054688</v>
       </c>
       <c r="D190" t="n">
-        <v>80.65940093994141</v>
+        <v>80.65939331054688</v>
       </c>
       <c r="E190" t="n">
-        <v>80.65940093994141</v>
+        <v>80.65939331054688</v>
       </c>
       <c r="F190" t="n">
         <v>18</v>
@@ -4232,16 +4232,16 @@
         <v>39682</v>
       </c>
       <c r="B191" t="n">
-        <v>80.65940093994141</v>
+        <v>80.65939331054688</v>
       </c>
       <c r="C191" t="n">
-        <v>80.65940093994141</v>
+        <v>80.65939331054688</v>
       </c>
       <c r="D191" t="n">
-        <v>80.65940093994141</v>
+        <v>80.65939331054688</v>
       </c>
       <c r="E191" t="n">
-        <v>80.65940093994141</v>
+        <v>80.65939331054688</v>
       </c>
       <c r="F191" t="n">
         <v>1865</v>
@@ -4432,16 +4432,16 @@
         <v>39699</v>
       </c>
       <c r="B201" t="n">
-        <v>71.56092834472656</v>
+        <v>71.56093597412109</v>
       </c>
       <c r="C201" t="n">
-        <v>74.11667578560966</v>
+        <v>74.11668368748256</v>
       </c>
       <c r="D201" t="n">
-        <v>71.50981610592017</v>
+        <v>71.50982372986542</v>
       </c>
       <c r="E201" t="n">
-        <v>74.11667578560966</v>
+        <v>74.11668368748256</v>
       </c>
       <c r="F201" t="n">
         <v>950</v>
@@ -4472,16 +4472,16 @@
         <v>39701</v>
       </c>
       <c r="B203" t="n">
-        <v>69.51634216308594</v>
+        <v>69.51633453369141</v>
       </c>
       <c r="C203" t="n">
-        <v>71.04978800316481</v>
+        <v>71.04978020547513</v>
       </c>
       <c r="D203" t="n">
-        <v>69.51634216308594</v>
+        <v>69.51633453369141</v>
       </c>
       <c r="E203" t="n">
-        <v>71.04978800316481</v>
+        <v>71.04978020547513</v>
       </c>
       <c r="F203" t="n">
         <v>13203</v>
@@ -4512,16 +4512,16 @@
         <v>39703</v>
       </c>
       <c r="B205" t="n">
-        <v>69.00518035888672</v>
+        <v>69.00518798828125</v>
       </c>
       <c r="C205" t="n">
-        <v>71.56092777958622</v>
+        <v>71.56093569155092</v>
       </c>
       <c r="D205" t="n">
-        <v>67.47173475911043</v>
+        <v>67.47174221896317</v>
       </c>
       <c r="E205" t="n">
-        <v>69.00518035888672</v>
+        <v>69.00518798828125</v>
       </c>
       <c r="F205" t="n">
         <v>1097</v>
@@ -4532,16 +4532,16 @@
         <v>39706</v>
       </c>
       <c r="B206" t="n">
-        <v>69.00518035888672</v>
+        <v>69.00518798828125</v>
       </c>
       <c r="C206" t="n">
-        <v>69.00518035888672</v>
+        <v>69.00518798828125</v>
       </c>
       <c r="D206" t="n">
-        <v>63.8936855174877</v>
+        <v>63.8936925817419</v>
       </c>
       <c r="E206" t="n">
-        <v>63.8936855174877</v>
+        <v>63.8936925817419</v>
       </c>
       <c r="F206" t="n">
         <v>457</v>
@@ -4552,16 +4552,16 @@
         <v>39707</v>
       </c>
       <c r="B207" t="n">
-        <v>69.00518035888672</v>
+        <v>69.00518798828125</v>
       </c>
       <c r="C207" t="n">
-        <v>71.04977686912461</v>
+        <v>71.04978472457513</v>
       </c>
       <c r="D207" t="n">
-        <v>66.44943293818721</v>
+        <v>66.44944028501158</v>
       </c>
       <c r="E207" t="n">
-        <v>69.00518035888672</v>
+        <v>69.00518798828125</v>
       </c>
       <c r="F207" t="n">
         <v>237</v>
@@ -4592,16 +4592,16 @@
         <v>39709</v>
       </c>
       <c r="B209" t="n">
-        <v>69.00518035888672</v>
+        <v>69.00518798828125</v>
       </c>
       <c r="C209" t="n">
-        <v>70.02748217980994</v>
+        <v>70.02748992223285</v>
       </c>
       <c r="D209" t="n">
-        <v>63.8936855174877</v>
+        <v>63.8936925817419</v>
       </c>
       <c r="E209" t="n">
-        <v>63.8936855174877</v>
+        <v>63.8936925817419</v>
       </c>
       <c r="F209" t="n">
         <v>274</v>
@@ -4632,16 +4632,16 @@
         <v>39713</v>
       </c>
       <c r="B211" t="n">
-        <v>71.56092834472656</v>
+        <v>71.56093597412109</v>
       </c>
       <c r="C211" t="n">
-        <v>71.56092834472656</v>
+        <v>71.56093597412109</v>
       </c>
       <c r="D211" t="n">
-        <v>69.00518090384347</v>
+        <v>69.00518826075962</v>
       </c>
       <c r="E211" t="n">
-        <v>71.50981610592017</v>
+        <v>71.50982372986542</v>
       </c>
       <c r="F211" t="n">
         <v>109</v>
@@ -4732,16 +4732,16 @@
         <v>39720</v>
       </c>
       <c r="B216" t="n">
-        <v>63.8936882019043</v>
+        <v>63.89368057250977</v>
       </c>
       <c r="C216" t="n">
-        <v>67.42061822169548</v>
+        <v>67.42061017115854</v>
       </c>
       <c r="D216" t="n">
-        <v>61.33794067382813</v>
+        <v>61.33793334960937</v>
       </c>
       <c r="E216" t="n">
-        <v>67.42061822169548</v>
+        <v>67.42061017115854</v>
       </c>
       <c r="F216" t="n">
         <v>6254</v>
@@ -4752,16 +4752,16 @@
         <v>39721</v>
       </c>
       <c r="B217" t="n">
-        <v>64.40483093261719</v>
+        <v>64.40483856201172</v>
       </c>
       <c r="C217" t="n">
-        <v>68.49402360418325</v>
+        <v>68.49403171798345</v>
       </c>
       <c r="D217" t="n">
-        <v>61.38904509718027</v>
+        <v>61.38905236932489</v>
       </c>
       <c r="E217" t="n">
-        <v>68.49402360418325</v>
+        <v>68.49403171798345</v>
       </c>
       <c r="F217" t="n">
         <v>987</v>
@@ -4792,16 +4792,16 @@
         <v>39723</v>
       </c>
       <c r="B219" t="n">
-        <v>63.8936882019043</v>
+        <v>63.89368057250977</v>
       </c>
       <c r="C219" t="n">
-        <v>63.8936882019043</v>
+        <v>63.89368057250977</v>
       </c>
       <c r="D219" t="n">
-        <v>55.2041473196062</v>
+        <v>55.20414072780924</v>
       </c>
       <c r="E219" t="n">
-        <v>58.78219314575195</v>
+        <v>58.78218612670899</v>
       </c>
       <c r="F219" t="n">
         <v>621</v>
@@ -4812,16 +4812,16 @@
         <v>39724</v>
       </c>
       <c r="B220" t="n">
-        <v>65.93828582763672</v>
+        <v>65.93827819824219</v>
       </c>
       <c r="C220" t="n">
-        <v>65.93828582763672</v>
+        <v>65.93827819824219</v>
       </c>
       <c r="D220" t="n">
-        <v>59.29334500352479</v>
+        <v>59.29333814298366</v>
       </c>
       <c r="E220" t="n">
-        <v>59.29334500352479</v>
+        <v>59.29333814298366</v>
       </c>
       <c r="F220" t="n">
         <v>182</v>
@@ -4972,16 +4972,16 @@
         <v>39736</v>
       </c>
       <c r="B228" t="n">
-        <v>46.77017974853516</v>
+        <v>46.77017593383789</v>
       </c>
       <c r="C228" t="n">
-        <v>46.77017974853516</v>
+        <v>46.77017593383789</v>
       </c>
       <c r="D228" t="n">
-        <v>41.91425681626334</v>
+        <v>41.91425339762775</v>
       </c>
       <c r="E228" t="n">
-        <v>46.00345338595338</v>
+        <v>46.00344963379231</v>
       </c>
       <c r="F228" t="n">
         <v>237</v>
@@ -4992,16 +4992,16 @@
         <v>39737</v>
       </c>
       <c r="B229" t="n">
-        <v>46.77017974853516</v>
+        <v>46.77017593383789</v>
       </c>
       <c r="C229" t="n">
-        <v>46.77017974853516</v>
+        <v>46.77017593383789</v>
       </c>
       <c r="D229" t="n">
-        <v>46.77017974853516</v>
+        <v>46.77017593383789</v>
       </c>
       <c r="E229" t="n">
-        <v>46.77017974853516</v>
+        <v>46.77017593383789</v>
       </c>
       <c r="F229" t="n">
         <v>3127</v>
@@ -5012,16 +5012,16 @@
         <v>39738</v>
       </c>
       <c r="B230" t="n">
-        <v>46.71906280517578</v>
+        <v>46.71905899047852</v>
       </c>
       <c r="C230" t="n">
-        <v>46.71906280517578</v>
+        <v>46.71905899047852</v>
       </c>
       <c r="D230" t="n">
-        <v>43.44770491604304</v>
+        <v>43.44770136845816</v>
       </c>
       <c r="E230" t="n">
-        <v>43.44770491604304</v>
+        <v>43.44770136845816</v>
       </c>
       <c r="F230" t="n">
         <v>128</v>
@@ -5152,16 +5152,16 @@
         <v>39749</v>
       </c>
       <c r="B237" t="n">
-        <v>35.78046417236328</v>
+        <v>35.78046798706055</v>
       </c>
       <c r="C237" t="n">
-        <v>39.86966079093708</v>
+        <v>39.86966504159983</v>
       </c>
       <c r="D237" t="n">
-        <v>35.78046417236328</v>
+        <v>35.78046798706055</v>
       </c>
       <c r="E237" t="n">
-        <v>39.86966079093708</v>
+        <v>39.86966504159983</v>
       </c>
       <c r="F237" t="n">
         <v>2194</v>
@@ -5172,16 +5172,16 @@
         <v>39750</v>
       </c>
       <c r="B238" t="n">
-        <v>35.78046417236328</v>
+        <v>35.78046798706055</v>
       </c>
       <c r="C238" t="n">
-        <v>35.78046417236328</v>
+        <v>35.78046798706055</v>
       </c>
       <c r="D238" t="n">
-        <v>35.78046417236328</v>
+        <v>35.78046798706055</v>
       </c>
       <c r="E238" t="n">
-        <v>35.78046417236328</v>
+        <v>35.78046798706055</v>
       </c>
       <c r="F238" t="n">
         <v>2194</v>
@@ -5192,16 +5192,16 @@
         <v>39751</v>
       </c>
       <c r="B239" t="n">
-        <v>32.20241546630859</v>
+        <v>32.20241928100586</v>
       </c>
       <c r="C239" t="n">
-        <v>35.78046083683089</v>
+        <v>35.78046507538331</v>
       </c>
       <c r="D239" t="n">
-        <v>32.20241546630859</v>
+        <v>32.20241928100586</v>
       </c>
       <c r="E239" t="n">
-        <v>35.78046083683089</v>
+        <v>35.78046507538331</v>
       </c>
       <c r="F239" t="n">
         <v>43761</v>
@@ -5232,16 +5232,16 @@
         <v>39755</v>
       </c>
       <c r="B241" t="n">
-        <v>38.33621215820312</v>
+        <v>38.33621597290039</v>
       </c>
       <c r="C241" t="n">
-        <v>39.4607420466023</v>
+        <v>39.46074597319745</v>
       </c>
       <c r="D241" t="n">
-        <v>38.33621215820312</v>
+        <v>38.33621597290039</v>
       </c>
       <c r="E241" t="n">
-        <v>38.33621215820312</v>
+        <v>38.33621597290039</v>
       </c>
       <c r="F241" t="n">
         <v>292</v>
@@ -5292,16 +5292,16 @@
         <v>39758</v>
       </c>
       <c r="B244" t="n">
-        <v>39.30739593505859</v>
+        <v>39.30739974975586</v>
       </c>
       <c r="C244" t="n">
-        <v>40.8919609924708</v>
+        <v>40.89196496094666</v>
       </c>
       <c r="D244" t="n">
-        <v>35.78046586841195</v>
+        <v>35.78046934082833</v>
       </c>
       <c r="E244" t="n">
-        <v>36.29161680713963</v>
+        <v>36.29162032916209</v>
       </c>
       <c r="F244" t="n">
         <v>493</v>
@@ -5352,16 +5352,16 @@
         <v>39763</v>
       </c>
       <c r="B247" t="n">
-        <v>35.78046417236328</v>
+        <v>35.78046798706055</v>
       </c>
       <c r="C247" t="n">
-        <v>35.78046417236328</v>
+        <v>35.78046798706055</v>
       </c>
       <c r="D247" t="n">
-        <v>35.78046417236328</v>
+        <v>35.78046798706055</v>
       </c>
       <c r="E247" t="n">
-        <v>35.78046417236328</v>
+        <v>35.78046798706055</v>
       </c>
       <c r="F247" t="n">
         <v>237</v>
@@ -5392,16 +5392,16 @@
         <v>39765</v>
       </c>
       <c r="B249" t="n">
-        <v>35.78046417236328</v>
+        <v>35.78046798706055</v>
       </c>
       <c r="C249" t="n">
-        <v>35.78046417236328</v>
+        <v>35.78046798706055</v>
       </c>
       <c r="D249" t="n">
-        <v>34.55370625653243</v>
+        <v>34.55370994044016</v>
       </c>
       <c r="E249" t="n">
-        <v>35.72934836775259</v>
+        <v>35.72935217700019</v>
       </c>
       <c r="F249" t="n">
         <v>1993</v>
@@ -5412,16 +5412,16 @@
         <v>39766</v>
       </c>
       <c r="B250" t="n">
-        <v>35.72934722900391</v>
+        <v>35.72935104370117</v>
       </c>
       <c r="C250" t="n">
-        <v>38.28509458843144</v>
+        <v>38.2850986759969</v>
       </c>
       <c r="D250" t="n">
-        <v>35.72934722900391</v>
+        <v>35.72935104370117</v>
       </c>
       <c r="E250" t="n">
-        <v>38.28509458843144</v>
+        <v>38.2850986759969</v>
       </c>
       <c r="F250" t="n">
         <v>1316</v>
@@ -5432,16 +5432,16 @@
         <v>39769</v>
       </c>
       <c r="B251" t="n">
-        <v>35.78046417236328</v>
+        <v>35.78046798706055</v>
       </c>
       <c r="C251" t="n">
-        <v>35.93380802039106</v>
+        <v>35.93381185143692</v>
       </c>
       <c r="D251" t="n">
-        <v>34.50259045192173</v>
+        <v>34.50259413037981</v>
       </c>
       <c r="E251" t="n">
-        <v>35.93380802039106</v>
+        <v>35.93381185143692</v>
       </c>
       <c r="F251" t="n">
         <v>292</v>
@@ -5472,16 +5472,16 @@
         <v>39771</v>
       </c>
       <c r="B253" t="n">
-        <v>31.18012046813965</v>
+        <v>31.18011665344238</v>
       </c>
       <c r="C253" t="n">
-        <v>34.24701528358996</v>
+        <v>34.24701109367685</v>
       </c>
       <c r="D253" t="n">
-        <v>31.18012046813965</v>
+        <v>31.18011665344238</v>
       </c>
       <c r="E253" t="n">
-        <v>34.24701528358996</v>
+        <v>34.24701109367685</v>
       </c>
       <c r="F253" t="n">
         <v>1590</v>
@@ -5492,16 +5492,16 @@
         <v>39773</v>
       </c>
       <c r="B254" t="n">
-        <v>33.22471618652344</v>
+        <v>33.2247200012207</v>
       </c>
       <c r="C254" t="n">
-        <v>33.22471618652344</v>
+        <v>33.2247200012207</v>
       </c>
       <c r="D254" t="n">
-        <v>30.6689687875601</v>
+        <v>30.66897230881911</v>
       </c>
       <c r="E254" t="n">
-        <v>31.18011969367446</v>
+        <v>31.18012327362129</v>
       </c>
       <c r="F254" t="n">
         <v>274</v>
@@ -5532,16 +5532,16 @@
         <v>39777</v>
       </c>
       <c r="B256" t="n">
-        <v>33.22471618652344</v>
+        <v>33.2247200012207</v>
       </c>
       <c r="C256" t="n">
-        <v>35.72934778171449</v>
+        <v>35.72935188398115</v>
       </c>
       <c r="D256" t="n">
-        <v>33.22471618652344</v>
+        <v>33.2247200012207</v>
       </c>
       <c r="E256" t="n">
-        <v>35.26931267937242</v>
+        <v>35.26931672882012</v>
       </c>
       <c r="F256" t="n">
         <v>310</v>
@@ -5592,16 +5592,16 @@
         <v>39780</v>
       </c>
       <c r="B259" t="n">
-        <v>29.64667320251465</v>
+        <v>29.64667129516602</v>
       </c>
       <c r="C259" t="n">
-        <v>32.96914567581348</v>
+        <v>32.96914355471023</v>
       </c>
       <c r="D259" t="n">
-        <v>28.87995029420925</v>
+        <v>28.87994843618851</v>
       </c>
       <c r="E259" t="n">
-        <v>29.64667320251465</v>
+        <v>29.64667129516602</v>
       </c>
       <c r="F259" t="n">
         <v>9728</v>
@@ -5612,16 +5612,16 @@
         <v>39783</v>
       </c>
       <c r="B260" t="n">
-        <v>29.64667320251465</v>
+        <v>29.64667129516602</v>
       </c>
       <c r="C260" t="n">
-        <v>30.6689733850925</v>
+        <v>30.66897141197315</v>
       </c>
       <c r="D260" t="n">
-        <v>28.11322560300146</v>
+        <v>28.11322379430872</v>
       </c>
       <c r="E260" t="n">
-        <v>30.6689733850925</v>
+        <v>30.66897141197315</v>
       </c>
       <c r="F260" t="n">
         <v>146</v>
@@ -5632,16 +5632,16 @@
         <v>39784</v>
       </c>
       <c r="B261" t="n">
-        <v>31.53792953491211</v>
+        <v>31.53792572021484</v>
       </c>
       <c r="C261" t="n">
-        <v>32.96914736791319</v>
+        <v>32.96914338010176</v>
       </c>
       <c r="D261" t="n">
-        <v>30.66897495913878</v>
+        <v>30.66897124954666</v>
       </c>
       <c r="E261" t="n">
-        <v>30.66897495913878</v>
+        <v>30.66897124954666</v>
       </c>
       <c r="F261" t="n">
         <v>6272</v>
@@ -5912,16 +5912,16 @@
         <v>39804</v>
       </c>
       <c r="B275" t="n">
-        <v>29.08440780639648</v>
+        <v>29.08440589904785</v>
       </c>
       <c r="C275" t="n">
-        <v>30.66897109924241</v>
+        <v>30.66896908797849</v>
       </c>
       <c r="D275" t="n">
-        <v>29.08440780639648</v>
+        <v>29.08440589904785</v>
       </c>
       <c r="E275" t="n">
-        <v>30.66897109924241</v>
+        <v>30.66896908797849</v>
       </c>
       <c r="F275" t="n">
         <v>3291</v>
@@ -5932,16 +5932,16 @@
         <v>39805</v>
       </c>
       <c r="B276" t="n">
-        <v>28.06210899353027</v>
+        <v>28.06210708618164</v>
       </c>
       <c r="C276" t="n">
-        <v>30.66897056439466</v>
+        <v>30.66896847986071</v>
       </c>
       <c r="D276" t="n">
-        <v>28.06210899353027</v>
+        <v>28.06210708618164</v>
       </c>
       <c r="E276" t="n">
-        <v>30.66897056439466</v>
+        <v>30.66896847986071</v>
       </c>
       <c r="F276" t="n">
         <v>1627</v>
@@ -6052,16 +6052,16 @@
         <v>39819</v>
       </c>
       <c r="B282" t="n">
-        <v>27.8576488494873</v>
+        <v>27.85764694213867</v>
       </c>
       <c r="C282" t="n">
-        <v>28.62437350595717</v>
+        <v>28.62437154611268</v>
       </c>
       <c r="D282" t="n">
-        <v>25.04632748630089</v>
+        <v>25.04632577143691</v>
       </c>
       <c r="E282" t="n">
-        <v>25.04632748630089</v>
+        <v>25.04632577143691</v>
       </c>
       <c r="F282" t="n">
         <v>2541</v>
@@ -6072,16 +6072,16 @@
         <v>39820</v>
       </c>
       <c r="B283" t="n">
-        <v>28.06210899353027</v>
+        <v>28.06210708618164</v>
       </c>
       <c r="C283" t="n">
-        <v>28.11322301736178</v>
+        <v>28.11322110653898</v>
       </c>
       <c r="D283" t="n">
-        <v>26.42642992158443</v>
+        <v>26.42642812541098</v>
       </c>
       <c r="E283" t="n">
-        <v>27.34649839667146</v>
+        <v>27.34649653796205</v>
       </c>
       <c r="F283" t="n">
         <v>1682</v>
@@ -6092,16 +6092,16 @@
         <v>39821</v>
       </c>
       <c r="B284" t="n">
-        <v>28.36879730224609</v>
+        <v>28.36879539489746</v>
       </c>
       <c r="C284" t="n">
-        <v>30.15782026642161</v>
+        <v>30.15781823878974</v>
       </c>
       <c r="D284" t="n">
-        <v>27.70430428097103</v>
+        <v>27.70430241829894</v>
       </c>
       <c r="E284" t="n">
-        <v>30.15782026642161</v>
+        <v>30.15781823878974</v>
       </c>
       <c r="F284" t="n">
         <v>2249</v>
@@ -6152,16 +6152,16 @@
         <v>39826</v>
       </c>
       <c r="B287" t="n">
-        <v>27.09092140197754</v>
+        <v>27.09092330932617</v>
       </c>
       <c r="C287" t="n">
-        <v>27.09092140197754</v>
+        <v>27.09092330932617</v>
       </c>
       <c r="D287" t="n">
-        <v>26.57977052869713</v>
+        <v>26.57977240005795</v>
       </c>
       <c r="E287" t="n">
-        <v>27.09092140197754</v>
+        <v>27.09092330932617</v>
       </c>
       <c r="F287" t="n">
         <v>5248</v>
@@ -6172,16 +6172,16 @@
         <v>39827</v>
       </c>
       <c r="B288" t="n">
-        <v>26.37531280517578</v>
+        <v>26.37531471252441</v>
       </c>
       <c r="C288" t="n">
-        <v>27.09092336650071</v>
+        <v>27.0909253255992</v>
       </c>
       <c r="D288" t="n">
-        <v>26.37531280517578</v>
+        <v>26.37531471252441</v>
       </c>
       <c r="E288" t="n">
-        <v>27.09092336650071</v>
+        <v>27.0909253255992</v>
       </c>
       <c r="F288" t="n">
         <v>1408</v>
@@ -6252,16 +6252,16 @@
         <v>39834</v>
       </c>
       <c r="B292" t="n">
-        <v>28.06210899353027</v>
+        <v>28.06210708618164</v>
       </c>
       <c r="C292" t="n">
-        <v>30.51562670999794</v>
+        <v>30.51562463588658</v>
       </c>
       <c r="D292" t="n">
-        <v>27.60207386453564</v>
+        <v>27.60207198845506</v>
       </c>
       <c r="E292" t="n">
-        <v>30.51562670999794</v>
+        <v>30.51562463588658</v>
       </c>
       <c r="F292" t="n">
         <v>804</v>
@@ -6312,16 +6312,16 @@
         <v>39840</v>
       </c>
       <c r="B295" t="n">
-        <v>28.06210899353027</v>
+        <v>28.06210708618164</v>
       </c>
       <c r="C295" t="n">
-        <v>28.87994763805209</v>
+        <v>28.87994567511592</v>
       </c>
       <c r="D295" t="n">
-        <v>26.83534924384533</v>
+        <v>26.83534741987812</v>
       </c>
       <c r="E295" t="n">
-        <v>27.60207386453564</v>
+        <v>27.60207198845506</v>
       </c>
       <c r="F295" t="n">
         <v>3346</v>
@@ -6332,16 +6332,16 @@
         <v>39841</v>
       </c>
       <c r="B296" t="n">
-        <v>28.11322021484375</v>
+        <v>28.11322212219238</v>
       </c>
       <c r="C296" t="n">
-        <v>28.11322021484375</v>
+        <v>28.11322212219238</v>
       </c>
       <c r="D296" t="n">
-        <v>27.09092201110116</v>
+        <v>27.09092384909171</v>
       </c>
       <c r="E296" t="n">
-        <v>27.09092201110116</v>
+        <v>27.09092384909171</v>
       </c>
       <c r="F296" t="n">
         <v>914</v>
@@ -6392,16 +6392,16 @@
         <v>39846</v>
       </c>
       <c r="B299" t="n">
-        <v>27.8576488494873</v>
+        <v>27.85764694213867</v>
       </c>
       <c r="C299" t="n">
-        <v>29.13552446553861</v>
+        <v>29.1355224706968</v>
       </c>
       <c r="D299" t="n">
-        <v>27.8576488494873</v>
+        <v>27.85764694213867</v>
       </c>
       <c r="E299" t="n">
-        <v>29.13552446553861</v>
+        <v>29.1355224706968</v>
       </c>
       <c r="F299" t="n">
         <v>54</v>
@@ -6512,16 +6512,16 @@
         <v>39855</v>
       </c>
       <c r="B305" t="n">
-        <v>29.64667320251465</v>
+        <v>29.64667129516602</v>
       </c>
       <c r="C305" t="n">
-        <v>30.61785757365753</v>
+        <v>30.61785560382677</v>
       </c>
       <c r="D305" t="n">
-        <v>29.64667320251465</v>
+        <v>29.64667129516602</v>
       </c>
       <c r="E305" t="n">
-        <v>29.69778901394962</v>
+        <v>29.6977871033124</v>
       </c>
       <c r="F305" t="n">
         <v>365</v>
@@ -6532,16 +6532,16 @@
         <v>39856</v>
       </c>
       <c r="B306" t="n">
-        <v>29.64667320251465</v>
+        <v>29.64667129516602</v>
       </c>
       <c r="C306" t="n">
-        <v>30.15782240235238</v>
+        <v>30.15782046211845</v>
       </c>
       <c r="D306" t="n">
-        <v>28.67549061427415</v>
+        <v>28.67548876940753</v>
       </c>
       <c r="E306" t="n">
-        <v>28.67549061427415</v>
+        <v>28.67548876940753</v>
       </c>
       <c r="F306" t="n">
         <v>109</v>
@@ -6592,16 +6592,16 @@
         <v>39861</v>
       </c>
       <c r="B309" t="n">
-        <v>30.41339492797852</v>
+        <v>30.41339874267578</v>
       </c>
       <c r="C309" t="n">
-        <v>30.41339492797852</v>
+        <v>30.41339874267578</v>
       </c>
       <c r="D309" t="n">
-        <v>30.41339492797852</v>
+        <v>30.41339874267578</v>
       </c>
       <c r="E309" t="n">
-        <v>30.41339492797852</v>
+        <v>30.41339874267578</v>
       </c>
       <c r="F309" t="n">
         <v>584754</v>
@@ -6612,16 +6612,16 @@
         <v>39864</v>
       </c>
       <c r="B310" t="n">
-        <v>30.41339492797852</v>
+        <v>30.41339874267578</v>
       </c>
       <c r="C310" t="n">
-        <v>30.41339492797852</v>
+        <v>30.41339874267578</v>
       </c>
       <c r="D310" t="n">
-        <v>28.87994747799853</v>
+        <v>28.87995110035825</v>
       </c>
       <c r="E310" t="n">
-        <v>28.87994747799853</v>
+        <v>28.87995110035825</v>
       </c>
       <c r="F310" t="n">
         <v>1097</v>
@@ -6712,16 +6712,16 @@
         <v>39876</v>
       </c>
       <c r="B315" t="n">
-        <v>29.80001258850098</v>
+        <v>29.80001068115234</v>
       </c>
       <c r="C315" t="n">
-        <v>29.90224240697483</v>
+        <v>29.90224049308298</v>
       </c>
       <c r="D315" t="n">
-        <v>29.39109331460557</v>
+        <v>29.3910914334298</v>
       </c>
       <c r="E315" t="n">
-        <v>29.90224240697483</v>
+        <v>29.90224049308298</v>
       </c>
       <c r="F315" t="n">
         <v>585</v>
@@ -6832,16 +6832,16 @@
         <v>39890</v>
       </c>
       <c r="B321" t="n">
-        <v>29.59555435180664</v>
+        <v>29.59555625915527</v>
       </c>
       <c r="C321" t="n">
-        <v>30.15781748856415</v>
+        <v>30.15781943214903</v>
       </c>
       <c r="D321" t="n">
-        <v>28.1132210223512</v>
+        <v>28.1132228341677</v>
       </c>
       <c r="E321" t="n">
-        <v>28.1132210223512</v>
+        <v>28.1132228341677</v>
       </c>
       <c r="F321" t="n">
         <v>128</v>
@@ -6872,16 +6872,16 @@
         <v>39892</v>
       </c>
       <c r="B323" t="n">
-        <v>29.59555435180664</v>
+        <v>29.59555625915527</v>
       </c>
       <c r="C323" t="n">
-        <v>30.66896838801949</v>
+        <v>30.66897036454658</v>
       </c>
       <c r="D323" t="n">
-        <v>29.59555435180664</v>
+        <v>29.59555625915527</v>
       </c>
       <c r="E323" t="n">
-        <v>29.64666837201091</v>
+        <v>29.6466702826537</v>
       </c>
       <c r="F323" t="n">
         <v>402</v>
@@ -6892,16 +6892,16 @@
         <v>39895</v>
       </c>
       <c r="B324" t="n">
-        <v>29.64667320251465</v>
+        <v>29.64667129516602</v>
       </c>
       <c r="C324" t="n">
-        <v>30.6689733850925</v>
+        <v>30.66897141197315</v>
       </c>
       <c r="D324" t="n">
-        <v>29.64667320251465</v>
+        <v>29.64667129516602</v>
       </c>
       <c r="E324" t="n">
-        <v>30.41339789372244</v>
+        <v>30.4133959370458</v>
       </c>
       <c r="F324" t="n">
         <v>585</v>
@@ -6912,16 +6912,16 @@
         <v>39896</v>
       </c>
       <c r="B325" t="n">
-        <v>29.59555435180664</v>
+        <v>29.59555625915527</v>
       </c>
       <c r="C325" t="n">
-        <v>29.64666837201091</v>
+        <v>29.6466702826537</v>
       </c>
       <c r="D325" t="n">
-        <v>29.59555435180664</v>
+        <v>29.59555625915527</v>
       </c>
       <c r="E325" t="n">
-        <v>29.64666837201091</v>
+        <v>29.6466702826537</v>
       </c>
       <c r="F325" t="n">
         <v>9363</v>
@@ -6992,16 +6992,16 @@
         <v>39902</v>
       </c>
       <c r="B329" t="n">
-        <v>32.81579208374023</v>
+        <v>32.8157958984375</v>
       </c>
       <c r="C329" t="n">
-        <v>35.7804583472479</v>
+        <v>35.78046250657511</v>
       </c>
       <c r="D329" t="n">
-        <v>32.71356049116231</v>
+        <v>32.71356429397559</v>
       </c>
       <c r="E329" t="n">
-        <v>32.96913590680339</v>
+        <v>32.96913973932624</v>
       </c>
       <c r="F329" t="n">
         <v>34032</v>
@@ -7012,16 +7012,16 @@
         <v>39903</v>
       </c>
       <c r="B330" t="n">
-        <v>32.96914291381836</v>
+        <v>32.96913909912109</v>
       </c>
       <c r="C330" t="n">
-        <v>35.78046595176043</v>
+        <v>35.78046181177881</v>
       </c>
       <c r="D330" t="n">
-        <v>32.30464811824627</v>
+        <v>32.30464438043442</v>
       </c>
       <c r="E330" t="n">
-        <v>33.17360257662482</v>
+        <v>33.17359873827053</v>
       </c>
       <c r="F330" t="n">
         <v>12673</v>
@@ -7072,16 +7072,16 @@
         <v>39906</v>
       </c>
       <c r="B333" t="n">
-        <v>35.52489471435547</v>
+        <v>35.5248908996582</v>
       </c>
       <c r="C333" t="n">
-        <v>36.29162121558337</v>
+        <v>36.29161731855428</v>
       </c>
       <c r="D333" t="n">
-        <v>34.55371209176601</v>
+        <v>34.55370838135526</v>
       </c>
       <c r="E333" t="n">
-        <v>36.03604571517407</v>
+        <v>36.03604184558892</v>
       </c>
       <c r="F333" t="n">
         <v>30100</v>
@@ -7232,16 +7232,16 @@
         <v>39919</v>
       </c>
       <c r="B341" t="n">
-        <v>42.11871337890625</v>
+        <v>42.11871719360352</v>
       </c>
       <c r="C341" t="n">
-        <v>45.90121841312269</v>
+        <v>45.90122257040191</v>
       </c>
       <c r="D341" t="n">
-        <v>41.45421867303515</v>
+        <v>41.45422242754904</v>
       </c>
       <c r="E341" t="n">
-        <v>45.90121841312269</v>
+        <v>45.90122257040191</v>
       </c>
       <c r="F341" t="n">
         <v>21725</v>
@@ -7352,16 +7352,16 @@
         <v>39930</v>
       </c>
       <c r="B347" t="n">
-        <v>39.97189331054688</v>
+        <v>39.97188949584961</v>
       </c>
       <c r="C347" t="n">
-        <v>42.42541298276661</v>
+        <v>42.42540893391894</v>
       </c>
       <c r="D347" t="n">
-        <v>39.97189331054688</v>
+        <v>39.97188949584961</v>
       </c>
       <c r="E347" t="n">
-        <v>40.38081266161605</v>
+        <v>40.38080880789377</v>
       </c>
       <c r="F347" t="n">
         <v>37726</v>
@@ -7612,16 +7612,16 @@
         <v>39948</v>
       </c>
       <c r="B360" t="n">
-        <v>42.68098831176758</v>
+        <v>42.68098449707031</v>
       </c>
       <c r="C360" t="n">
-        <v>43.44771120075311</v>
+        <v>43.44770731752848</v>
       </c>
       <c r="D360" t="n">
-        <v>41.91426185697736</v>
+        <v>41.91425811080778</v>
       </c>
       <c r="E360" t="n">
-        <v>43.44771120075311</v>
+        <v>43.44770731752848</v>
       </c>
       <c r="F360" t="n">
         <v>2066</v>
@@ -7712,16 +7712,16 @@
         <v>39955</v>
       </c>
       <c r="B365" t="n">
-        <v>42.47652053833008</v>
+        <v>42.47652435302734</v>
       </c>
       <c r="C365" t="n">
-        <v>42.47652053833008</v>
+        <v>42.47652435302734</v>
       </c>
       <c r="D365" t="n">
-        <v>41.24975915772333</v>
+        <v>41.24976286224859</v>
       </c>
       <c r="E365" t="n">
-        <v>41.40310655892667</v>
+        <v>41.40311027722364</v>
       </c>
       <c r="F365" t="n">
         <v>14501</v>
@@ -7752,16 +7752,16 @@
         <v>39959</v>
       </c>
       <c r="B367" t="n">
-        <v>43.29435729980469</v>
+        <v>43.29436111450195</v>
       </c>
       <c r="C367" t="n">
-        <v>43.70327655457702</v>
+        <v>43.70328040530446</v>
       </c>
       <c r="D367" t="n">
-        <v>43.19212570320968</v>
+        <v>43.19212950889924</v>
       </c>
       <c r="E367" t="n">
-        <v>43.19212570320968</v>
+        <v>43.19212950889924</v>
       </c>
       <c r="F367" t="n">
         <v>4882</v>
@@ -7832,16 +7832,16 @@
         <v>39965</v>
       </c>
       <c r="B371" t="n">
-        <v>46.77017974853516</v>
+        <v>46.77017593383789</v>
       </c>
       <c r="C371" t="n">
-        <v>47.48578674131304</v>
+        <v>47.48578286824901</v>
       </c>
       <c r="D371" t="n">
-        <v>46.51460429434123</v>
+        <v>46.51460050048936</v>
       </c>
       <c r="E371" t="n">
-        <v>47.28132709111875</v>
+        <v>47.28132323473098</v>
       </c>
       <c r="F371" t="n">
         <v>10076</v>
@@ -7932,16 +7932,16 @@
         <v>39972</v>
       </c>
       <c r="B376" t="n">
-        <v>39.46074295043945</v>
+        <v>39.46073913574219</v>
       </c>
       <c r="C376" t="n">
-        <v>42.42540980664766</v>
+        <v>42.42540570535401</v>
       </c>
       <c r="D376" t="n">
-        <v>38.84736396975545</v>
+        <v>38.84736021435396</v>
       </c>
       <c r="E376" t="n">
-        <v>39.76743065787924</v>
+        <v>39.76742681353426</v>
       </c>
       <c r="F376" t="n">
         <v>138727</v>
@@ -8132,16 +8132,16 @@
         <v>39987</v>
       </c>
       <c r="B386" t="n">
-        <v>39.10293579101562</v>
+        <v>39.10293197631836</v>
       </c>
       <c r="C386" t="n">
-        <v>39.35851125723101</v>
+        <v>39.358507417601</v>
       </c>
       <c r="D386" t="n">
-        <v>38.89847613120421</v>
+        <v>38.89847233645306</v>
       </c>
       <c r="E386" t="n">
-        <v>38.89847613120421</v>
+        <v>38.89847233645306</v>
       </c>
       <c r="F386" t="n">
         <v>134978</v>
@@ -8332,16 +8332,16 @@
         <v>40001</v>
       </c>
       <c r="B396" t="n">
-        <v>40.1252326965332</v>
+        <v>40.12523651123047</v>
       </c>
       <c r="C396" t="n">
-        <v>40.1252326965332</v>
+        <v>40.12523651123047</v>
       </c>
       <c r="D396" t="n">
-        <v>39.61408182727898</v>
+        <v>39.61408559338124</v>
       </c>
       <c r="E396" t="n">
-        <v>39.61408182727898</v>
+        <v>39.61408559338124</v>
       </c>
       <c r="F396" t="n">
         <v>5559</v>
@@ -8572,16 +8572,16 @@
         <v>40018</v>
       </c>
       <c r="B408" t="n">
-        <v>42.16983032226562</v>
+        <v>42.16983413696289</v>
       </c>
       <c r="C408" t="n">
-        <v>42.27206192554193</v>
+        <v>42.2720657494871</v>
       </c>
       <c r="D408" t="n">
-        <v>41.55645140002007</v>
+        <v>41.55645515923087</v>
       </c>
       <c r="E408" t="n">
-        <v>42.27206192554193</v>
+        <v>42.2720657494871</v>
       </c>
       <c r="F408" t="n">
         <v>3181</v>
@@ -8632,16 +8632,16 @@
         <v>40023</v>
       </c>
       <c r="B411" t="n">
-        <v>41.8631477355957</v>
+        <v>41.86315155029297</v>
       </c>
       <c r="C411" t="n">
-        <v>41.8631477355957</v>
+        <v>41.86315155029297</v>
       </c>
       <c r="D411" t="n">
-        <v>41.8631477355957</v>
+        <v>41.86315155029297</v>
       </c>
       <c r="E411" t="n">
-        <v>41.8631477355957</v>
+        <v>41.86315155029297</v>
       </c>
       <c r="F411" t="n">
         <v>6473</v>
@@ -8672,16 +8672,16 @@
         <v>40025</v>
       </c>
       <c r="B413" t="n">
-        <v>42.16983032226562</v>
+        <v>42.16983413696289</v>
       </c>
       <c r="C413" t="n">
-        <v>42.78320924451118</v>
+        <v>42.78321311469491</v>
       </c>
       <c r="D413" t="n">
-        <v>41.45421979674376</v>
+        <v>41.45422354670666</v>
       </c>
       <c r="E413" t="n">
-        <v>41.91425487987895</v>
+        <v>41.91425867145678</v>
       </c>
       <c r="F413" t="n">
         <v>3511</v>
@@ -8732,16 +8732,16 @@
         <v>40030</v>
       </c>
       <c r="B416" t="n">
-        <v>42.0164909362793</v>
+        <v>42.01648712158203</v>
       </c>
       <c r="C416" t="n">
-        <v>43.2943647178442</v>
+        <v>43.29436078712816</v>
       </c>
       <c r="D416" t="n">
-        <v>42.0164909362793</v>
+        <v>42.01648712158203</v>
       </c>
       <c r="E416" t="n">
-        <v>42.73209797184079</v>
+        <v>42.73209409217321</v>
       </c>
       <c r="F416" t="n">
         <v>1280</v>
@@ -8812,16 +8812,16 @@
         <v>40036</v>
       </c>
       <c r="B420" t="n">
-        <v>43.70328140258789</v>
+        <v>43.70328521728516</v>
       </c>
       <c r="C420" t="n">
-        <v>44.41888839491993</v>
+        <v>44.41889227207987</v>
       </c>
       <c r="D420" t="n">
-        <v>42.73209539041691</v>
+        <v>42.73209912034295</v>
       </c>
       <c r="E420" t="n">
-        <v>44.41888839491993</v>
+        <v>44.41889227207987</v>
       </c>
       <c r="F420" t="n">
         <v>256</v>
@@ -8832,16 +8832,16 @@
         <v>40037</v>
       </c>
       <c r="B421" t="n">
-        <v>42.68098831176758</v>
+        <v>42.68098449707031</v>
       </c>
       <c r="C421" t="n">
-        <v>42.93656379669765</v>
+        <v>42.93655995915783</v>
       </c>
       <c r="D421" t="n">
-        <v>42.68098831176758</v>
+        <v>42.68098449707031</v>
       </c>
       <c r="E421" t="n">
-        <v>42.93656379669765</v>
+        <v>42.93655995915783</v>
       </c>
       <c r="F421" t="n">
         <v>146</v>
@@ -8852,16 +8852,16 @@
         <v>40038</v>
       </c>
       <c r="B422" t="n">
-        <v>42.16983032226562</v>
+        <v>42.16983413696289</v>
       </c>
       <c r="C422" t="n">
-        <v>42.68098120703897</v>
+        <v>42.68098506797512</v>
       </c>
       <c r="D422" t="n">
-        <v>42.16983032226562</v>
+        <v>42.16983413696289</v>
       </c>
       <c r="E422" t="n">
-        <v>42.22094612390378</v>
+        <v>42.22094994322499</v>
       </c>
       <c r="F422" t="n">
         <v>1462</v>
@@ -9032,16 +9032,16 @@
         <v>40053</v>
       </c>
       <c r="B431" t="n">
-        <v>40.1252326965332</v>
+        <v>40.12523651123047</v>
       </c>
       <c r="C431" t="n">
-        <v>40.1252326965332</v>
+        <v>40.12523651123047</v>
       </c>
       <c r="D431" t="n">
-        <v>39.61408182727898</v>
+        <v>39.61408559338124</v>
       </c>
       <c r="E431" t="n">
-        <v>39.61408182727898</v>
+        <v>39.61408559338124</v>
       </c>
       <c r="F431" t="n">
         <v>1792</v>
@@ -9052,16 +9052,16 @@
         <v>40056</v>
       </c>
       <c r="B432" t="n">
-        <v>40.1252326965332</v>
+        <v>40.12523651123047</v>
       </c>
       <c r="C432" t="n">
-        <v>40.1252326965332</v>
+        <v>40.12523651123047</v>
       </c>
       <c r="D432" t="n">
-        <v>40.1252326965332</v>
+        <v>40.12523651123047</v>
       </c>
       <c r="E432" t="n">
-        <v>40.1252326965332</v>
+        <v>40.12523651123047</v>
       </c>
       <c r="F432" t="n">
         <v>310</v>
@@ -9112,16 +9112,16 @@
         <v>40060</v>
       </c>
       <c r="B435" t="n">
-        <v>38.3873291015625</v>
+        <v>38.38732528686523</v>
       </c>
       <c r="C435" t="n">
-        <v>38.48955714946341</v>
+        <v>38.48955332460735</v>
       </c>
       <c r="D435" t="n">
-        <v>38.3873291015625</v>
+        <v>38.38732528686523</v>
       </c>
       <c r="E435" t="n">
-        <v>38.48955714946341</v>
+        <v>38.48955332460735</v>
       </c>
       <c r="F435" t="n">
         <v>182</v>
@@ -9232,16 +9232,16 @@
         <v>40071</v>
       </c>
       <c r="B441" t="n">
-        <v>42.32317352294922</v>
+        <v>42.32316970825195</v>
       </c>
       <c r="C441" t="n">
-        <v>42.32317352294922</v>
+        <v>42.32316970825195</v>
       </c>
       <c r="D441" t="n">
-        <v>39.0007035194528</v>
+        <v>39.00070000421836</v>
       </c>
       <c r="E441" t="n">
-        <v>40.58526481990037</v>
+        <v>40.58526116184532</v>
       </c>
       <c r="F441" t="n">
         <v>1810</v>
@@ -9312,16 +9312,16 @@
         <v>40078</v>
       </c>
       <c r="B445" t="n">
-        <v>42.37429428100586</v>
+        <v>42.37429046630859</v>
       </c>
       <c r="C445" t="n">
-        <v>42.37429428100586</v>
+        <v>42.37429046630859</v>
       </c>
       <c r="D445" t="n">
-        <v>41.60757144151995</v>
+        <v>41.60756769584604</v>
       </c>
       <c r="E445" t="n">
-        <v>41.60757144151995</v>
+        <v>41.60756769584604</v>
       </c>
       <c r="F445" t="n">
         <v>1334</v>
@@ -9332,16 +9332,16 @@
         <v>40079</v>
       </c>
       <c r="B446" t="n">
-        <v>42.32317352294922</v>
+        <v>42.32316970825195</v>
       </c>
       <c r="C446" t="n">
-        <v>42.68098056321483</v>
+        <v>42.68097671626749</v>
       </c>
       <c r="D446" t="n">
-        <v>42.32317352294922</v>
+        <v>42.32316970825195</v>
       </c>
       <c r="E446" t="n">
-        <v>42.37428932381631</v>
+        <v>42.37428550451185</v>
       </c>
       <c r="F446" t="n">
         <v>1280</v>
@@ -9392,16 +9392,16 @@
         <v>40085</v>
       </c>
       <c r="B449" t="n">
-        <v>42.16983032226562</v>
+        <v>42.16983413696289</v>
       </c>
       <c r="C449" t="n">
-        <v>42.16983032226562</v>
+        <v>42.16983413696289</v>
       </c>
       <c r="D449" t="n">
-        <v>41.65868300329637</v>
+        <v>41.65868677175508</v>
       </c>
       <c r="E449" t="n">
-        <v>41.65868300329637</v>
+        <v>41.65868677175508</v>
       </c>
       <c r="F449" t="n">
         <v>621</v>
@@ -9672,16 +9672,16 @@
         <v>40106</v>
       </c>
       <c r="B463" t="n">
-        <v>42.16983032226562</v>
+        <v>42.16983413696289</v>
       </c>
       <c r="C463" t="n">
-        <v>42.16983032226562</v>
+        <v>42.16983413696289</v>
       </c>
       <c r="D463" t="n">
-        <v>40.94307247777451</v>
+        <v>40.94307618149885</v>
       </c>
       <c r="E463" t="n">
-        <v>40.99418471360858</v>
+        <v>40.99418842195654</v>
       </c>
       <c r="F463" t="n">
         <v>9125</v>
@@ -9692,16 +9692,16 @@
         <v>40107</v>
       </c>
       <c r="B464" t="n">
-        <v>41.96537780761719</v>
+        <v>41.96537399291992</v>
       </c>
       <c r="C464" t="n">
-        <v>42.4254129688705</v>
+        <v>42.42540911235555</v>
       </c>
       <c r="D464" t="n">
-        <v>41.35199878121433</v>
+        <v>41.35199502227388</v>
       </c>
       <c r="E464" t="n">
-        <v>42.32318134823434</v>
+        <v>42.32317750101236</v>
       </c>
       <c r="F464" t="n">
         <v>8174</v>
@@ -9952,16 +9952,16 @@
         <v>40128</v>
       </c>
       <c r="B477" t="n">
-        <v>42.16983032226562</v>
+        <v>42.16983413696289</v>
       </c>
       <c r="C477" t="n">
-        <v>42.16983032226562</v>
+        <v>42.16983413696289</v>
       </c>
       <c r="D477" t="n">
-        <v>41.14753211852303</v>
+        <v>41.14753584074285</v>
       </c>
       <c r="E477" t="n">
-        <v>41.14753211852303</v>
+        <v>41.14753584074285</v>
       </c>
       <c r="F477" t="n">
         <v>4571</v>
@@ -9992,16 +9992,16 @@
         <v>40133</v>
       </c>
       <c r="B479" t="n">
-        <v>42.16983032226562</v>
+        <v>42.16983413696289</v>
       </c>
       <c r="C479" t="n">
-        <v>42.16983032226562</v>
+        <v>42.16983413696289</v>
       </c>
       <c r="D479" t="n">
-        <v>41.60756720165822</v>
+        <v>41.60757096549298</v>
       </c>
       <c r="E479" t="n">
-        <v>41.60756720165822</v>
+        <v>41.60757096549298</v>
       </c>
       <c r="F479" t="n">
         <v>1280</v>
@@ -10012,16 +10012,16 @@
         <v>40134</v>
       </c>
       <c r="B480" t="n">
-        <v>42.16983032226562</v>
+        <v>42.16983413696289</v>
       </c>
       <c r="C480" t="n">
-        <v>42.16983032226562</v>
+        <v>42.16983413696289</v>
       </c>
       <c r="D480" t="n">
-        <v>41.91425487987895</v>
+        <v>41.91425867145678</v>
       </c>
       <c r="E480" t="n">
-        <v>42.11871452062747</v>
+        <v>42.11871833070079</v>
       </c>
       <c r="F480" t="n">
         <v>182</v>
@@ -10032,16 +10032,16 @@
         <v>40135</v>
       </c>
       <c r="B481" t="n">
-        <v>42.06760787963867</v>
+        <v>42.06760406494141</v>
       </c>
       <c r="C481" t="n">
-        <v>42.11872012227048</v>
+        <v>42.11871630293835</v>
       </c>
       <c r="D481" t="n">
-        <v>41.65868854375679</v>
+        <v>41.65868476614039</v>
       </c>
       <c r="E481" t="n">
-        <v>42.11872012227048</v>
+        <v>42.11871630293835</v>
       </c>
       <c r="F481" t="n">
         <v>585</v>
@@ -10132,16 +10132,16 @@
         <v>40143</v>
       </c>
       <c r="B486" t="n">
-        <v>47.38356018066406</v>
+        <v>47.3835563659668</v>
       </c>
       <c r="C486" t="n">
-        <v>47.38356018066406</v>
+        <v>47.3835563659668</v>
       </c>
       <c r="D486" t="n">
-        <v>46.00345482434754</v>
+        <v>46.00345112075809</v>
       </c>
       <c r="E486" t="n">
-        <v>47.38356018066406</v>
+        <v>47.3835563659668</v>
       </c>
       <c r="F486" t="n">
         <v>310</v>
@@ -10292,16 +10292,16 @@
         <v>40155</v>
       </c>
       <c r="B494" t="n">
-        <v>84.33966064453125</v>
+        <v>84.33966827392578</v>
       </c>
       <c r="C494" t="n">
-        <v>88.32662898783349</v>
+        <v>88.32663697789054</v>
       </c>
       <c r="D494" t="n">
-        <v>84.33966064453125</v>
+        <v>84.33966827392578</v>
       </c>
       <c r="E494" t="n">
-        <v>88.32662898783349</v>
+        <v>88.32663697789054</v>
       </c>
       <c r="F494" t="n">
         <v>15306</v>
@@ -10352,16 +10352,16 @@
         <v>40158</v>
       </c>
       <c r="B497" t="n">
-        <v>78.20587158203125</v>
+        <v>78.20586395263672</v>
       </c>
       <c r="C497" t="n">
-        <v>78.97259798067739</v>
+        <v>78.97259027648465</v>
       </c>
       <c r="D497" t="n">
-        <v>74.62782931823367</v>
+        <v>74.627822037896</v>
       </c>
       <c r="E497" t="n">
-        <v>74.98563639725695</v>
+        <v>74.98562908201332</v>
       </c>
       <c r="F497" t="n">
         <v>4718</v>
@@ -10372,16 +10372,16 @@
         <v>40161</v>
       </c>
       <c r="B498" t="n">
-        <v>77.49025726318359</v>
+        <v>77.49024963378906</v>
       </c>
       <c r="C498" t="n">
-        <v>80.81273087970516</v>
+        <v>80.81272292319258</v>
       </c>
       <c r="D498" t="n">
-        <v>77.03022574625362</v>
+        <v>77.03021816215202</v>
       </c>
       <c r="E498" t="n">
-        <v>80.81273087970516</v>
+        <v>80.81272292319258</v>
       </c>
       <c r="F498" t="n">
         <v>3053</v>
@@ -10512,16 +10512,16 @@
         <v>40170</v>
       </c>
       <c r="B505" t="n">
-        <v>79.38150787353516</v>
+        <v>79.38151550292969</v>
       </c>
       <c r="C505" t="n">
-        <v>79.48373947420281</v>
+        <v>79.48374711342287</v>
       </c>
       <c r="D505" t="n">
-        <v>77.23467991755459</v>
+        <v>77.23468734061646</v>
       </c>
       <c r="E505" t="n">
-        <v>79.43262723967298</v>
+        <v>79.43263487398062</v>
       </c>
       <c r="F505" t="n">
         <v>1005</v>
@@ -10532,16 +10532,16 @@
         <v>40175</v>
       </c>
       <c r="B506" t="n">
-        <v>78.66590881347656</v>
+        <v>78.66591644287109</v>
       </c>
       <c r="C506" t="n">
-        <v>79.3815158266295</v>
+        <v>79.381523525427</v>
       </c>
       <c r="D506" t="n">
-        <v>76.67242449296978</v>
+        <v>76.6724319290267</v>
       </c>
       <c r="E506" t="n">
-        <v>79.3815158266295</v>
+        <v>79.381523525427</v>
       </c>
       <c r="F506" t="n">
         <v>1737</v>
@@ -10552,16 +10552,16 @@
         <v>40176</v>
       </c>
       <c r="B507" t="n">
-        <v>78.46144866943359</v>
+        <v>78.46144104003906</v>
       </c>
       <c r="C507" t="n">
-        <v>78.66591189927409</v>
+        <v>78.66590424999806</v>
       </c>
       <c r="D507" t="n">
-        <v>76.67242750056967</v>
+        <v>76.67242004513507</v>
       </c>
       <c r="E507" t="n">
-        <v>78.66591189927409</v>
+        <v>78.66590424999806</v>
       </c>
       <c r="F507" t="n">
         <v>548</v>
@@ -10572,16 +10572,16 @@
         <v>40182</v>
       </c>
       <c r="B508" t="n">
-        <v>79.48374176025391</v>
+        <v>79.48374938964844</v>
       </c>
       <c r="C508" t="n">
-        <v>79.48374176025391</v>
+        <v>79.48374938964844</v>
       </c>
       <c r="D508" t="n">
-        <v>76.77465062009647</v>
+        <v>76.77465798945384</v>
       </c>
       <c r="E508" t="n">
-        <v>76.77465062009647</v>
+        <v>76.77465798945384</v>
       </c>
       <c r="F508" t="n">
         <v>969</v>
@@ -10592,16 +10592,16 @@
         <v>40183</v>
       </c>
       <c r="B509" t="n">
-        <v>77.49025726318359</v>
+        <v>77.49024963378906</v>
       </c>
       <c r="C509" t="n">
-        <v>79.48374143309654</v>
+        <v>79.48373360743116</v>
       </c>
       <c r="D509" t="n">
-        <v>77.49025726318359</v>
+        <v>77.49024963378906</v>
       </c>
       <c r="E509" t="n">
-        <v>79.48374143309654</v>
+        <v>79.48373360743116</v>
       </c>
       <c r="F509" t="n">
         <v>658</v>
@@ -10612,16 +10612,16 @@
         <v>40184</v>
       </c>
       <c r="B510" t="n">
-        <v>76.72354125976562</v>
+        <v>76.72353363037109</v>
       </c>
       <c r="C510" t="n">
-        <v>78.41033797868201</v>
+        <v>78.41033018155228</v>
       </c>
       <c r="D510" t="n">
-        <v>76.72354125976562</v>
+        <v>76.72353363037109</v>
       </c>
       <c r="E510" t="n">
-        <v>76.72354125976562</v>
+        <v>76.72353363037109</v>
       </c>
       <c r="F510" t="n">
         <v>1901</v>
@@ -10632,16 +10632,16 @@
         <v>40185</v>
       </c>
       <c r="B511" t="n">
-        <v>76.92800140380859</v>
+        <v>76.92800903320312</v>
       </c>
       <c r="C511" t="n">
-        <v>77.03023301664474</v>
+        <v>77.03024065617818</v>
       </c>
       <c r="D511" t="n">
-        <v>76.67242593752263</v>
+        <v>76.67243354157027</v>
       </c>
       <c r="E511" t="n">
-        <v>76.67242593752263</v>
+        <v>76.67243354157027</v>
       </c>
       <c r="F511" t="n">
         <v>1280</v>
@@ -10652,16 +10652,16 @@
         <v>40186</v>
       </c>
       <c r="B512" t="n">
-        <v>76.87688446044922</v>
+        <v>76.87687683105469</v>
       </c>
       <c r="C512" t="n">
-        <v>76.87688446044922</v>
+        <v>76.87687683105469</v>
       </c>
       <c r="D512" t="n">
-        <v>76.41684579663263</v>
+        <v>76.41683821289313</v>
       </c>
       <c r="E512" t="n">
-        <v>76.77465285386683</v>
+        <v>76.77464523461792</v>
       </c>
       <c r="F512" t="n">
         <v>566</v>
@@ -10772,16 +10772,16 @@
         <v>40196</v>
       </c>
       <c r="B518" t="n">
-        <v>76.92800140380859</v>
+        <v>76.92800903320312</v>
       </c>
       <c r="C518" t="n">
-        <v>76.92800140380859</v>
+        <v>76.92800903320312</v>
       </c>
       <c r="D518" t="n">
-        <v>76.92800140380859</v>
+        <v>76.92800903320312</v>
       </c>
       <c r="E518" t="n">
-        <v>76.92800140380859</v>
+        <v>76.92800903320312</v>
       </c>
       <c r="F518" t="n">
         <v>18</v>
@@ -10892,16 +10892,16 @@
         <v>40205</v>
       </c>
       <c r="B524" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="C524" t="n">
-        <v>69.00517977201022</v>
+        <v>69.005187694843</v>
       </c>
       <c r="D524" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="E524" t="n">
-        <v>67.47173418527561</v>
+        <v>67.47174193204576</v>
       </c>
       <c r="F524" t="n">
         <v>201</v>
@@ -10912,16 +10912,16 @@
         <v>40206</v>
       </c>
       <c r="B525" t="n">
-        <v>65.42713165283203</v>
+        <v>65.4271240234375</v>
       </c>
       <c r="C525" t="n">
-        <v>65.42713165283203</v>
+        <v>65.4271240234375</v>
       </c>
       <c r="D525" t="n">
-        <v>65.42713165283203</v>
+        <v>65.4271240234375</v>
       </c>
       <c r="E525" t="n">
-        <v>65.42713165283203</v>
+        <v>65.4271240234375</v>
       </c>
       <c r="F525" t="n">
         <v>201</v>
@@ -10952,16 +10952,16 @@
         <v>40210</v>
       </c>
       <c r="B527" t="n">
-        <v>63.8936882019043</v>
+        <v>63.89368057250977</v>
       </c>
       <c r="C527" t="n">
-        <v>64.45595137439146</v>
+        <v>64.45594367785841</v>
       </c>
       <c r="D527" t="n">
-        <v>61.33794067382813</v>
+        <v>61.33793334960937</v>
       </c>
       <c r="E527" t="n">
-        <v>64.45595137439146</v>
+        <v>64.45594367785841</v>
       </c>
       <c r="F527" t="n">
         <v>713</v>
@@ -11252,16 +11252,16 @@
         <v>40233</v>
       </c>
       <c r="B542" t="n">
-        <v>55.61306381225586</v>
+        <v>55.61306762695312</v>
       </c>
       <c r="C542" t="n">
-        <v>58.2710428179473</v>
+        <v>58.27104681496478</v>
       </c>
       <c r="D542" t="n">
-        <v>55.45971996679035</v>
+        <v>55.45972377096922</v>
       </c>
       <c r="E542" t="n">
-        <v>58.2710428179473</v>
+        <v>58.27104681496478</v>
       </c>
       <c r="F542" t="n">
         <v>109</v>
@@ -11292,16 +11292,16 @@
         <v>40235</v>
       </c>
       <c r="B544" t="n">
-        <v>56.2264404296875</v>
+        <v>56.22644424438477</v>
       </c>
       <c r="C544" t="n">
-        <v>56.2264404296875</v>
+        <v>56.22644424438477</v>
       </c>
       <c r="D544" t="n">
-        <v>55.45971766833158</v>
+        <v>55.45972143101034</v>
       </c>
       <c r="E544" t="n">
-        <v>55.45971766833158</v>
+        <v>55.45972143101034</v>
       </c>
       <c r="F544" t="n">
         <v>91</v>
@@ -11332,16 +11332,16 @@
         <v>40239</v>
       </c>
       <c r="B546" t="n">
-        <v>56.48202133178711</v>
+        <v>56.48201751708984</v>
       </c>
       <c r="C546" t="n">
-        <v>58.11769861588448</v>
+        <v>58.11769469071642</v>
       </c>
       <c r="D546" t="n">
-        <v>55.25526336871409</v>
+        <v>55.25525963686991</v>
       </c>
       <c r="E546" t="n">
-        <v>55.25526336871409</v>
+        <v>55.25525963686991</v>
       </c>
       <c r="F546" t="n">
         <v>384</v>
@@ -11352,16 +11352,16 @@
         <v>40240</v>
       </c>
       <c r="B547" t="n">
-        <v>56.2264404296875</v>
+        <v>56.22644424438477</v>
       </c>
       <c r="C547" t="n">
-        <v>56.48201587207417</v>
+        <v>56.48201970411102</v>
       </c>
       <c r="D547" t="n">
-        <v>56.2264404296875</v>
+        <v>56.22644424438477</v>
       </c>
       <c r="E547" t="n">
-        <v>56.48201587207417</v>
+        <v>56.48201970411102</v>
       </c>
       <c r="F547" t="n">
         <v>1664</v>
@@ -11412,16 +11412,16 @@
         <v>40246</v>
       </c>
       <c r="B550" t="n">
-        <v>63.8936882019043</v>
+        <v>63.89368057250977</v>
       </c>
       <c r="C550" t="n">
-        <v>65.27379001284713</v>
+        <v>65.2737822186579</v>
       </c>
       <c r="D550" t="n">
-        <v>61.33794067382813</v>
+        <v>61.33793334960937</v>
       </c>
       <c r="E550" t="n">
-        <v>61.33794067382813</v>
+        <v>61.33793334960937</v>
       </c>
       <c r="F550" t="n">
         <v>1170</v>
@@ -11432,16 +11432,16 @@
         <v>40247</v>
       </c>
       <c r="B551" t="n">
-        <v>65.42713165283203</v>
+        <v>65.4271240234375</v>
       </c>
       <c r="C551" t="n">
-        <v>65.42713165283203</v>
+        <v>65.4271240234375</v>
       </c>
       <c r="D551" t="n">
-        <v>63.89368604050339</v>
+        <v>63.89367858992247</v>
       </c>
       <c r="E551" t="n">
-        <v>63.89368604050339</v>
+        <v>63.89367858992247</v>
       </c>
       <c r="F551" t="n">
         <v>694</v>
@@ -11452,16 +11452,16 @@
         <v>40248</v>
       </c>
       <c r="B552" t="n">
-        <v>65.42713165283203</v>
+        <v>65.4271240234375</v>
       </c>
       <c r="C552" t="n">
-        <v>65.42713165283203</v>
+        <v>65.4271240234375</v>
       </c>
       <c r="D552" t="n">
-        <v>64.66041241247201</v>
+        <v>64.66040487248387</v>
       </c>
       <c r="E552" t="n">
-        <v>65.3760194140109</v>
+        <v>65.37601179057651</v>
       </c>
       <c r="F552" t="n">
         <v>329</v>
@@ -11472,16 +11472,16 @@
         <v>40249</v>
       </c>
       <c r="B553" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="C553" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="D553" t="n">
-        <v>61.95132008877913</v>
+        <v>61.9513272017227</v>
       </c>
       <c r="E553" t="n">
-        <v>65.42713056081816</v>
+        <v>65.42713807283705</v>
       </c>
       <c r="F553" t="n">
         <v>91</v>
@@ -11512,16 +11512,16 @@
         <v>40253</v>
       </c>
       <c r="B555" t="n">
-        <v>69.00518035888672</v>
+        <v>69.00518798828125</v>
       </c>
       <c r="C555" t="n">
-        <v>69.4140996609343</v>
+        <v>69.41410733554002</v>
       </c>
       <c r="D555" t="n">
-        <v>66.44943293818721</v>
+        <v>66.44944028501158</v>
       </c>
       <c r="E555" t="n">
-        <v>69.20964357571478</v>
+        <v>69.2096512277153</v>
       </c>
       <c r="F555" t="n">
         <v>566</v>
@@ -11532,16 +11532,16 @@
         <v>40254</v>
       </c>
       <c r="B556" t="n">
-        <v>65.42713165283203</v>
+        <v>65.4271240234375</v>
       </c>
       <c r="C556" t="n">
-        <v>67.98287909445217</v>
+        <v>67.9828711670344</v>
       </c>
       <c r="D556" t="n">
-        <v>65.42713165283203</v>
+        <v>65.4271240234375</v>
       </c>
       <c r="E556" t="n">
-        <v>67.98287909445217</v>
+        <v>67.9828711670344</v>
       </c>
       <c r="F556" t="n">
         <v>1682</v>
@@ -11612,16 +11612,16 @@
         <v>40260</v>
       </c>
       <c r="B560" t="n">
-        <v>69.00518035888672</v>
+        <v>69.00518798828125</v>
       </c>
       <c r="C560" t="n">
-        <v>69.00518035888672</v>
+        <v>69.00518798828125</v>
       </c>
       <c r="D560" t="n">
-        <v>66.44943293818721</v>
+        <v>66.44944028501158</v>
       </c>
       <c r="E560" t="n">
-        <v>66.44943293818721</v>
+        <v>66.44944028501158</v>
       </c>
       <c r="F560" t="n">
         <v>475</v>
@@ -11632,16 +11632,16 @@
         <v>40261</v>
       </c>
       <c r="B561" t="n">
-        <v>69.00518035888672</v>
+        <v>69.00518798828125</v>
       </c>
       <c r="C561" t="n">
-        <v>69.00518035888672</v>
+        <v>69.00518798828125</v>
       </c>
       <c r="D561" t="n">
-        <v>64.40483642794931</v>
+        <v>64.40484354871769</v>
       </c>
       <c r="E561" t="n">
-        <v>64.40483642794931</v>
+        <v>64.40484354871769</v>
       </c>
       <c r="F561" t="n">
         <v>1462</v>
@@ -11652,16 +11652,16 @@
         <v>40262</v>
       </c>
       <c r="B562" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="C562" t="n">
-        <v>69.15852361752283</v>
+        <v>69.15853155796179</v>
       </c>
       <c r="D562" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="E562" t="n">
-        <v>69.15852361752283</v>
+        <v>69.15853155796179</v>
       </c>
       <c r="F562" t="n">
         <v>182</v>
@@ -11712,16 +11712,16 @@
         <v>40267</v>
       </c>
       <c r="B565" t="n">
-        <v>66.50054931640625</v>
+        <v>66.50055694580078</v>
       </c>
       <c r="C565" t="n">
-        <v>69.26076012576347</v>
+        <v>69.26076807182811</v>
       </c>
       <c r="D565" t="n">
-        <v>66.50054931640625</v>
+        <v>66.50055694580078</v>
       </c>
       <c r="E565" t="n">
-        <v>69.26076012576347</v>
+        <v>69.26076807182811</v>
       </c>
       <c r="F565" t="n">
         <v>402</v>
@@ -11752,16 +11752,16 @@
         <v>40269</v>
       </c>
       <c r="B567" t="n">
-        <v>66.50054931640625</v>
+        <v>66.50055694580078</v>
       </c>
       <c r="C567" t="n">
-        <v>66.50054931640625</v>
+        <v>66.50055694580078</v>
       </c>
       <c r="D567" t="n">
-        <v>66.50054931640625</v>
+        <v>66.50055694580078</v>
       </c>
       <c r="E567" t="n">
-        <v>66.50054931640625</v>
+        <v>66.50055694580078</v>
       </c>
       <c r="F567" t="n">
         <v>36</v>
@@ -11832,16 +11832,16 @@
         <v>40280</v>
       </c>
       <c r="B571" t="n">
-        <v>66.602783203125</v>
+        <v>66.60279083251953</v>
       </c>
       <c r="C571" t="n">
-        <v>69.51633796823158</v>
+        <v>69.51634593137582</v>
       </c>
       <c r="D571" t="n">
-        <v>66.44943934153137</v>
+        <v>66.44944695336025</v>
       </c>
       <c r="E571" t="n">
-        <v>69.51633796823158</v>
+        <v>69.51634593137582</v>
       </c>
       <c r="F571" t="n">
         <v>713</v>
@@ -11872,16 +11872,16 @@
         <v>40282</v>
       </c>
       <c r="B573" t="n">
-        <v>69.00518035888672</v>
+        <v>69.00518798828125</v>
       </c>
       <c r="C573" t="n">
-        <v>69.92525057139591</v>
+        <v>69.92525830251583</v>
       </c>
       <c r="D573" t="n">
-        <v>66.50054517658995</v>
+        <v>66.50055252906543</v>
       </c>
       <c r="E573" t="n">
-        <v>66.50054517658995</v>
+        <v>66.50055252906543</v>
       </c>
       <c r="F573" t="n">
         <v>1280</v>
@@ -12012,16 +12012,16 @@
         <v>40294</v>
       </c>
       <c r="B580" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="C580" t="n">
-        <v>66.50054461101492</v>
+        <v>66.50055224627791</v>
       </c>
       <c r="D580" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="E580" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="F580" t="n">
         <v>54</v>
@@ -12032,16 +12032,16 @@
         <v>40295</v>
       </c>
       <c r="B581" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="C581" t="n">
-        <v>67.21615873221842</v>
+        <v>67.21616644964467</v>
       </c>
       <c r="D581" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="E581" t="n">
-        <v>66.50054461101492</v>
+        <v>66.50055224627791</v>
       </c>
       <c r="F581" t="n">
         <v>384</v>
@@ -12052,16 +12052,16 @@
         <v>40297</v>
       </c>
       <c r="B582" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="C582" t="n">
-        <v>67.21615873221842</v>
+        <v>67.21616644964467</v>
       </c>
       <c r="D582" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="E582" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="F582" t="n">
         <v>73</v>
@@ -12072,16 +12072,16 @@
         <v>40298</v>
       </c>
       <c r="B583" t="n">
-        <v>64.91599273681641</v>
+        <v>64.91600036621094</v>
       </c>
       <c r="C583" t="n">
-        <v>64.91599273681641</v>
+        <v>64.91600036621094</v>
       </c>
       <c r="D583" t="n">
-        <v>64.91599273681641</v>
+        <v>64.91600036621094</v>
       </c>
       <c r="E583" t="n">
-        <v>64.91599273681641</v>
+        <v>64.91600036621094</v>
       </c>
       <c r="F583" t="n">
         <v>36</v>
@@ -12192,16 +12192,16 @@
         <v>40311</v>
       </c>
       <c r="B589" t="n">
-        <v>64.91599273681641</v>
+        <v>64.91600036621094</v>
       </c>
       <c r="C589" t="n">
-        <v>66.44943846411384</v>
+        <v>66.44944627372995</v>
       </c>
       <c r="D589" t="n">
-        <v>64.91599273681641</v>
+        <v>64.91600036621094</v>
       </c>
       <c r="E589" t="n">
-        <v>66.39832622146061</v>
+        <v>66.39833402506963</v>
       </c>
       <c r="F589" t="n">
         <v>2999</v>
@@ -12212,16 +12212,16 @@
         <v>40315</v>
       </c>
       <c r="B590" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="C590" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="D590" t="n">
-        <v>63.79145336653897</v>
+        <v>63.79146069075752</v>
       </c>
       <c r="E590" t="n">
-        <v>63.79145336653897</v>
+        <v>63.79146069075752</v>
       </c>
       <c r="F590" t="n">
         <v>402</v>
@@ -12232,16 +12232,16 @@
         <v>40316</v>
       </c>
       <c r="B591" t="n">
-        <v>65.93828582763672</v>
+        <v>65.93827819824219</v>
       </c>
       <c r="C591" t="n">
-        <v>67.36950703308636</v>
+        <v>67.36949923809226</v>
       </c>
       <c r="D591" t="n">
-        <v>65.93828582763672</v>
+        <v>65.93827819824219</v>
       </c>
       <c r="E591" t="n">
-        <v>66.39832452620684</v>
+        <v>66.39831684358349</v>
       </c>
       <c r="F591" t="n">
         <v>2669</v>
@@ -12252,16 +12252,16 @@
         <v>40317</v>
       </c>
       <c r="B592" t="n">
-        <v>64.40483093261719</v>
+        <v>64.40483856201172</v>
       </c>
       <c r="C592" t="n">
-        <v>65.93827640155249</v>
+        <v>65.93828421259892</v>
       </c>
       <c r="D592" t="n">
-        <v>63.89368006576944</v>
+        <v>63.89368763461306</v>
       </c>
       <c r="E592" t="n">
-        <v>63.89368006576944</v>
+        <v>63.89368763461306</v>
       </c>
       <c r="F592" t="n">
         <v>256</v>
@@ -12272,16 +12272,16 @@
         <v>40318</v>
       </c>
       <c r="B593" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="C593" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="D593" t="n">
-        <v>62.36023938734892</v>
+        <v>62.36024654724258</v>
       </c>
       <c r="E593" t="n">
-        <v>62.36023938734892</v>
+        <v>62.36024654724258</v>
       </c>
       <c r="F593" t="n">
         <v>164</v>
@@ -12292,16 +12292,16 @@
         <v>40319</v>
       </c>
       <c r="B594" t="n">
-        <v>63.8936882019043</v>
+        <v>63.89368057250977</v>
       </c>
       <c r="C594" t="n">
-        <v>66.3472041172713</v>
+        <v>66.34719619490822</v>
       </c>
       <c r="D594" t="n">
-        <v>63.8936882019043</v>
+        <v>63.89368057250977</v>
       </c>
       <c r="E594" t="n">
-        <v>66.3472041172713</v>
+        <v>66.34719619490822</v>
       </c>
       <c r="F594" t="n">
         <v>1280</v>
@@ -12312,16 +12312,16 @@
         <v>40322</v>
       </c>
       <c r="B595" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="C595" t="n">
-        <v>66.70500782610407</v>
+        <v>66.70501548484251</v>
       </c>
       <c r="D595" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="E595" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="F595" t="n">
         <v>292</v>
@@ -12332,16 +12332,16 @@
         <v>40324</v>
       </c>
       <c r="B596" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="C596" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="D596" t="n">
-        <v>66.39832013507883</v>
+        <v>66.39832775860491</v>
       </c>
       <c r="E596" t="n">
-        <v>66.39832013507883</v>
+        <v>66.39832775860491</v>
       </c>
       <c r="F596" t="n">
         <v>932</v>
@@ -12432,16 +12432,16 @@
         <v>40340</v>
       </c>
       <c r="B601" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="C601" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="D601" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="E601" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="F601" t="n">
         <v>73</v>
@@ -12472,16 +12472,16 @@
         <v>40357</v>
       </c>
       <c r="B603" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="C603" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="D603" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="E603" t="n">
-        <v>66.44943237304688</v>
+        <v>66.44944000244141</v>
       </c>
       <c r="F603" t="n">
         <v>128</v>
@@ -12492,16 +12492,16 @@
         <v>40359</v>
       </c>
       <c r="B604" t="n">
-        <v>65.42713165283203</v>
+        <v>65.4271240234375</v>
       </c>
       <c r="C604" t="n">
-        <v>65.93828256747778</v>
+        <v>65.93827487847844</v>
       </c>
       <c r="D604" t="n">
-        <v>65.42713165283203</v>
+        <v>65.4271240234375</v>
       </c>
       <c r="E604" t="n">
-        <v>65.93828256747778</v>
+        <v>65.93827487847844</v>
       </c>
       <c r="F604" t="n">
         <v>73</v>
@@ -12532,16 +12532,16 @@
         <v>40361</v>
       </c>
       <c r="B606" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C606" t="n">
-        <v>81.78391927083332</v>
+        <v>81.78392740885417</v>
       </c>
       <c r="D606" t="n">
-        <v>69.66967665673766</v>
+        <v>69.6696835893142</v>
       </c>
       <c r="E606" t="n">
-        <v>69.66967665673766</v>
+        <v>69.6696835893142</v>
       </c>
       <c r="F606" t="n">
         <v>1517</v>
@@ -12552,16 +12552,16 @@
         <v>40364</v>
       </c>
       <c r="B607" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C607" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D607" t="n">
-        <v>76.57019270573161</v>
+        <v>76.57020032495346</v>
       </c>
       <c r="E607" t="n">
-        <v>76.57019270573161</v>
+        <v>76.57020032495346</v>
       </c>
       <c r="F607" t="n">
         <v>2231</v>
@@ -12572,16 +12572,16 @@
         <v>40365</v>
       </c>
       <c r="B608" t="n">
-        <v>73.09436798095703</v>
+        <v>73.09437561035156</v>
       </c>
       <c r="C608" t="n">
-        <v>76.67241695832192</v>
+        <v>76.67242496118364</v>
       </c>
       <c r="D608" t="n">
-        <v>73.09436798095703</v>
+        <v>73.09437561035156</v>
       </c>
       <c r="E608" t="n">
-        <v>76.62130472369408</v>
+        <v>76.62131272122085</v>
       </c>
       <c r="F608" t="n">
         <v>932</v>
@@ -12592,16 +12592,16 @@
         <v>40366</v>
       </c>
       <c r="B609" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C609" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D609" t="n">
-        <v>73.09437499566381</v>
+        <v>73.09438226901965</v>
       </c>
       <c r="E609" t="n">
-        <v>73.09437499566381</v>
+        <v>73.09438226901965</v>
       </c>
       <c r="F609" t="n">
         <v>36</v>
@@ -12632,16 +12632,16 @@
         <v>40373</v>
       </c>
       <c r="B611" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C611" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D611" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E611" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F611" t="n">
         <v>36</v>
@@ -12652,16 +12652,16 @@
         <v>40378</v>
       </c>
       <c r="B612" t="n">
-        <v>71.56092834472656</v>
+        <v>71.56093597412109</v>
       </c>
       <c r="C612" t="n">
-        <v>71.56092834472656</v>
+        <v>71.56093597412109</v>
       </c>
       <c r="D612" t="n">
-        <v>71.56092834472656</v>
+        <v>71.56093597412109</v>
       </c>
       <c r="E612" t="n">
-        <v>71.56092834472656</v>
+        <v>71.56093597412109</v>
       </c>
       <c r="F612" t="n">
         <v>73</v>
@@ -12672,16 +12672,16 @@
         <v>40379</v>
       </c>
       <c r="B613" t="n">
-        <v>71.56092834472656</v>
+        <v>71.56093597412109</v>
       </c>
       <c r="C613" t="n">
-        <v>71.56092834472656</v>
+        <v>71.56093597412109</v>
       </c>
       <c r="D613" t="n">
-        <v>71.56092834472656</v>
+        <v>71.56093597412109</v>
       </c>
       <c r="E613" t="n">
-        <v>71.56092834472656</v>
+        <v>71.56093597412109</v>
       </c>
       <c r="F613" t="n">
         <v>585</v>
@@ -12732,16 +12732,16 @@
         <v>40386</v>
       </c>
       <c r="B616" t="n">
-        <v>69.51634216308594</v>
+        <v>69.51633453369141</v>
       </c>
       <c r="C616" t="n">
-        <v>69.51634216308594</v>
+        <v>69.51633453369141</v>
       </c>
       <c r="D616" t="n">
-        <v>69.51634216308594</v>
+        <v>69.51633453369141</v>
       </c>
       <c r="E616" t="n">
-        <v>69.51634216308594</v>
+        <v>69.51633453369141</v>
       </c>
       <c r="F616" t="n">
         <v>201</v>
@@ -12752,16 +12752,16 @@
         <v>40387</v>
       </c>
       <c r="B617" t="n">
-        <v>71.56092834472656</v>
+        <v>71.56093597412109</v>
       </c>
       <c r="C617" t="n">
-        <v>71.56092834472656</v>
+        <v>71.56093597412109</v>
       </c>
       <c r="D617" t="n">
-        <v>71.56092834472656</v>
+        <v>71.56093597412109</v>
       </c>
       <c r="E617" t="n">
-        <v>71.56092834472656</v>
+        <v>71.56093597412109</v>
       </c>
       <c r="F617" t="n">
         <v>54</v>
@@ -12792,16 +12792,16 @@
         <v>40389</v>
       </c>
       <c r="B619" t="n">
-        <v>78.46144866943359</v>
+        <v>78.46144104003906</v>
       </c>
       <c r="C619" t="n">
-        <v>78.46144866943359</v>
+        <v>78.46144104003906</v>
       </c>
       <c r="D619" t="n">
-        <v>74.88340633170574</v>
+        <v>74.88339905023106</v>
       </c>
       <c r="E619" t="n">
-        <v>74.88340633170574</v>
+        <v>74.88339905023106</v>
       </c>
       <c r="F619" t="n">
         <v>4900</v>
@@ -12812,16 +12812,16 @@
         <v>40392</v>
       </c>
       <c r="B620" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C620" t="n">
-        <v>78.46144541097311</v>
+        <v>78.46145321838664</v>
       </c>
       <c r="D620" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E620" t="n">
-        <v>78.41033317144014</v>
+        <v>78.41034097376769</v>
       </c>
       <c r="F620" t="n">
         <v>457</v>
@@ -12832,16 +12832,16 @@
         <v>40394</v>
       </c>
       <c r="B621" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C621" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D621" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E621" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F621" t="n">
         <v>548</v>
@@ -12852,16 +12852,16 @@
         <v>40395</v>
       </c>
       <c r="B622" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C622" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D622" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E622" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F622" t="n">
         <v>2395</v>
@@ -12872,16 +12872,16 @@
         <v>40396</v>
       </c>
       <c r="B623" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C623" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D623" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E623" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F623" t="n">
         <v>4590</v>
@@ -12892,16 +12892,16 @@
         <v>40399</v>
       </c>
       <c r="B624" t="n">
-        <v>77.18356323242188</v>
+        <v>77.18357086181641</v>
       </c>
       <c r="C624" t="n">
-        <v>77.18356323242188</v>
+        <v>77.18357086181641</v>
       </c>
       <c r="D624" t="n">
-        <v>76.62130015858335</v>
+        <v>76.62130773239964</v>
       </c>
       <c r="E624" t="n">
-        <v>76.62130015858335</v>
+        <v>76.62130773239964</v>
       </c>
       <c r="F624" t="n">
         <v>2487</v>
@@ -12912,16 +12912,16 @@
         <v>40403</v>
       </c>
       <c r="B625" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C625" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D625" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E625" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F625" t="n">
         <v>182</v>
@@ -12932,16 +12932,16 @@
         <v>40406</v>
       </c>
       <c r="B626" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C626" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D626" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E626" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F626" t="n">
         <v>18</v>
@@ -12952,16 +12952,16 @@
         <v>40407</v>
       </c>
       <c r="B627" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C627" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D627" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E627" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F627" t="n">
         <v>786</v>
@@ -12972,16 +12972,16 @@
         <v>40408</v>
       </c>
       <c r="B628" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C628" t="n">
-        <v>78.15475771055793</v>
+        <v>78.15476548745407</v>
       </c>
       <c r="D628" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E628" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F628" t="n">
         <v>585</v>
@@ -12992,16 +12992,16 @@
         <v>40409</v>
       </c>
       <c r="B629" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C629" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D629" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E629" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F629" t="n">
         <v>36</v>
@@ -13012,16 +13012,16 @@
         <v>40413</v>
       </c>
       <c r="B630" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C630" t="n">
-        <v>78.20586995009089</v>
+        <v>78.20587773207303</v>
       </c>
       <c r="D630" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E630" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F630" t="n">
         <v>4187</v>
@@ -13032,16 +13032,16 @@
         <v>40414</v>
       </c>
       <c r="B631" t="n">
-        <v>78.20587158203125</v>
+        <v>78.20586395263672</v>
       </c>
       <c r="C631" t="n">
-        <v>78.20587158203125</v>
+        <v>78.20586395263672</v>
       </c>
       <c r="D631" t="n">
-        <v>78.20587158203125</v>
+        <v>78.20586395263672</v>
       </c>
       <c r="E631" t="n">
-        <v>78.20587158203125</v>
+        <v>78.20586395263672</v>
       </c>
       <c r="F631" t="n">
         <v>73</v>
@@ -13092,16 +13092,16 @@
         <v>40417</v>
       </c>
       <c r="B634" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C634" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D634" t="n">
-        <v>76.57019270573161</v>
+        <v>76.57020032495346</v>
       </c>
       <c r="E634" t="n">
-        <v>76.57019270573161</v>
+        <v>76.57020032495346</v>
       </c>
       <c r="F634" t="n">
         <v>1883</v>
@@ -13112,16 +13112,16 @@
         <v>40420</v>
       </c>
       <c r="B635" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C635" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D635" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E635" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F635" t="n">
         <v>310</v>
@@ -13172,16 +13172,16 @@
         <v>40424</v>
       </c>
       <c r="B638" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C638" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D638" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E638" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F638" t="n">
         <v>548</v>
@@ -13192,16 +13192,16 @@
         <v>40427</v>
       </c>
       <c r="B639" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C639" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D639" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E639" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F639" t="n">
         <v>18</v>
@@ -13212,16 +13212,16 @@
         <v>40429</v>
       </c>
       <c r="B640" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C640" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D640" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E640" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F640" t="n">
         <v>2194</v>
@@ -13252,16 +13252,16 @@
         <v>40431</v>
       </c>
       <c r="B642" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C642" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D642" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E642" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F642" t="n">
         <v>2743</v>
@@ -13272,16 +13272,16 @@
         <v>40434</v>
       </c>
       <c r="B643" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C643" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D643" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E643" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F643" t="n">
         <v>91</v>
@@ -13292,16 +13292,16 @@
         <v>40436</v>
       </c>
       <c r="B644" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C644" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D644" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E644" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F644" t="n">
         <v>109</v>
@@ -13312,16 +13312,16 @@
         <v>40438</v>
       </c>
       <c r="B645" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C645" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D645" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E645" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F645" t="n">
         <v>969</v>
@@ -13412,16 +13412,16 @@
         <v>40456</v>
       </c>
       <c r="B650" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C650" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D650" t="n">
-        <v>72.53211183436639</v>
+        <v>72.53211905177346</v>
       </c>
       <c r="E650" t="n">
-        <v>72.53211183436639</v>
+        <v>72.53211905177346</v>
       </c>
       <c r="F650" t="n">
         <v>310</v>
@@ -13432,16 +13432,16 @@
         <v>40458</v>
       </c>
       <c r="B651" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C651" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D651" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E651" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F651" t="n">
         <v>2048</v>
@@ -13492,16 +13492,16 @@
         <v>40465</v>
       </c>
       <c r="B654" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C654" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D654" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E654" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F654" t="n">
         <v>1847</v>
@@ -13512,16 +13512,16 @@
         <v>40476</v>
       </c>
       <c r="B655" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C655" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D655" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E655" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F655" t="n">
         <v>237</v>
@@ -13532,16 +13532,16 @@
         <v>40477</v>
       </c>
       <c r="B656" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C656" t="n">
-        <v>77.18357523817069</v>
+        <v>77.183582918428</v>
       </c>
       <c r="D656" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E656" t="n">
-        <v>77.18357523817069</v>
+        <v>77.183582918428</v>
       </c>
       <c r="F656" t="n">
         <v>182</v>
@@ -13552,16 +13552,16 @@
         <v>40479</v>
       </c>
       <c r="B657" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C657" t="n">
-        <v>77.18357523817069</v>
+        <v>77.183582918428</v>
       </c>
       <c r="D657" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E657" t="n">
-        <v>77.18357523817069</v>
+        <v>77.183582918428</v>
       </c>
       <c r="F657" t="n">
         <v>768</v>
@@ -13612,16 +13612,16 @@
         <v>40487</v>
       </c>
       <c r="B660" t="n">
-        <v>77.18356323242188</v>
+        <v>77.18357086181641</v>
       </c>
       <c r="C660" t="n">
-        <v>77.18356323242188</v>
+        <v>77.18357086181641</v>
       </c>
       <c r="D660" t="n">
-        <v>77.18356323242188</v>
+        <v>77.18357086181641</v>
       </c>
       <c r="E660" t="n">
-        <v>77.18356323242188</v>
+        <v>77.18357086181641</v>
       </c>
       <c r="F660" t="n">
         <v>91</v>
@@ -13632,16 +13632,16 @@
         <v>40490</v>
       </c>
       <c r="B661" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C661" t="n">
-        <v>77.18357523817069</v>
+        <v>77.183582918428</v>
       </c>
       <c r="D661" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E661" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F661" t="n">
         <v>548</v>
@@ -13652,16 +13652,16 @@
         <v>40491</v>
       </c>
       <c r="B662" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C662" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D662" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E662" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F662" t="n">
         <v>676</v>
@@ -13672,16 +13672,16 @@
         <v>40492</v>
       </c>
       <c r="B663" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="C663" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="D663" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="E663" t="n">
-        <v>76.67242431640625</v>
+        <v>76.67243194580078</v>
       </c>
       <c r="F663" t="n">
         <v>109</v>
@@ -13792,16 +13792,16 @@
         <v>40501</v>
       </c>
       <c r="B669" t="n">
-        <v>97.83401489257812</v>
+        <v>97.83402252197266</v>
       </c>
       <c r="C669" t="n">
-        <v>98.14070973634817</v>
+        <v>98.14071738965968</v>
       </c>
       <c r="D669" t="n">
-        <v>94.56266027856951</v>
+        <v>94.56266765285385</v>
       </c>
       <c r="E669" t="n">
-        <v>95.5849621612517</v>
+        <v>95.58496961525823</v>
       </c>
       <c r="F669" t="n">
         <v>3310</v>
@@ -13912,16 +13912,16 @@
         <v>40513</v>
       </c>
       <c r="B675" t="n">
-        <v>96.60725402832031</v>
+        <v>96.60726165771484</v>
       </c>
       <c r="C675" t="n">
-        <v>99.16300152712036</v>
+        <v>99.16300935835073</v>
       </c>
       <c r="D675" t="n">
-        <v>96.60725402832031</v>
+        <v>96.60726165771484</v>
       </c>
       <c r="E675" t="n">
-        <v>97.11840495440207</v>
+        <v>97.11841262416388</v>
       </c>
       <c r="F675" t="n">
         <v>1938</v>
@@ -13932,16 +13932,16 @@
         <v>40515</v>
       </c>
       <c r="B676" t="n">
-        <v>96.60725402832031</v>
+        <v>96.60726165771484</v>
       </c>
       <c r="C676" t="n">
-        <v>96.60725402832031</v>
+        <v>96.60726165771484</v>
       </c>
       <c r="D676" t="n">
-        <v>96.60725402832031</v>
+        <v>96.60726165771484</v>
       </c>
       <c r="E676" t="n">
-        <v>96.60725402832031</v>
+        <v>96.60726165771484</v>
       </c>
       <c r="F676" t="n">
         <v>91</v>
@@ -14052,16 +14052,16 @@
         <v>40526</v>
       </c>
       <c r="B682" t="n">
-        <v>93.02920532226562</v>
+        <v>93.02921295166016</v>
       </c>
       <c r="C682" t="n">
-        <v>93.02920532226562</v>
+        <v>93.02921295166016</v>
       </c>
       <c r="D682" t="n">
-        <v>93.02920532226562</v>
+        <v>93.02921295166016</v>
       </c>
       <c r="E682" t="n">
-        <v>93.02920532226562</v>
+        <v>93.02921295166016</v>
       </c>
       <c r="F682" t="n">
         <v>182</v>
@@ -14172,16 +14172,16 @@
         <v>40534</v>
       </c>
       <c r="B688" t="n">
-        <v>99.67414855957031</v>
+        <v>99.67415618896484</v>
       </c>
       <c r="C688" t="n">
-        <v>101.2076012779134</v>
+        <v>101.2076090246836</v>
       </c>
       <c r="D688" t="n">
-        <v>97.62955206672135</v>
+        <v>97.62955953961558</v>
       </c>
       <c r="E688" t="n">
-        <v>97.62955206672135</v>
+        <v>97.62955953961558</v>
       </c>
       <c r="F688" t="n">
         <v>1828</v>
@@ -14292,16 +14292,16 @@
         <v>40554</v>
       </c>
       <c r="B694" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="C694" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="D694" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="E694" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="F694" t="n">
         <v>548</v>
@@ -14312,16 +14312,16 @@
         <v>40555</v>
       </c>
       <c r="B695" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="C695" t="n">
-        <v>111.9417448107898</v>
+        <v>111.9417370394532</v>
       </c>
       <c r="D695" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="E695" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="F695" t="n">
         <v>219</v>
@@ -14332,16 +14332,16 @@
         <v>40556</v>
       </c>
       <c r="B696" t="n">
-        <v>104.78564453125</v>
+        <v>104.7856521606445</v>
       </c>
       <c r="C696" t="n">
-        <v>107.3413919588415</v>
+        <v>107.3413997743188</v>
       </c>
       <c r="D696" t="n">
-        <v>104.78564453125</v>
+        <v>104.7856521606445</v>
       </c>
       <c r="E696" t="n">
-        <v>104.78564453125</v>
+        <v>104.7856521606445</v>
       </c>
       <c r="F696" t="n">
         <v>1206</v>
@@ -14372,16 +14372,16 @@
         <v>40560</v>
       </c>
       <c r="B698" t="n">
-        <v>105.8079605102539</v>
+        <v>105.8079528808594</v>
       </c>
       <c r="C698" t="n">
-        <v>105.8079605102539</v>
+        <v>105.8079528808594</v>
       </c>
       <c r="D698" t="n">
-        <v>105.8079605102539</v>
+        <v>105.8079528808594</v>
       </c>
       <c r="E698" t="n">
-        <v>105.8079605102539</v>
+        <v>105.8079528808594</v>
       </c>
       <c r="F698" t="n">
         <v>36</v>
@@ -14512,16 +14512,16 @@
         <v>40570</v>
       </c>
       <c r="B705" t="n">
-        <v>118.5867004394531</v>
+        <v>118.5866928100586</v>
       </c>
       <c r="C705" t="n">
-        <v>118.5867004394531</v>
+        <v>118.5866928100586</v>
       </c>
       <c r="D705" t="n">
-        <v>117.5643984696816</v>
+        <v>117.5643909060579</v>
       </c>
       <c r="E705" t="n">
-        <v>117.5643984696816</v>
+        <v>117.5643909060579</v>
       </c>
       <c r="F705" t="n">
         <v>914</v>
@@ -14532,16 +14532,16 @@
         <v>40571</v>
       </c>
       <c r="B706" t="n">
-        <v>112.452880859375</v>
+        <v>112.4528884887695</v>
       </c>
       <c r="C706" t="n">
-        <v>112.452880859375</v>
+        <v>112.4528884887695</v>
       </c>
       <c r="D706" t="n">
-        <v>112.452880859375</v>
+        <v>112.4528884887695</v>
       </c>
       <c r="E706" t="n">
-        <v>112.452880859375</v>
+        <v>112.4528884887695</v>
       </c>
       <c r="F706" t="n">
         <v>548</v>
@@ -14552,16 +14552,16 @@
         <v>40574</v>
       </c>
       <c r="B707" t="n">
-        <v>112.452880859375</v>
+        <v>112.4528884887695</v>
       </c>
       <c r="C707" t="n">
-        <v>115.0086281516335</v>
+        <v>115.0086359544234</v>
       </c>
       <c r="D707" t="n">
-        <v>112.452880859375</v>
+        <v>112.4528884887695</v>
       </c>
       <c r="E707" t="n">
-        <v>115.0086281516335</v>
+        <v>115.0086359544234</v>
       </c>
       <c r="F707" t="n">
         <v>786</v>
@@ -14612,16 +14612,16 @@
         <v>40577</v>
       </c>
       <c r="B710" t="n">
-        <v>118.9955978393555</v>
+        <v>118.99560546875</v>
       </c>
       <c r="C710" t="n">
-        <v>118.9955978393555</v>
+        <v>118.99560546875</v>
       </c>
       <c r="D710" t="n">
-        <v>118.9444784713357</v>
+        <v>118.9444860974527</v>
       </c>
       <c r="E710" t="n">
-        <v>118.9444784713357</v>
+        <v>118.9444860974527</v>
       </c>
       <c r="F710" t="n">
         <v>73</v>
@@ -14732,16 +14732,16 @@
         <v>40590</v>
       </c>
       <c r="B716" t="n">
-        <v>120.1201400756836</v>
+        <v>120.1201477050781</v>
       </c>
       <c r="C716" t="n">
-        <v>122.6758804535232</v>
+        <v>122.6758882452448</v>
       </c>
       <c r="D716" t="n">
-        <v>120.1201400756836</v>
+        <v>120.1201477050781</v>
       </c>
       <c r="E716" t="n">
-        <v>122.6758804535232</v>
+        <v>122.6758882452448</v>
       </c>
       <c r="F716" t="n">
         <v>73</v>
@@ -14752,16 +14752,16 @@
         <v>40591</v>
       </c>
       <c r="B717" t="n">
-        <v>130.3431091308594</v>
+        <v>130.3431243896484</v>
       </c>
       <c r="C717" t="n">
-        <v>130.3431091308594</v>
+        <v>130.3431243896484</v>
       </c>
       <c r="D717" t="n">
-        <v>128.8096565930801</v>
+        <v>128.8096716723535</v>
       </c>
       <c r="E717" t="n">
-        <v>128.8096565930801</v>
+        <v>128.8096716723535</v>
       </c>
       <c r="F717" t="n">
         <v>91</v>
@@ -14772,16 +14772,16 @@
         <v>40592</v>
       </c>
       <c r="B718" t="n">
-        <v>130.3431091308594</v>
+        <v>130.3431243896484</v>
       </c>
       <c r="C718" t="n">
-        <v>131.365396559497</v>
+        <v>131.3654119379615</v>
       </c>
       <c r="D718" t="n">
-        <v>127.7873549012272</v>
+        <v>127.7873698608235</v>
       </c>
       <c r="E718" t="n">
-        <v>130.3431091308594</v>
+        <v>130.3431243896484</v>
       </c>
       <c r="F718" t="n">
         <v>676</v>
@@ -14792,16 +14792,16 @@
         <v>40595</v>
       </c>
       <c r="B719" t="n">
-        <v>130.3431091308594</v>
+        <v>130.3431243896484</v>
       </c>
       <c r="C719" t="n">
-        <v>130.3431091308594</v>
+        <v>130.3431243896484</v>
       </c>
       <c r="D719" t="n">
-        <v>130.3431091308594</v>
+        <v>130.3431243896484</v>
       </c>
       <c r="E719" t="n">
-        <v>130.3431091308594</v>
+        <v>130.3431243896484</v>
       </c>
       <c r="F719" t="n">
         <v>164</v>
@@ -14812,16 +14812,16 @@
         <v>40599</v>
       </c>
       <c r="B720" t="n">
-        <v>140.0038452148438</v>
+        <v>140.0038299560547</v>
       </c>
       <c r="C720" t="n">
-        <v>140.0549645849373</v>
+        <v>140.0549493205768</v>
       </c>
       <c r="D720" t="n">
-        <v>140.0038452148438</v>
+        <v>140.0038299560547</v>
       </c>
       <c r="E720" t="n">
-        <v>140.0549645849373</v>
+        <v>140.0549493205768</v>
       </c>
       <c r="F720" t="n">
         <v>201</v>
@@ -14892,16 +14892,16 @@
         <v>40617</v>
       </c>
       <c r="B724" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="C724" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="D724" t="n">
-        <v>135.7101887523047</v>
+        <v>135.7102037567807</v>
       </c>
       <c r="E724" t="n">
-        <v>135.7101887523047</v>
+        <v>135.7102037567807</v>
       </c>
       <c r="F724" t="n">
         <v>54</v>
@@ -14912,16 +14912,16 @@
         <v>40618</v>
       </c>
       <c r="B725" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="C725" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="D725" t="n">
-        <v>135.965757075927</v>
+        <v>135.9657721086593</v>
       </c>
       <c r="E725" t="n">
-        <v>135.965757075927</v>
+        <v>135.9657721086593</v>
       </c>
       <c r="F725" t="n">
         <v>36</v>
@@ -14972,16 +14972,16 @@
         <v>40627</v>
       </c>
       <c r="B728" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="C728" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="D728" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="E728" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="F728" t="n">
         <v>2</v>
@@ -14992,16 +14992,16 @@
         <v>40630</v>
       </c>
       <c r="B729" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="C729" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="D729" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="E729" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="F729" t="n">
         <v>1792</v>
@@ -15012,16 +15012,16 @@
         <v>40632</v>
       </c>
       <c r="B730" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="C730" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="D730" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="E730" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="F730" t="n">
         <v>73</v>
@@ -15032,16 +15032,16 @@
         <v>40634</v>
       </c>
       <c r="B731" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="C731" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="D731" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="E731" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="F731" t="n">
         <v>402</v>
@@ -15052,16 +15052,16 @@
         <v>40637</v>
       </c>
       <c r="B732" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="C732" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="D732" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="E732" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="F732" t="n">
         <v>365</v>
@@ -15072,16 +15072,16 @@
         <v>40640</v>
       </c>
       <c r="B733" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="C733" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="D733" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="E733" t="n">
-        <v>138.0103607177734</v>
+        <v>138.0103759765625</v>
       </c>
       <c r="F733" t="n">
         <v>18</v>
@@ -15232,16 +15232,16 @@
         <v>40662</v>
       </c>
       <c r="B741" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="C741" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="D741" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="E741" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="F741" t="n">
         <v>146</v>
@@ -15252,16 +15252,16 @@
         <v>40665</v>
       </c>
       <c r="B742" t="n">
-        <v>130.3431091308594</v>
+        <v>130.3431243896484</v>
       </c>
       <c r="C742" t="n">
-        <v>130.3431091308594</v>
+        <v>130.3431243896484</v>
       </c>
       <c r="D742" t="n">
-        <v>130.3431091308594</v>
+        <v>130.3431243896484</v>
       </c>
       <c r="E742" t="n">
-        <v>130.3431091308594</v>
+        <v>130.3431243896484</v>
       </c>
       <c r="F742" t="n">
         <v>18</v>
@@ -15272,16 +15272,16 @@
         <v>40667</v>
       </c>
       <c r="B743" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="C743" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="D743" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="E743" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="F743" t="n">
         <v>18</v>
@@ -15292,16 +15292,16 @@
         <v>40668</v>
       </c>
       <c r="B744" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="C744" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="D744" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="E744" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="F744" t="n">
         <v>201</v>
@@ -15312,16 +15312,16 @@
         <v>40672</v>
       </c>
       <c r="B745" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="C745" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="D745" t="n">
-        <v>124.5160155596087</v>
+        <v>124.5160298559206</v>
       </c>
       <c r="E745" t="n">
-        <v>124.5160155596087</v>
+        <v>124.5160298559206</v>
       </c>
       <c r="F745" t="n">
         <v>2615</v>
@@ -15332,16 +15332,16 @@
         <v>40676</v>
       </c>
       <c r="B746" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="C746" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="D746" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="E746" t="n">
-        <v>132.8988647460938</v>
+        <v>132.8988800048828</v>
       </c>
       <c r="F746" t="n">
         <v>3712</v>
@@ -15352,16 +15352,16 @@
         <v>40682</v>
       </c>
       <c r="B747" t="n">
-        <v>127.7873764038086</v>
+        <v>127.7873611450195</v>
       </c>
       <c r="C747" t="n">
-        <v>127.7873764038086</v>
+        <v>127.7873611450195</v>
       </c>
       <c r="D747" t="n">
-        <v>127.7873764038086</v>
+        <v>127.7873611450195</v>
       </c>
       <c r="E747" t="n">
-        <v>127.7873764038086</v>
+        <v>127.7873611450195</v>
       </c>
       <c r="F747" t="n">
         <v>54</v>
@@ -15412,16 +15412,16 @@
         <v>40695</v>
       </c>
       <c r="B750" t="n">
-        <v>127.7873764038086</v>
+        <v>127.7873611450195</v>
       </c>
       <c r="C750" t="n">
-        <v>130.3431310634936</v>
+        <v>130.3431154995279</v>
       </c>
       <c r="D750" t="n">
-        <v>127.7873764038086</v>
+        <v>127.7873611450195</v>
       </c>
       <c r="E750" t="n">
-        <v>130.3431310634936</v>
+        <v>130.3431154995279</v>
       </c>
       <c r="F750" t="n">
         <v>3785</v>
@@ -15432,16 +15432,16 @@
         <v>40703</v>
       </c>
       <c r="B751" t="n">
-        <v>127.7873764038086</v>
+        <v>127.7873611450195</v>
       </c>
       <c r="C751" t="n">
-        <v>127.7873764038086</v>
+        <v>127.7873611450195</v>
       </c>
       <c r="D751" t="n">
-        <v>127.7873764038086</v>
+        <v>127.7873611450195</v>
       </c>
       <c r="E751" t="n">
-        <v>127.7873764038086</v>
+        <v>127.7873611450195</v>
       </c>
       <c r="F751" t="n">
         <v>768</v>
@@ -15512,16 +15512,16 @@
         <v>40764</v>
       </c>
       <c r="B755" t="n">
-        <v>112.452880859375</v>
+        <v>112.4528884887695</v>
       </c>
       <c r="C755" t="n">
-        <v>112.452880859375</v>
+        <v>112.4528884887695</v>
       </c>
       <c r="D755" t="n">
-        <v>110.0504774062268</v>
+        <v>110.0504848726297</v>
       </c>
       <c r="E755" t="n">
-        <v>110.0504774062268</v>
+        <v>110.0504848726297</v>
       </c>
       <c r="F755" t="n">
         <v>54</v>
@@ -15532,16 +15532,16 @@
         <v>40778</v>
       </c>
       <c r="B756" t="n">
-        <v>112.452880859375</v>
+        <v>112.4528884887695</v>
       </c>
       <c r="C756" t="n">
-        <v>112.452880859375</v>
+        <v>112.4528884887695</v>
       </c>
       <c r="D756" t="n">
-        <v>112.452880859375</v>
+        <v>112.4528884887695</v>
       </c>
       <c r="E756" t="n">
-        <v>112.452880859375</v>
+        <v>112.4528884887695</v>
       </c>
       <c r="F756" t="n">
         <v>73</v>
@@ -15552,16 +15552,16 @@
         <v>40779</v>
       </c>
       <c r="B757" t="n">
-        <v>110.1016006469727</v>
+        <v>110.1016082763672</v>
       </c>
       <c r="C757" t="n">
-        <v>110.1016006469727</v>
+        <v>110.1016082763672</v>
       </c>
       <c r="D757" t="n">
-        <v>110.1016006469727</v>
+        <v>110.1016082763672</v>
       </c>
       <c r="E757" t="n">
-        <v>110.1016006469727</v>
+        <v>110.1016082763672</v>
       </c>
       <c r="F757" t="n">
         <v>18</v>
@@ -15592,16 +15592,16 @@
         <v>40781</v>
       </c>
       <c r="B759" t="n">
-        <v>111.9417343139648</v>
+        <v>111.9417419433594</v>
       </c>
       <c r="C759" t="n">
-        <v>111.9417343139648</v>
+        <v>111.9417419433594</v>
       </c>
       <c r="D759" t="n">
-        <v>111.9417343139648</v>
+        <v>111.9417419433594</v>
       </c>
       <c r="E759" t="n">
-        <v>111.9417343139648</v>
+        <v>111.9417419433594</v>
       </c>
       <c r="F759" t="n">
         <v>91</v>
@@ -15652,16 +15652,16 @@
         <v>40787</v>
       </c>
       <c r="B762" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="C762" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="D762" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="E762" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="F762" t="n">
         <v>36</v>
@@ -15672,16 +15672,16 @@
         <v>40794</v>
       </c>
       <c r="B763" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="C763" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="D763" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="E763" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="F763" t="n">
         <v>18</v>
@@ -15772,16 +15772,16 @@
         <v>40808</v>
       </c>
       <c r="B768" t="n">
-        <v>94.61376190185547</v>
+        <v>94.61376953125</v>
       </c>
       <c r="C768" t="n">
-        <v>94.71598636565891</v>
+        <v>94.71599400329654</v>
       </c>
       <c r="D768" t="n">
-        <v>94.61376190185547</v>
+        <v>94.61376953125</v>
       </c>
       <c r="E768" t="n">
-        <v>94.71598636565891</v>
+        <v>94.71599400329654</v>
       </c>
       <c r="F768" t="n">
         <v>36</v>
@@ -15792,16 +15792,16 @@
         <v>40812</v>
       </c>
       <c r="B769" t="n">
-        <v>94.61376190185547</v>
+        <v>94.61376953125</v>
       </c>
       <c r="C769" t="n">
-        <v>94.61376190185547</v>
+        <v>94.61376953125</v>
       </c>
       <c r="D769" t="n">
-        <v>94.61376190185547</v>
+        <v>94.61376953125</v>
       </c>
       <c r="E769" t="n">
-        <v>94.61376190185547</v>
+        <v>94.61376953125</v>
       </c>
       <c r="F769" t="n">
         <v>384</v>
@@ -15932,16 +15932,16 @@
         <v>40870</v>
       </c>
       <c r="B776" t="n">
-        <v>80.19935607910156</v>
+        <v>80.19936370849609</v>
       </c>
       <c r="C776" t="n">
-        <v>80.19935607910156</v>
+        <v>80.19936370849609</v>
       </c>
       <c r="D776" t="n">
-        <v>80.19935607910156</v>
+        <v>80.19936370849609</v>
       </c>
       <c r="E776" t="n">
-        <v>80.19935607910156</v>
+        <v>80.19936370849609</v>
       </c>
       <c r="F776" t="n">
         <v>694</v>
@@ -15992,16 +15992,16 @@
         <v>40886</v>
       </c>
       <c r="B779" t="n">
-        <v>77.18356323242188</v>
+        <v>77.18357086181641</v>
       </c>
       <c r="C779" t="n">
-        <v>77.18356323242188</v>
+        <v>77.18357086181641</v>
       </c>
       <c r="D779" t="n">
-        <v>77.18356323242188</v>
+        <v>77.18357086181641</v>
       </c>
       <c r="E779" t="n">
-        <v>77.18356323242188</v>
+        <v>77.18357086181641</v>
       </c>
       <c r="F779" t="n">
         <v>329</v>
@@ -16052,16 +16052,16 @@
         <v>40891</v>
       </c>
       <c r="B782" t="n">
-        <v>77.18356323242188</v>
+        <v>77.18357086181641</v>
       </c>
       <c r="C782" t="n">
-        <v>77.18356323242188</v>
+        <v>77.18357086181641</v>
       </c>
       <c r="D782" t="n">
-        <v>77.18356323242188</v>
+        <v>77.18357086181641</v>
       </c>
       <c r="E782" t="n">
-        <v>77.18356323242188</v>
+        <v>77.18357086181641</v>
       </c>
       <c r="F782" t="n">
         <v>18</v>
@@ -16112,16 +16112,16 @@
         <v>40905</v>
       </c>
       <c r="B785" t="n">
-        <v>78.46144866943359</v>
+        <v>78.46144104003906</v>
       </c>
       <c r="C785" t="n">
-        <v>79.33040669884224</v>
+        <v>79.33039898495241</v>
       </c>
       <c r="D785" t="n">
-        <v>78.46144866943359</v>
+        <v>78.46144104003906</v>
       </c>
       <c r="E785" t="n">
-        <v>79.228175083922</v>
+        <v>79.2281673799729</v>
       </c>
       <c r="F785" t="n">
         <v>731</v>
@@ -16372,16 +16372,16 @@
         <v>40956</v>
       </c>
       <c r="B798" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="C798" t="n">
-        <v>125.7427777391395</v>
+        <v>125.7427690096931</v>
       </c>
       <c r="D798" t="n">
-        <v>101.4631788105933</v>
+        <v>101.4631717667106</v>
       </c>
       <c r="E798" t="n">
-        <v>101.4631788105933</v>
+        <v>101.4631717667106</v>
       </c>
       <c r="F798" t="n">
         <v>475</v>
@@ -16392,16 +16392,16 @@
         <v>40966</v>
       </c>
       <c r="B799" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="C799" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="D799" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="E799" t="n">
-        <v>109.8971481323242</v>
+        <v>109.8971405029297</v>
       </c>
       <c r="F799" t="n">
         <v>18</v>
@@ -16472,16 +16472,16 @@
         <v>40976</v>
       </c>
       <c r="B803" t="n">
-        <v>129.8319854736328</v>
+        <v>129.8320007324219</v>
       </c>
       <c r="C803" t="n">
-        <v>129.8319854736328</v>
+        <v>129.8320007324219</v>
       </c>
       <c r="D803" t="n">
-        <v>127.2762307087885</v>
+        <v>127.2762456672069</v>
       </c>
       <c r="E803" t="n">
-        <v>127.2762307087885</v>
+        <v>127.2762456672069</v>
       </c>
       <c r="F803" t="n">
         <v>182</v>
@@ -16692,16 +16692,16 @@
         <v>41031</v>
       </c>
       <c r="B814" t="n">
-        <v>112.452880859375</v>
+        <v>112.4528884887695</v>
       </c>
       <c r="C814" t="n">
-        <v>112.452880859375</v>
+        <v>112.4528884887695</v>
       </c>
       <c r="D814" t="n">
-        <v>112.452880859375</v>
+        <v>112.4528884887695</v>
       </c>
       <c r="E814" t="n">
-        <v>112.452880859375</v>
+        <v>112.4528884887695</v>
       </c>
       <c r="F814" t="n">
         <v>182</v>
@@ -17012,16 +17012,16 @@
         <v>41095</v>
       </c>
       <c r="B830" t="n">
-        <v>93.02920532226562</v>
+        <v>93.02921295166016</v>
       </c>
       <c r="C830" t="n">
-        <v>93.02920532226562</v>
+        <v>93.02921295166016</v>
       </c>
       <c r="D830" t="n">
-        <v>81.83502649540937</v>
+        <v>81.83503320676095</v>
       </c>
       <c r="E830" t="n">
-        <v>81.83502649540937</v>
+        <v>81.83503320676095</v>
       </c>
       <c r="F830" t="n">
         <v>36</v>
@@ -17032,16 +17032,16 @@
         <v>41101</v>
       </c>
       <c r="B831" t="n">
-        <v>93.02920532226562</v>
+        <v>93.02921295166016</v>
       </c>
       <c r="C831" t="n">
-        <v>93.02920532226562</v>
+        <v>93.02921295166016</v>
       </c>
       <c r="D831" t="n">
-        <v>93.02920532226562</v>
+        <v>93.02921295166016</v>
       </c>
       <c r="E831" t="n">
-        <v>93.02920532226562</v>
+        <v>93.02921295166016</v>
       </c>
       <c r="F831" t="n">
         <v>73</v>
@@ -17052,16 +17052,16 @@
         <v>41108</v>
       </c>
       <c r="B832" t="n">
-        <v>93.02920532226562</v>
+        <v>93.02921295166016</v>
       </c>
       <c r="C832" t="n">
-        <v>93.02920532226562</v>
+        <v>93.02921295166016</v>
       </c>
       <c r="D832" t="n">
-        <v>93.02920532226562</v>
+        <v>93.02921295166016</v>
       </c>
       <c r="E832" t="n">
-        <v>93.02920532226562</v>
+        <v>93.02921295166016</v>
       </c>
       <c r="F832" t="n">
         <v>18</v>
@@ -17152,16 +17152,16 @@
         <v>41158</v>
       </c>
       <c r="B837" t="n">
-        <v>91.75133514404297</v>
+        <v>91.7513427734375</v>
       </c>
       <c r="C837" t="n">
-        <v>91.75133514404297</v>
+        <v>91.7513427734375</v>
       </c>
       <c r="D837" t="n">
-        <v>91.75133514404297</v>
+        <v>91.7513427734375</v>
       </c>
       <c r="E837" t="n">
-        <v>91.75133514404297</v>
+        <v>91.7513427734375</v>
       </c>
       <c r="F837" t="n">
         <v>18</v>
@@ -17192,16 +17192,16 @@
         <v>41164</v>
       </c>
       <c r="B839" t="n">
-        <v>92.51806640625</v>
+        <v>92.51807403564453</v>
       </c>
       <c r="C839" t="n">
-        <v>92.51806640625</v>
+        <v>92.51807403564453</v>
       </c>
       <c r="D839" t="n">
-        <v>92.51806640625</v>
+        <v>92.51807403564453</v>
       </c>
       <c r="E839" t="n">
-        <v>92.51806640625</v>
+        <v>92.51807403564453</v>
       </c>
       <c r="F839" t="n">
         <v>36</v>
@@ -17352,16 +17352,16 @@
         <v>41219</v>
       </c>
       <c r="B847" t="n">
-        <v>84.33966064453125</v>
+        <v>84.33966827392578</v>
       </c>
       <c r="C847" t="n">
-        <v>84.33966064453125</v>
+        <v>84.33966827392578</v>
       </c>
       <c r="D847" t="n">
-        <v>84.33966064453125</v>
+        <v>84.33966827392578</v>
       </c>
       <c r="E847" t="n">
-        <v>84.33966064453125</v>
+        <v>84.33966827392578</v>
       </c>
       <c r="F847" t="n">
         <v>219</v>
@@ -17372,16 +17372,16 @@
         <v>41227</v>
       </c>
       <c r="B848" t="n">
-        <v>91.49575042724609</v>
+        <v>91.49575805664062</v>
       </c>
       <c r="C848" t="n">
-        <v>91.49575042724609</v>
+        <v>91.49575805664062</v>
       </c>
       <c r="D848" t="n">
-        <v>91.49575042724609</v>
+        <v>91.49575805664062</v>
       </c>
       <c r="E848" t="n">
-        <v>91.49575042724609</v>
+        <v>91.49575805664062</v>
       </c>
       <c r="F848" t="n">
         <v>18</v>
@@ -17652,16 +17652,16 @@
         <v>41331</v>
       </c>
       <c r="B862" t="n">
-        <v>114.7530517578125</v>
+        <v>114.753059387207</v>
       </c>
       <c r="C862" t="n">
-        <v>114.7530517578125</v>
+        <v>114.753059387207</v>
       </c>
       <c r="D862" t="n">
-        <v>114.7530517578125</v>
+        <v>114.753059387207</v>
       </c>
       <c r="E862" t="n">
-        <v>114.7530517578125</v>
+        <v>114.753059387207</v>
       </c>
       <c r="F862" t="n">
         <v>201</v>
@@ -17792,16 +17792,16 @@
         <v>41367</v>
       </c>
       <c r="B869" t="n">
-        <v>120.1201400756836</v>
+        <v>120.1201477050781</v>
       </c>
       <c r="C869" t="n">
-        <v>120.1201400756836</v>
+        <v>120.1201477050781</v>
       </c>
       <c r="D869" t="n">
-        <v>120.1201400756836</v>
+        <v>120.1201477050781</v>
       </c>
       <c r="E869" t="n">
-        <v>120.1201400756836</v>
+        <v>120.1201477050781</v>
       </c>
       <c r="F869" t="n">
         <v>9253</v>
@@ -17852,16 +17852,16 @@
         <v>41407</v>
       </c>
       <c r="B872" t="n">
-        <v>127.8664779663086</v>
+        <v>127.8664627075195</v>
       </c>
       <c r="C872" t="n">
-        <v>127.8664779663086</v>
+        <v>127.8664627075195</v>
       </c>
       <c r="D872" t="n">
-        <v>127.8664779663086</v>
+        <v>127.8664627075195</v>
       </c>
       <c r="E872" t="n">
-        <v>127.8664779663086</v>
+        <v>127.8664627075195</v>
       </c>
       <c r="F872" t="n">
         <v>73</v>
@@ -17872,16 +17872,16 @@
         <v>41408</v>
       </c>
       <c r="B873" t="n">
-        <v>138.0957641601562</v>
+        <v>138.0957794189453</v>
       </c>
       <c r="C873" t="n">
-        <v>138.0957641601562</v>
+        <v>138.0957794189453</v>
       </c>
       <c r="D873" t="n">
-        <v>138.0957641601562</v>
+        <v>138.0957794189453</v>
       </c>
       <c r="E873" t="n">
-        <v>138.0957641601562</v>
+        <v>138.0957794189453</v>
       </c>
       <c r="F873" t="n">
         <v>1517</v>
@@ -17912,16 +17912,16 @@
         <v>41430</v>
       </c>
       <c r="B875" t="n">
-        <v>127.8664779663086</v>
+        <v>127.8664627075195</v>
       </c>
       <c r="C875" t="n">
-        <v>127.8664779663086</v>
+        <v>127.8664627075195</v>
       </c>
       <c r="D875" t="n">
-        <v>127.8664779663086</v>
+        <v>127.8664627075195</v>
       </c>
       <c r="E875" t="n">
-        <v>127.8664779663086</v>
+        <v>127.8664627075195</v>
       </c>
       <c r="F875" t="n">
         <v>91</v>
@@ -17932,16 +17932,16 @@
         <v>41435</v>
       </c>
       <c r="B876" t="n">
-        <v>128.3779296875</v>
+        <v>128.3779449462891</v>
       </c>
       <c r="C876" t="n">
-        <v>128.3779296875</v>
+        <v>128.3779449462891</v>
       </c>
       <c r="D876" t="n">
-        <v>128.3779296875</v>
+        <v>128.3779449462891</v>
       </c>
       <c r="E876" t="n">
-        <v>128.3779296875</v>
+        <v>128.3779449462891</v>
       </c>
       <c r="F876" t="n">
         <v>18</v>
@@ -17952,16 +17952,16 @@
         <v>41450</v>
       </c>
       <c r="B877" t="n">
-        <v>128.3779296875</v>
+        <v>128.3779449462891</v>
       </c>
       <c r="C877" t="n">
-        <v>128.3779296875</v>
+        <v>128.3779449462891</v>
       </c>
       <c r="D877" t="n">
-        <v>128.3779296875</v>
+        <v>128.3779449462891</v>
       </c>
       <c r="E877" t="n">
-        <v>128.3779296875</v>
+        <v>128.3779449462891</v>
       </c>
       <c r="F877" t="n">
         <v>786</v>
@@ -18112,16 +18112,16 @@
         <v>41478</v>
       </c>
       <c r="B885" t="n">
-        <v>111.9087295532227</v>
+        <v>111.9087371826172</v>
       </c>
       <c r="C885" t="n">
-        <v>111.9087295532227</v>
+        <v>111.9087371826172</v>
       </c>
       <c r="D885" t="n">
-        <v>111.9087295532227</v>
+        <v>111.9087371826172</v>
       </c>
       <c r="E885" t="n">
-        <v>111.9087295532227</v>
+        <v>111.9087371826172</v>
       </c>
       <c r="F885" t="n">
         <v>329</v>
@@ -18172,16 +18172,16 @@
         <v>41485</v>
       </c>
       <c r="B888" t="n">
-        <v>117.9440307617188</v>
+        <v>117.9440231323242</v>
       </c>
       <c r="C888" t="n">
-        <v>117.9440307617188</v>
+        <v>117.9440231323242</v>
       </c>
       <c r="D888" t="n">
-        <v>117.9440307617188</v>
+        <v>117.9440231323242</v>
       </c>
       <c r="E888" t="n">
-        <v>117.9440307617188</v>
+        <v>117.9440231323242</v>
       </c>
       <c r="F888" t="n">
         <v>402</v>
@@ -18192,16 +18192,16 @@
         <v>41486</v>
       </c>
       <c r="B889" t="n">
-        <v>118.1997604370117</v>
+        <v>118.1997680664062</v>
       </c>
       <c r="C889" t="n">
-        <v>118.1997604370117</v>
+        <v>118.1997680664062</v>
       </c>
       <c r="D889" t="n">
-        <v>117.8928829152673</v>
+        <v>117.8928905248539</v>
       </c>
       <c r="E889" t="n">
-        <v>117.8928829152673</v>
+        <v>117.8928905248539</v>
       </c>
       <c r="F889" t="n">
         <v>420</v>
@@ -18252,16 +18252,16 @@
         <v>41521</v>
       </c>
       <c r="B892" t="n">
-        <v>127.8664779663086</v>
+        <v>127.8664627075195</v>
       </c>
       <c r="C892" t="n">
-        <v>127.8664779663086</v>
+        <v>127.8664627075195</v>
       </c>
       <c r="D892" t="n">
-        <v>122.7518188476563</v>
+        <v>122.7518041992188</v>
       </c>
       <c r="E892" t="n">
-        <v>122.7518188476563</v>
+        <v>122.7518041992188</v>
       </c>
       <c r="F892" t="n">
         <v>256</v>
@@ -18272,16 +18272,16 @@
         <v>41527</v>
       </c>
       <c r="B893" t="n">
-        <v>127.8664779663086</v>
+        <v>127.8664627075195</v>
       </c>
       <c r="C893" t="n">
-        <v>127.8664779663086</v>
+        <v>127.8664627075195</v>
       </c>
       <c r="D893" t="n">
-        <v>127.8664779663086</v>
+        <v>127.8664627075195</v>
       </c>
       <c r="E893" t="n">
-        <v>127.8664779663086</v>
+        <v>127.8664627075195</v>
       </c>
       <c r="F893" t="n">
         <v>201</v>
@@ -18332,16 +18332,16 @@
         <v>41557</v>
       </c>
       <c r="B896" t="n">
-        <v>134.1823883056641</v>
+        <v>134.1824035644531</v>
       </c>
       <c r="C896" t="n">
-        <v>134.1823883056641</v>
+        <v>134.1824035644531</v>
       </c>
       <c r="D896" t="n">
-        <v>134.1823883056641</v>
+        <v>134.1824035644531</v>
       </c>
       <c r="E896" t="n">
-        <v>134.1823883056641</v>
+        <v>134.1824035644531</v>
       </c>
       <c r="F896" t="n">
         <v>182</v>
@@ -18372,16 +18372,16 @@
         <v>41568</v>
       </c>
       <c r="B898" t="n">
-        <v>147.0744476318359</v>
+        <v>147.0744323730469</v>
       </c>
       <c r="C898" t="n">
-        <v>147.0744476318359</v>
+        <v>147.0744323730469</v>
       </c>
       <c r="D898" t="n">
-        <v>147.0744476318359</v>
+        <v>147.0744323730469</v>
       </c>
       <c r="E898" t="n">
-        <v>147.0744476318359</v>
+        <v>147.0744323730469</v>
       </c>
       <c r="F898" t="n">
         <v>256</v>
@@ -18412,16 +18412,16 @@
         <v>41578</v>
       </c>
       <c r="B900" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="C900" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="D900" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="E900" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="F900" t="n">
         <v>457</v>
@@ -18432,16 +18432,16 @@
         <v>41579</v>
       </c>
       <c r="B901" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="C901" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="D901" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="E901" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="F901" t="n">
         <v>475</v>
@@ -18452,16 +18452,16 @@
         <v>41583</v>
       </c>
       <c r="B902" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="C902" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="D902" t="n">
-        <v>157.8090082045118</v>
+        <v>157.8090234582141</v>
       </c>
       <c r="E902" t="n">
-        <v>157.8090082045118</v>
+        <v>157.8090234582141</v>
       </c>
       <c r="F902" t="n">
         <v>91</v>
@@ -18512,16 +18512,16 @@
         <v>41589</v>
       </c>
       <c r="B905" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="C905" t="n">
-        <v>163.1236877441406</v>
+        <v>163.123703511556</v>
       </c>
       <c r="D905" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="E905" t="n">
-        <v>163.1236877441406</v>
+        <v>163.123703511556</v>
       </c>
       <c r="F905" t="n">
         <v>182</v>
@@ -18532,16 +18532,16 @@
         <v>41592</v>
       </c>
       <c r="B906" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="C906" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="D906" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="E906" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="F906" t="n">
         <v>292</v>
@@ -18672,16 +18672,16 @@
         <v>41621</v>
       </c>
       <c r="B913" t="n">
-        <v>200.1685638427734</v>
+        <v>200.1685791015625</v>
       </c>
       <c r="C913" t="n">
-        <v>200.1685638427734</v>
+        <v>200.1685791015625</v>
       </c>
       <c r="D913" t="n">
-        <v>199.9580781312647</v>
+        <v>199.9580933740085</v>
       </c>
       <c r="E913" t="n">
-        <v>199.9580781312647</v>
+        <v>199.9580933740085</v>
       </c>
       <c r="F913" t="n">
         <v>86</v>
@@ -18732,16 +18732,16 @@
         <v>41631</v>
       </c>
       <c r="B916" t="n">
-        <v>158.0721282958984</v>
+        <v>158.0721130371094</v>
       </c>
       <c r="C916" t="n">
-        <v>172.5953929527522</v>
+        <v>172.5953762920244</v>
       </c>
       <c r="D916" t="n">
-        <v>158.0721282958984</v>
+        <v>158.0721130371094</v>
       </c>
       <c r="E916" t="n">
-        <v>172.5953929527522</v>
+        <v>172.5953762920244</v>
       </c>
       <c r="F916" t="n">
         <v>132</v>
@@ -18792,16 +18792,16 @@
         <v>41663</v>
       </c>
       <c r="B919" t="n">
-        <v>131.7618713378906</v>
+        <v>131.7618560791016</v>
       </c>
       <c r="C919" t="n">
-        <v>147.3375518685648</v>
+        <v>147.3375348060216</v>
       </c>
       <c r="D919" t="n">
-        <v>131.7618713378906</v>
+        <v>131.7618560791016</v>
       </c>
       <c r="E919" t="n">
-        <v>147.3375518685648</v>
+        <v>147.3375348060216</v>
       </c>
       <c r="F919" t="n">
         <v>210</v>
@@ -18892,16 +18892,16 @@
         <v>41683</v>
       </c>
       <c r="B924" t="n">
-        <v>133.6561889648438</v>
+        <v>133.6562042236328</v>
       </c>
       <c r="C924" t="n">
-        <v>156.8092197454936</v>
+        <v>156.8092376475363</v>
       </c>
       <c r="D924" t="n">
-        <v>133.6561889648438</v>
+        <v>133.6562042236328</v>
       </c>
       <c r="E924" t="n">
-        <v>147.3375246678031</v>
+        <v>147.3375414885147</v>
       </c>
       <c r="F924" t="n">
         <v>45</v>
@@ -19052,16 +19052,16 @@
         <v>41712</v>
       </c>
       <c r="B932" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="C932" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="D932" t="n">
-        <v>115.7651977539062</v>
+        <v>115.7652089436849</v>
       </c>
       <c r="E932" t="n">
-        <v>115.7651977539062</v>
+        <v>115.7652089436849</v>
       </c>
       <c r="F932" t="n">
         <v>91</v>
@@ -19072,16 +19072,16 @@
         <v>41715</v>
       </c>
       <c r="B933" t="n">
-        <v>148.3899230957031</v>
+        <v>148.3899383544922</v>
       </c>
       <c r="C933" t="n">
-        <v>148.3899230957031</v>
+        <v>148.3899383544922</v>
       </c>
       <c r="D933" t="n">
-        <v>148.3899230957031</v>
+        <v>148.3899383544922</v>
       </c>
       <c r="E933" t="n">
-        <v>148.3899230957031</v>
+        <v>148.3899383544922</v>
       </c>
       <c r="F933" t="n">
         <v>9</v>
@@ -19092,16 +19092,16 @@
         <v>41719</v>
       </c>
       <c r="B934" t="n">
-        <v>136.8134155273438</v>
+        <v>136.8134307861328</v>
       </c>
       <c r="C934" t="n">
-        <v>137.0239012290801</v>
+        <v>137.0239165113446</v>
       </c>
       <c r="D934" t="n">
-        <v>136.8134155273438</v>
+        <v>136.8134307861328</v>
       </c>
       <c r="E934" t="n">
-        <v>137.0239012290801</v>
+        <v>137.0239165113446</v>
       </c>
       <c r="F934" t="n">
         <v>18</v>
@@ -19152,16 +19152,16 @@
         <v>41726</v>
       </c>
       <c r="B937" t="n">
-        <v>139.5496978759766</v>
+        <v>139.5496826171875</v>
       </c>
       <c r="C937" t="n">
-        <v>139.5496978759766</v>
+        <v>139.5496826171875</v>
       </c>
       <c r="D937" t="n">
-        <v>139.3392121557239</v>
+        <v>139.33919691995</v>
       </c>
       <c r="E937" t="n">
-        <v>139.3392121557239</v>
+        <v>139.33919691995</v>
       </c>
       <c r="F937" t="n">
         <v>214</v>
@@ -19192,16 +19192,16 @@
         <v>41736</v>
       </c>
       <c r="B939" t="n">
-        <v>151.5471801757812</v>
+        <v>151.5471649169922</v>
       </c>
       <c r="C939" t="n">
-        <v>151.5471801757812</v>
+        <v>151.5471649169922</v>
       </c>
       <c r="D939" t="n">
-        <v>151.5471801757812</v>
+        <v>151.5471649169922</v>
       </c>
       <c r="E939" t="n">
-        <v>151.5471801757812</v>
+        <v>151.5471649169922</v>
       </c>
       <c r="F939" t="n">
         <v>50</v>
@@ -19252,16 +19252,16 @@
         <v>41754</v>
       </c>
       <c r="B942" t="n">
-        <v>147.1270294189453</v>
+        <v>147.1270446777344</v>
       </c>
       <c r="C942" t="n">
-        <v>147.1270294189453</v>
+        <v>147.1270446777344</v>
       </c>
       <c r="D942" t="n">
-        <v>147.1270294189453</v>
+        <v>147.1270446777344</v>
       </c>
       <c r="E942" t="n">
-        <v>147.1270294189453</v>
+        <v>147.1270446777344</v>
       </c>
       <c r="F942" t="n">
         <v>18</v>
@@ -19272,16 +19272,16 @@
         <v>41758</v>
       </c>
       <c r="B943" t="n">
-        <v>159.9664611816406</v>
+        <v>159.9664459228516</v>
       </c>
       <c r="C943" t="n">
-        <v>160.1769322003382</v>
+        <v>160.1769169214729</v>
       </c>
       <c r="D943" t="n">
-        <v>151.9681366542244</v>
+        <v>151.968122158375</v>
       </c>
       <c r="E943" t="n">
-        <v>151.9681366542244</v>
+        <v>151.968122158375</v>
       </c>
       <c r="F943" t="n">
         <v>54</v>
@@ -19292,16 +19292,16 @@
         <v>41766</v>
       </c>
       <c r="B944" t="n">
-        <v>159.9664611816406</v>
+        <v>159.9664459228516</v>
       </c>
       <c r="C944" t="n">
-        <v>159.9664611816406</v>
+        <v>159.9664459228516</v>
       </c>
       <c r="D944" t="n">
-        <v>159.9664611816406</v>
+        <v>159.9664459228516</v>
       </c>
       <c r="E944" t="n">
-        <v>159.9664611816406</v>
+        <v>159.9664459228516</v>
       </c>
       <c r="F944" t="n">
         <v>9</v>
@@ -19332,16 +19332,16 @@
         <v>41772</v>
       </c>
       <c r="B946" t="n">
-        <v>158.2826080322266</v>
+        <v>158.2825927734375</v>
       </c>
       <c r="C946" t="n">
-        <v>166.2809180329608</v>
+        <v>166.2809020031171</v>
       </c>
       <c r="D946" t="n">
-        <v>157.8616366199027</v>
+        <v>157.8616214016962</v>
       </c>
       <c r="E946" t="n">
-        <v>157.8616366199027</v>
+        <v>157.8616214016962</v>
       </c>
       <c r="F946" t="n">
         <v>315</v>
@@ -19492,16 +19492,16 @@
         <v>41793</v>
       </c>
       <c r="B954" t="n">
-        <v>158.0721282958984</v>
+        <v>158.0721130371094</v>
       </c>
       <c r="C954" t="n">
-        <v>158.0721282958984</v>
+        <v>158.0721130371094</v>
       </c>
       <c r="D954" t="n">
-        <v>158.0721282958984</v>
+        <v>158.0721130371094</v>
       </c>
       <c r="E954" t="n">
-        <v>158.0721282958984</v>
+        <v>158.0721130371094</v>
       </c>
       <c r="F954" t="n">
         <v>18</v>
@@ -19592,16 +19592,16 @@
         <v>41814</v>
       </c>
       <c r="B959" t="n">
-        <v>177.8574523925781</v>
+        <v>177.8574371337891</v>
       </c>
       <c r="C959" t="n">
-        <v>177.8574523925781</v>
+        <v>177.8574371337891</v>
       </c>
       <c r="D959" t="n">
-        <v>177.8574523925781</v>
+        <v>177.8574371337891</v>
       </c>
       <c r="E959" t="n">
-        <v>177.8574523925781</v>
+        <v>177.8574371337891</v>
       </c>
       <c r="F959" t="n">
         <v>50</v>
@@ -19612,16 +19612,16 @@
         <v>41820</v>
       </c>
       <c r="B960" t="n">
-        <v>151.7576446533203</v>
+        <v>151.7576599121094</v>
       </c>
       <c r="C960" t="n">
-        <v>156.177770795974</v>
+        <v>156.1777864991938</v>
       </c>
       <c r="D960" t="n">
-        <v>137.0238957389219</v>
+        <v>137.0239095162754</v>
       </c>
       <c r="E960" t="n">
-        <v>137.0238957389219</v>
+        <v>137.0239095162754</v>
       </c>
       <c r="F960" t="n">
         <v>27</v>
@@ -19632,16 +19632,16 @@
         <v>41821</v>
       </c>
       <c r="B961" t="n">
-        <v>159.9664611816406</v>
+        <v>159.9664459228516</v>
       </c>
       <c r="C961" t="n">
-        <v>163.9656161036779</v>
+        <v>163.9656004634198</v>
       </c>
       <c r="D961" t="n">
-        <v>159.9664611816406</v>
+        <v>159.9664459228516</v>
       </c>
       <c r="E961" t="n">
-        <v>159.9664611816406</v>
+        <v>159.9664459228516</v>
       </c>
       <c r="F961" t="n">
         <v>201</v>
@@ -19652,16 +19652,16 @@
         <v>41824</v>
       </c>
       <c r="B962" t="n">
-        <v>159.9664611816406</v>
+        <v>159.9664459228516</v>
       </c>
       <c r="C962" t="n">
-        <v>159.9664611816406</v>
+        <v>159.9664459228516</v>
       </c>
       <c r="D962" t="n">
-        <v>159.9664611816406</v>
+        <v>159.9664459228516</v>
       </c>
       <c r="E962" t="n">
-        <v>159.9664611816406</v>
+        <v>159.9664459228516</v>
       </c>
       <c r="F962" t="n">
         <v>4</v>
@@ -19672,16 +19672,16 @@
         <v>41830</v>
       </c>
       <c r="B963" t="n">
-        <v>159.5454864501953</v>
+        <v>159.5454711914062</v>
       </c>
       <c r="C963" t="n">
-        <v>159.5454864501953</v>
+        <v>159.5454711914062</v>
       </c>
       <c r="D963" t="n">
-        <v>159.5454864501953</v>
+        <v>159.5454711914062</v>
       </c>
       <c r="E963" t="n">
-        <v>159.5454864501953</v>
+        <v>159.5454711914062</v>
       </c>
       <c r="F963" t="n">
         <v>45</v>
@@ -19692,16 +19692,16 @@
         <v>41831</v>
       </c>
       <c r="B964" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="C964" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="D964" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="E964" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="F964" t="n">
         <v>278</v>
@@ -19732,16 +19732,16 @@
         <v>41841</v>
       </c>
       <c r="B966" t="n">
-        <v>158.9140319824219</v>
+        <v>158.9140472412109</v>
       </c>
       <c r="C966" t="n">
-        <v>158.9140319824219</v>
+        <v>158.9140472412109</v>
       </c>
       <c r="D966" t="n">
-        <v>158.9140319824219</v>
+        <v>158.9140472412109</v>
       </c>
       <c r="E966" t="n">
-        <v>158.9140319824219</v>
+        <v>158.9140472412109</v>
       </c>
       <c r="F966" t="n">
         <v>4</v>
@@ -19772,16 +19772,16 @@
         <v>41843</v>
       </c>
       <c r="B968" t="n">
-        <v>159.9664611816406</v>
+        <v>159.9664459228516</v>
       </c>
       <c r="C968" t="n">
-        <v>178.9098513316558</v>
+        <v>178.9098342659055</v>
       </c>
       <c r="D968" t="n">
-        <v>159.7559754796014</v>
+        <v>159.75596024089</v>
       </c>
       <c r="E968" t="n">
-        <v>159.7559754796014</v>
+        <v>159.75596024089</v>
       </c>
       <c r="F968" t="n">
         <v>210</v>
@@ -19792,16 +19792,16 @@
         <v>41844</v>
       </c>
       <c r="B969" t="n">
-        <v>159.9664611816406</v>
+        <v>159.9664459228516</v>
       </c>
       <c r="C969" t="n">
-        <v>159.9664611816406</v>
+        <v>159.9664459228516</v>
       </c>
       <c r="D969" t="n">
-        <v>159.9664611816406</v>
+        <v>159.9664459228516</v>
       </c>
       <c r="E969" t="n">
-        <v>159.9664611816406</v>
+        <v>159.9664459228516</v>
       </c>
       <c r="F969" t="n">
         <v>36</v>
@@ -19812,16 +19812,16 @@
         <v>41848</v>
       </c>
       <c r="B970" t="n">
-        <v>151.5471801757812</v>
+        <v>151.5471649169922</v>
       </c>
       <c r="C970" t="n">
-        <v>151.5471801757812</v>
+        <v>151.5471649169922</v>
       </c>
       <c r="D970" t="n">
-        <v>151.5471801757812</v>
+        <v>151.5471649169922</v>
       </c>
       <c r="E970" t="n">
-        <v>151.5471801757812</v>
+        <v>151.5471649169922</v>
       </c>
       <c r="F970" t="n">
         <v>4</v>
@@ -19872,16 +19872,16 @@
         <v>41865</v>
       </c>
       <c r="B973" t="n">
-        <v>151.5471801757812</v>
+        <v>151.5471649169922</v>
       </c>
       <c r="C973" t="n">
-        <v>151.5471801757812</v>
+        <v>151.5471649169922</v>
       </c>
       <c r="D973" t="n">
-        <v>151.5471801757812</v>
+        <v>151.5471649169922</v>
       </c>
       <c r="E973" t="n">
-        <v>151.5471801757812</v>
+        <v>151.5471649169922</v>
       </c>
       <c r="F973" t="n">
         <v>27</v>
@@ -19912,16 +19912,16 @@
         <v>41877</v>
       </c>
       <c r="B975" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="C975" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="D975" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="E975" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="F975" t="n">
         <v>18</v>
@@ -20012,16 +20012,16 @@
         <v>41908</v>
       </c>
       <c r="B980" t="n">
-        <v>147.3375244140625</v>
+        <v>147.3375396728516</v>
       </c>
       <c r="C980" t="n">
-        <v>151.5471650320817</v>
+        <v>151.5471807268358</v>
       </c>
       <c r="D980" t="n">
-        <v>147.3375244140625</v>
+        <v>147.3375396728516</v>
       </c>
       <c r="E980" t="n">
-        <v>151.5471650320817</v>
+        <v>151.5471807268358</v>
       </c>
       <c r="F980" t="n">
         <v>54</v>
@@ -20032,16 +20032,16 @@
         <v>41948</v>
       </c>
       <c r="B981" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="C981" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="D981" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="E981" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="F981" t="n">
         <v>13</v>
@@ -20052,16 +20052,16 @@
         <v>41964</v>
       </c>
       <c r="B982" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="C982" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="D982" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="E982" t="n">
-        <v>157.8616333007812</v>
+        <v>157.8616485595703</v>
       </c>
       <c r="F982" t="n">
         <v>4</v>
@@ -20072,16 +20072,16 @@
         <v>41982</v>
       </c>
       <c r="B983" t="n">
-        <v>147.3375244140625</v>
+        <v>147.3375396728516</v>
       </c>
       <c r="C983" t="n">
-        <v>147.3375244140625</v>
+        <v>147.3375396728516</v>
       </c>
       <c r="D983" t="n">
-        <v>147.3375244140625</v>
+        <v>147.3375396728516</v>
       </c>
       <c r="E983" t="n">
-        <v>147.3375244140625</v>
+        <v>147.3375396728516</v>
       </c>
       <c r="F983" t="n">
         <v>4</v>
@@ -20092,16 +20092,16 @@
         <v>41983</v>
       </c>
       <c r="B984" t="n">
-        <v>136.8134155273438</v>
+        <v>136.8134307861328</v>
       </c>
       <c r="C984" t="n">
-        <v>136.8134155273438</v>
+        <v>136.8134307861328</v>
       </c>
       <c r="D984" t="n">
-        <v>128.8150910114365</v>
+        <v>128.8151053781731</v>
       </c>
       <c r="E984" t="n">
-        <v>128.8150910114365</v>
+        <v>128.8151053781731</v>
       </c>
       <c r="F984" t="n">
         <v>18</v>
@@ -20132,16 +20132,16 @@
         <v>41999</v>
       </c>
       <c r="B986" t="n">
-        <v>143.1278991699219</v>
+        <v>143.1278839111328</v>
       </c>
       <c r="C986" t="n">
-        <v>143.1278991699219</v>
+        <v>143.1278839111328</v>
       </c>
       <c r="D986" t="n">
-        <v>143.1278991699219</v>
+        <v>143.1278839111328</v>
       </c>
       <c r="E986" t="n">
-        <v>143.1278991699219</v>
+        <v>143.1278839111328</v>
       </c>
       <c r="F986" t="n">
         <v>4</v>
@@ -20172,16 +20172,16 @@
         <v>42017</v>
       </c>
       <c r="B988" t="n">
-        <v>155.3358459472656</v>
+        <v>155.3358612060547</v>
       </c>
       <c r="C988" t="n">
-        <v>155.3358459472656</v>
+        <v>155.3358612060547</v>
       </c>
       <c r="D988" t="n">
-        <v>155.3358459472656</v>
+        <v>155.3358612060547</v>
       </c>
       <c r="E988" t="n">
-        <v>155.3358459472656</v>
+        <v>155.3358612060547</v>
       </c>
       <c r="F988" t="n">
         <v>50</v>
@@ -20292,16 +20292,16 @@
         <v>42139</v>
       </c>
       <c r="B994" t="n">
-        <v>119.6006469726562</v>
+        <v>119.6006546020508</v>
       </c>
       <c r="C994" t="n">
-        <v>119.6006469726562</v>
+        <v>119.6006546020508</v>
       </c>
       <c r="D994" t="n">
-        <v>119.6006469726562</v>
+        <v>119.6006546020508</v>
       </c>
       <c r="E994" t="n">
-        <v>119.6006469726562</v>
+        <v>119.6006546020508</v>
       </c>
       <c r="F994" t="n">
         <v>4</v>
@@ -20312,16 +20312,16 @@
         <v>42145</v>
       </c>
       <c r="B995" t="n">
-        <v>125.9068603515625</v>
+        <v>125.906867980957</v>
       </c>
       <c r="C995" t="n">
-        <v>125.9068603515625</v>
+        <v>125.906867980957</v>
       </c>
       <c r="D995" t="n">
-        <v>117.4260894574169</v>
+        <v>117.4260965729145</v>
       </c>
       <c r="E995" t="n">
-        <v>122.8624824176222</v>
+        <v>122.862489862541</v>
       </c>
       <c r="F995" t="n">
         <v>310</v>
@@ -20332,16 +20332,16 @@
         <v>42146</v>
       </c>
       <c r="B996" t="n">
-        <v>126.1243286132812</v>
+        <v>126.1243209838867</v>
       </c>
       <c r="C996" t="n">
-        <v>130.4734402544661</v>
+        <v>130.4734323619891</v>
       </c>
       <c r="D996" t="n">
-        <v>121.7752093871863</v>
+        <v>121.7752020208746</v>
       </c>
       <c r="E996" t="n">
-        <v>121.7752093871863</v>
+        <v>121.7752020208746</v>
       </c>
       <c r="F996" t="n">
         <v>114</v>
@@ -20392,16 +20392,16 @@
         <v>42165</v>
       </c>
       <c r="B999" t="n">
-        <v>140.2589569091797</v>
+        <v>140.2589416503906</v>
       </c>
       <c r="C999" t="n">
-        <v>140.2589569091797</v>
+        <v>140.2589416503906</v>
       </c>
       <c r="D999" t="n">
-        <v>140.2589569091797</v>
+        <v>140.2589416503906</v>
       </c>
       <c r="E999" t="n">
-        <v>140.2589569091797</v>
+        <v>140.2589416503906</v>
       </c>
       <c r="F999" t="n">
         <v>4</v>
@@ -20412,16 +20412,16 @@
         <v>42172</v>
       </c>
       <c r="B1000" t="n">
-        <v>152.2190093994141</v>
+        <v>152.2190246582031</v>
       </c>
       <c r="C1000" t="n">
-        <v>152.2190093994141</v>
+        <v>152.2190246582031</v>
       </c>
       <c r="D1000" t="n">
-        <v>141.3462230137416</v>
+        <v>141.3462371826172</v>
       </c>
       <c r="E1000" t="n">
-        <v>141.3462230137416</v>
+        <v>141.3462371826172</v>
       </c>
       <c r="F1000" t="n">
         <v>18</v>
@@ -20432,16 +20432,16 @@
         <v>42184</v>
       </c>
       <c r="B1001" t="n">
-        <v>149.6095428466797</v>
+        <v>149.6095275878906</v>
       </c>
       <c r="C1001" t="n">
-        <v>149.6095428466797</v>
+        <v>149.6095275878906</v>
       </c>
       <c r="D1001" t="n">
-        <v>149.6095428466797</v>
+        <v>149.6095275878906</v>
       </c>
       <c r="E1001" t="n">
-        <v>149.6095428466797</v>
+        <v>149.6095275878906</v>
       </c>
       <c r="F1001" t="n">
         <v>772</v>
@@ -20492,16 +20492,16 @@
         <v>42220</v>
       </c>
       <c r="B1004" t="n">
-        <v>167.2234497070312</v>
+        <v>167.2234649658203</v>
       </c>
       <c r="C1004" t="n">
-        <v>167.2234497070312</v>
+        <v>167.2234649658203</v>
       </c>
       <c r="D1004" t="n">
-        <v>167.2234497070312</v>
+        <v>167.2234649658203</v>
       </c>
       <c r="E1004" t="n">
-        <v>167.2234497070312</v>
+        <v>167.2234649658203</v>
       </c>
       <c r="F1004" t="n">
         <v>22</v>
@@ -20532,16 +20532,16 @@
         <v>42228</v>
       </c>
       <c r="B1006" t="n">
-        <v>166.3536376953125</v>
+        <v>166.3536224365234</v>
       </c>
       <c r="C1006" t="n">
-        <v>167.4409194466835</v>
+        <v>167.4409040881635</v>
       </c>
       <c r="D1006" t="n">
-        <v>166.3536376953125</v>
+        <v>166.3536224365234</v>
       </c>
       <c r="E1006" t="n">
-        <v>167.4409194466835</v>
+        <v>167.4409040881635</v>
       </c>
       <c r="F1006" t="n">
         <v>571</v>
@@ -20592,16 +20592,16 @@
         <v>42240</v>
       </c>
       <c r="B1009" t="n">
-        <v>165.266357421875</v>
+        <v>165.2663421630859</v>
       </c>
       <c r="C1009" t="n">
-        <v>167.4409055746403</v>
+        <v>167.4408901150786</v>
       </c>
       <c r="D1009" t="n">
-        <v>165.266357421875</v>
+        <v>165.2663421630859</v>
       </c>
       <c r="E1009" t="n">
-        <v>167.4409055746403</v>
+        <v>167.4408901150786</v>
       </c>
       <c r="F1009" t="n">
         <v>22</v>
@@ -20612,16 +20612,16 @@
         <v>42241</v>
       </c>
       <c r="B1010" t="n">
-        <v>165.266357421875</v>
+        <v>165.2663421630859</v>
       </c>
       <c r="C1010" t="n">
-        <v>165.266357421875</v>
+        <v>165.2663421630859</v>
       </c>
       <c r="D1010" t="n">
-        <v>165.266357421875</v>
+        <v>165.2663421630859</v>
       </c>
       <c r="E1010" t="n">
-        <v>165.266357421875</v>
+        <v>165.2663421630859</v>
       </c>
       <c r="F1010" t="n">
         <v>45</v>
@@ -20712,16 +20712,16 @@
         <v>42257</v>
       </c>
       <c r="B1015" t="n">
-        <v>96.98526000976562</v>
+        <v>96.98525238037109</v>
       </c>
       <c r="C1015" t="n">
-        <v>96.98526000976562</v>
+        <v>96.98525238037109</v>
       </c>
       <c r="D1015" t="n">
-        <v>96.76780821534732</v>
+        <v>96.76780060305873</v>
       </c>
       <c r="E1015" t="n">
-        <v>96.76780821534732</v>
+        <v>96.76780060305873</v>
       </c>
       <c r="F1015" t="n">
         <v>18</v>
@@ -20732,16 +20732,16 @@
         <v>42258</v>
       </c>
       <c r="B1016" t="n">
-        <v>76.10950469970703</v>
+        <v>76.10951232910156</v>
       </c>
       <c r="C1016" t="n">
-        <v>97.8550774710519</v>
+        <v>97.85508728027344</v>
       </c>
       <c r="D1016" t="n">
-        <v>76.10950469970703</v>
+        <v>76.10951232910156</v>
       </c>
       <c r="E1016" t="n">
-        <v>97.8550774710519</v>
+        <v>97.85508728027344</v>
       </c>
       <c r="F1016" t="n">
         <v>448</v>
@@ -20752,16 +20752,16 @@
         <v>42261</v>
       </c>
       <c r="B1017" t="n">
-        <v>76.10950469970703</v>
+        <v>76.10951232910156</v>
       </c>
       <c r="C1017" t="n">
-        <v>76.10950469970703</v>
+        <v>76.10951232910156</v>
       </c>
       <c r="D1017" t="n">
-        <v>76.10950469970703</v>
+        <v>76.10951232910156</v>
       </c>
       <c r="E1017" t="n">
-        <v>76.10950469970703</v>
+        <v>76.10951232910156</v>
       </c>
       <c r="F1017" t="n">
         <v>18</v>
@@ -20852,16 +20852,16 @@
         <v>42269</v>
       </c>
       <c r="B1022" t="n">
-        <v>59.14795684814453</v>
+        <v>59.1479606628418</v>
       </c>
       <c r="C1022" t="n">
-        <v>59.14795684814453</v>
+        <v>59.1479606628418</v>
       </c>
       <c r="D1022" t="n">
-        <v>52.1893748049672</v>
+        <v>52.18937817087662</v>
       </c>
       <c r="E1022" t="n">
-        <v>58.71304570747438</v>
+        <v>58.71304949412242</v>
       </c>
       <c r="F1022" t="n">
         <v>470</v>
@@ -20912,16 +20912,16 @@
         <v>42276</v>
       </c>
       <c r="B1025" t="n">
-        <v>59.14795684814453</v>
+        <v>59.1479606628418</v>
       </c>
       <c r="C1025" t="n">
-        <v>59.14795684814453</v>
+        <v>59.1479606628418</v>
       </c>
       <c r="D1025" t="n">
-        <v>53.27665265664258</v>
+        <v>53.27665609267507</v>
       </c>
       <c r="E1025" t="n">
-        <v>53.27665265664258</v>
+        <v>53.27665609267507</v>
       </c>
       <c r="F1025" t="n">
         <v>489</v>
@@ -20932,16 +20932,16 @@
         <v>42278</v>
       </c>
       <c r="B1026" t="n">
-        <v>61.32251739501953</v>
+        <v>61.32251358032227</v>
       </c>
       <c r="C1026" t="n">
-        <v>61.32251739501953</v>
+        <v>61.32251358032227</v>
       </c>
       <c r="D1026" t="n">
-        <v>58.71305034489134</v>
+        <v>58.71304669252151</v>
       </c>
       <c r="E1026" t="n">
-        <v>58.71305034489134</v>
+        <v>58.71304669252151</v>
       </c>
       <c r="F1026" t="n">
         <v>173</v>
@@ -20952,16 +20952,16 @@
         <v>42279</v>
       </c>
       <c r="B1027" t="n">
-        <v>53.49411010742188</v>
+        <v>53.49410629272461</v>
       </c>
       <c r="C1027" t="n">
-        <v>62.62725196745635</v>
+        <v>62.62724750146923</v>
       </c>
       <c r="D1027" t="n">
-        <v>52.40683221752611</v>
+        <v>52.40682848036329</v>
       </c>
       <c r="E1027" t="n">
-        <v>62.62725196745635</v>
+        <v>62.62724750146923</v>
       </c>
       <c r="F1027" t="n">
         <v>365</v>
@@ -21012,16 +21012,16 @@
         <v>42284</v>
       </c>
       <c r="B1030" t="n">
-        <v>75.67459106445312</v>
+        <v>75.67458343505859</v>
       </c>
       <c r="C1030" t="n">
-        <v>75.67459106445312</v>
+        <v>75.67458343505859</v>
       </c>
       <c r="D1030" t="n">
-        <v>65.01926439690007</v>
+        <v>65.019257841759</v>
       </c>
       <c r="E1030" t="n">
-        <v>65.01926439690007</v>
+        <v>65.019257841759</v>
       </c>
       <c r="F1030" t="n">
         <v>374</v>
@@ -21072,16 +21072,16 @@
         <v>42293</v>
       </c>
       <c r="B1033" t="n">
-        <v>66.32400512695312</v>
+        <v>66.32399749755859</v>
       </c>
       <c r="C1033" t="n">
-        <v>66.32400512695312</v>
+        <v>66.32399749755859</v>
       </c>
       <c r="D1033" t="n">
-        <v>66.32400512695312</v>
+        <v>66.32399749755859</v>
       </c>
       <c r="E1033" t="n">
-        <v>66.32400512695312</v>
+        <v>66.32399749755859</v>
       </c>
       <c r="F1033" t="n">
         <v>13</v>
@@ -21112,16 +21112,16 @@
         <v>42305</v>
       </c>
       <c r="B1035" t="n">
-        <v>61.32251739501953</v>
+        <v>61.32251358032227</v>
       </c>
       <c r="C1035" t="n">
-        <v>61.32251739501953</v>
+        <v>61.32251358032227</v>
       </c>
       <c r="D1035" t="n">
-        <v>61.32251739501953</v>
+        <v>61.32251358032227</v>
       </c>
       <c r="E1035" t="n">
-        <v>61.32251739501953</v>
+        <v>61.32251358032227</v>
       </c>
       <c r="F1035" t="n">
         <v>27</v>
@@ -21132,16 +21132,16 @@
         <v>42306</v>
       </c>
       <c r="B1036" t="n">
-        <v>54.14648056030273</v>
+        <v>54.14647674560547</v>
       </c>
       <c r="C1036" t="n">
-        <v>54.14648056030273</v>
+        <v>54.14647674560547</v>
       </c>
       <c r="D1036" t="n">
-        <v>52.1893802240708</v>
+        <v>52.18937654725407</v>
       </c>
       <c r="E1036" t="n">
-        <v>52.1893802240708</v>
+        <v>52.18937654725407</v>
       </c>
       <c r="F1036" t="n">
         <v>64</v>
@@ -21152,16 +21152,16 @@
         <v>42307</v>
       </c>
       <c r="B1037" t="n">
-        <v>63.06216430664062</v>
+        <v>63.06216049194336</v>
       </c>
       <c r="C1037" t="n">
-        <v>65.23672012723303</v>
+        <v>65.23671618099456</v>
       </c>
       <c r="D1037" t="n">
-        <v>58.27813770888226</v>
+        <v>58.27813418357584</v>
       </c>
       <c r="E1037" t="n">
-        <v>60.88760469359314</v>
+        <v>60.88760101043729</v>
       </c>
       <c r="F1037" t="n">
         <v>68</v>
@@ -21192,16 +21192,16 @@
         <v>42312</v>
       </c>
       <c r="B1039" t="n">
-        <v>68.49855041503906</v>
+        <v>68.49855804443359</v>
       </c>
       <c r="C1039" t="n">
-        <v>68.49855041503906</v>
+        <v>68.49855804443359</v>
       </c>
       <c r="D1039" t="n">
-        <v>68.49855041503906</v>
+        <v>68.49855804443359</v>
       </c>
       <c r="E1039" t="n">
-        <v>68.49855041503906</v>
+        <v>68.49855804443359</v>
       </c>
       <c r="F1039" t="n">
         <v>45</v>
@@ -21212,16 +21212,16 @@
         <v>42313</v>
       </c>
       <c r="B1040" t="n">
-        <v>60.01778030395508</v>
+        <v>60.01777648925781</v>
       </c>
       <c r="C1040" t="n">
-        <v>64.80180673739885</v>
+        <v>64.80180261863148</v>
       </c>
       <c r="D1040" t="n">
-        <v>59.80032472936468</v>
+        <v>59.80032092848877</v>
       </c>
       <c r="E1040" t="n">
-        <v>59.80032472936468</v>
+        <v>59.80032092848877</v>
       </c>
       <c r="F1040" t="n">
         <v>73</v>
@@ -21232,16 +21232,16 @@
         <v>42317</v>
       </c>
       <c r="B1041" t="n">
-        <v>59.80032348632812</v>
+        <v>59.80032730102539</v>
       </c>
       <c r="C1041" t="n">
-        <v>59.80032348632812</v>
+        <v>59.80032730102539</v>
       </c>
       <c r="D1041" t="n">
-        <v>59.80032348632812</v>
+        <v>59.80032730102539</v>
       </c>
       <c r="E1041" t="n">
-        <v>59.80032348632812</v>
+        <v>59.80032730102539</v>
       </c>
       <c r="F1041" t="n">
         <v>18</v>
@@ -21252,16 +21252,16 @@
         <v>42318</v>
       </c>
       <c r="B1042" t="n">
-        <v>59.80032348632812</v>
+        <v>59.80032730102539</v>
       </c>
       <c r="C1042" t="n">
-        <v>59.80032348632812</v>
+        <v>59.80032730102539</v>
       </c>
       <c r="D1042" t="n">
-        <v>59.80032348632812</v>
+        <v>59.80032730102539</v>
       </c>
       <c r="E1042" t="n">
-        <v>59.80032348632812</v>
+        <v>59.80032730102539</v>
       </c>
       <c r="F1042" t="n">
         <v>329</v>
@@ -21292,16 +21292,16 @@
         <v>42325</v>
       </c>
       <c r="B1044" t="n">
-        <v>56.53849029541016</v>
+        <v>56.53848648071289</v>
       </c>
       <c r="C1044" t="n">
-        <v>56.53849029541016</v>
+        <v>56.53848648071289</v>
       </c>
       <c r="D1044" t="n">
-        <v>56.53849029541016</v>
+        <v>56.53848648071289</v>
       </c>
       <c r="E1044" t="n">
-        <v>56.53849029541016</v>
+        <v>56.53848648071289</v>
       </c>
       <c r="F1044" t="n">
         <v>128</v>
@@ -21312,16 +21312,16 @@
         <v>42326</v>
       </c>
       <c r="B1045" t="n">
-        <v>63.06216430664062</v>
+        <v>63.06216049194336</v>
       </c>
       <c r="C1045" t="n">
-        <v>63.06216430664062</v>
+        <v>63.06216049194336</v>
       </c>
       <c r="D1045" t="n">
-        <v>58.4955932909415</v>
+        <v>58.49558975248096</v>
       </c>
       <c r="E1045" t="n">
-        <v>58.4955932909415</v>
+        <v>58.49558975248096</v>
       </c>
       <c r="F1045" t="n">
         <v>118</v>
@@ -21372,16 +21372,16 @@
         <v>42338</v>
       </c>
       <c r="B1048" t="n">
-        <v>63.06216430664062</v>
+        <v>63.06216049194336</v>
       </c>
       <c r="C1048" t="n">
-        <v>63.06216430664062</v>
+        <v>63.06216049194336</v>
       </c>
       <c r="D1048" t="n">
-        <v>63.06216430664062</v>
+        <v>63.06216049194336</v>
       </c>
       <c r="E1048" t="n">
-        <v>63.06216430664062</v>
+        <v>63.06216049194336</v>
       </c>
       <c r="F1048" t="n">
         <v>4</v>
@@ -21412,16 +21412,16 @@
         <v>42340</v>
       </c>
       <c r="B1050" t="n">
-        <v>48.49263000488281</v>
+        <v>48.49262619018555</v>
       </c>
       <c r="C1050" t="n">
-        <v>50.66718587361763</v>
+        <v>50.66718188785782</v>
       </c>
       <c r="D1050" t="n">
-        <v>48.49263000488281</v>
+        <v>48.49262619018555</v>
       </c>
       <c r="E1050" t="n">
-        <v>48.49263000488281</v>
+        <v>48.49262619018555</v>
       </c>
       <c r="F1050" t="n">
         <v>2176</v>
@@ -21432,16 +21432,16 @@
         <v>42341</v>
       </c>
       <c r="B1051" t="n">
-        <v>48.49263000488281</v>
+        <v>48.49262619018555</v>
       </c>
       <c r="C1051" t="n">
-        <v>53.71156788230153</v>
+        <v>53.71156365705388</v>
       </c>
       <c r="D1051" t="n">
-        <v>48.49263000488281</v>
+        <v>48.49262619018555</v>
       </c>
       <c r="E1051" t="n">
-        <v>53.71156788230153</v>
+        <v>53.71156365705388</v>
       </c>
       <c r="F1051" t="n">
         <v>1581</v>
@@ -21452,16 +21452,16 @@
         <v>42342</v>
       </c>
       <c r="B1052" t="n">
-        <v>48.49263000488281</v>
+        <v>48.49262619018555</v>
       </c>
       <c r="C1052" t="n">
-        <v>48.49263000488281</v>
+        <v>48.49262619018555</v>
       </c>
       <c r="D1052" t="n">
-        <v>48.49263000488281</v>
+        <v>48.49262619018555</v>
       </c>
       <c r="E1052" t="n">
-        <v>48.49263000488281</v>
+        <v>48.49262619018555</v>
       </c>
       <c r="F1052" t="n">
         <v>233</v>
@@ -21552,16 +21552,16 @@
         <v>42352</v>
       </c>
       <c r="B1057" t="n">
-        <v>40.88167953491211</v>
+        <v>40.88167572021484</v>
       </c>
       <c r="C1057" t="n">
-        <v>40.88167953491211</v>
+        <v>40.88167572021484</v>
       </c>
       <c r="D1057" t="n">
-        <v>40.88167953491211</v>
+        <v>40.88167572021484</v>
       </c>
       <c r="E1057" t="n">
-        <v>40.88167953491211</v>
+        <v>40.88167572021484</v>
       </c>
       <c r="F1057" t="n">
         <v>128</v>
@@ -21592,16 +21592,16 @@
         <v>42356</v>
       </c>
       <c r="B1059" t="n">
-        <v>40.88167953491211</v>
+        <v>40.88167572021484</v>
       </c>
       <c r="C1059" t="n">
-        <v>42.4038686006935</v>
+        <v>42.40386464395974</v>
       </c>
       <c r="D1059" t="n">
-        <v>40.88167953491211</v>
+        <v>40.88167572021484</v>
       </c>
       <c r="E1059" t="n">
-        <v>42.4038686006935</v>
+        <v>42.40386464395974</v>
       </c>
       <c r="F1059" t="n">
         <v>114</v>
@@ -21612,16 +21612,16 @@
         <v>42359</v>
       </c>
       <c r="B1060" t="n">
-        <v>40.88167953491211</v>
+        <v>40.88167572021484</v>
       </c>
       <c r="C1060" t="n">
-        <v>40.88167953491211</v>
+        <v>40.88167572021484</v>
       </c>
       <c r="D1060" t="n">
-        <v>40.88167953491211</v>
+        <v>40.88167572021484</v>
       </c>
       <c r="E1060" t="n">
-        <v>40.88167953491211</v>
+        <v>40.88167572021484</v>
       </c>
       <c r="F1060" t="n">
         <v>457</v>
@@ -21672,16 +21672,16 @@
         <v>42366</v>
       </c>
       <c r="B1063" t="n">
-        <v>39.14203262329102</v>
+        <v>39.14202880859375</v>
       </c>
       <c r="C1063" t="n">
-        <v>43.27369261266837</v>
+        <v>43.27368839530852</v>
       </c>
       <c r="D1063" t="n">
-        <v>33.9230946873552</v>
+        <v>33.92309138128426</v>
       </c>
       <c r="E1063" t="n">
-        <v>33.9230946873552</v>
+        <v>33.92309138128426</v>
       </c>
       <c r="F1063" t="n">
         <v>36</v>
@@ -22072,16 +22072,16 @@
         <v>42405</v>
       </c>
       <c r="B1083" t="n">
-        <v>34.57545852661133</v>
+        <v>34.57546234130859</v>
       </c>
       <c r="C1083" t="n">
-        <v>34.79291409750367</v>
+        <v>34.79291793619272</v>
       </c>
       <c r="D1083" t="n">
-        <v>31.31362306699879</v>
+        <v>31.31362652181899</v>
       </c>
       <c r="E1083" t="n">
-        <v>32.61835838858028</v>
+        <v>32.61836198735142</v>
       </c>
       <c r="F1083" t="n">
         <v>411</v>
@@ -22132,16 +22132,16 @@
         <v>42416</v>
       </c>
       <c r="B1086" t="n">
-        <v>37.83729553222656</v>
+        <v>37.8372917175293</v>
       </c>
       <c r="C1086" t="n">
-        <v>38.27220666998567</v>
+        <v>38.27220281144135</v>
       </c>
       <c r="D1086" t="n">
-        <v>35.44528427455145</v>
+        <v>35.44528070101305</v>
       </c>
       <c r="E1086" t="n">
-        <v>35.66273984343101</v>
+        <v>35.66273624796907</v>
       </c>
       <c r="F1086" t="n">
         <v>653</v>
@@ -22152,16 +22152,16 @@
         <v>42417</v>
       </c>
       <c r="B1087" t="n">
-        <v>40.88167953491211</v>
+        <v>40.88167572021484</v>
       </c>
       <c r="C1087" t="n">
-        <v>40.88167953491211</v>
+        <v>40.88167572021484</v>
       </c>
       <c r="D1087" t="n">
-        <v>37.83729761089427</v>
+        <v>37.83729408027035</v>
       </c>
       <c r="E1087" t="n">
-        <v>37.83729761089427</v>
+        <v>37.83729408027035</v>
       </c>
       <c r="F1087" t="n">
         <v>1984</v>
@@ -22232,16 +22232,16 @@
         <v>42423</v>
       </c>
       <c r="B1091" t="n">
-        <v>41.31658935546875</v>
+        <v>41.31658554077148</v>
       </c>
       <c r="C1091" t="n">
-        <v>42.40386722430636</v>
+        <v>42.4038633092224</v>
       </c>
       <c r="D1091" t="n">
-        <v>41.31658935546875</v>
+        <v>41.31658554077148</v>
       </c>
       <c r="E1091" t="n">
-        <v>42.40386722430636</v>
+        <v>42.4038633092224</v>
       </c>
       <c r="F1091" t="n">
         <v>201</v>
@@ -22372,16 +22372,16 @@
         <v>42433</v>
       </c>
       <c r="B1098" t="n">
-        <v>49.36245346069336</v>
+        <v>49.36244964599609</v>
       </c>
       <c r="C1098" t="n">
-        <v>52.40683553773163</v>
+        <v>52.40683148776657</v>
       </c>
       <c r="D1098" t="n">
-        <v>49.36245346069336</v>
+        <v>49.36244964599609</v>
       </c>
       <c r="E1098" t="n">
-        <v>50.01482023596115</v>
+        <v>50.01481637084942</v>
       </c>
       <c r="F1098" t="n">
         <v>1078</v>
@@ -22392,16 +22392,16 @@
         <v>42436</v>
       </c>
       <c r="B1099" t="n">
-        <v>52.84174728393555</v>
+        <v>52.84174346923828</v>
       </c>
       <c r="C1099" t="n">
-        <v>52.84174728393555</v>
+        <v>52.84174346923828</v>
       </c>
       <c r="D1099" t="n">
-        <v>48.92754279819265</v>
+        <v>48.92753926606563</v>
       </c>
       <c r="E1099" t="n">
-        <v>48.92754279819265</v>
+        <v>48.92753926606563</v>
       </c>
       <c r="F1099" t="n">
         <v>173</v>
@@ -22452,16 +22452,16 @@
         <v>42443</v>
       </c>
       <c r="B1102" t="n">
-        <v>51.53701019287109</v>
+        <v>51.53700637817383</v>
       </c>
       <c r="C1102" t="n">
-        <v>51.53701019287109</v>
+        <v>51.53700637817383</v>
       </c>
       <c r="D1102" t="n">
-        <v>46.10061692063539</v>
+        <v>46.10061350833233</v>
       </c>
       <c r="E1102" t="n">
-        <v>46.10061692063539</v>
+        <v>46.10061350833233</v>
       </c>
       <c r="F1102" t="n">
         <v>150</v>
@@ -22472,16 +22472,16 @@
         <v>42444</v>
       </c>
       <c r="B1103" t="n">
-        <v>51.53701019287109</v>
+        <v>51.53700637817383</v>
       </c>
       <c r="C1103" t="n">
-        <v>51.53701019287109</v>
+        <v>51.53700637817383</v>
       </c>
       <c r="D1103" t="n">
-        <v>51.53701019287109</v>
+        <v>51.53700637817383</v>
       </c>
       <c r="E1103" t="n">
-        <v>51.53701019287109</v>
+        <v>51.53700637817383</v>
       </c>
       <c r="F1103" t="n">
         <v>9</v>
@@ -22512,16 +22512,16 @@
         <v>42447</v>
       </c>
       <c r="B1105" t="n">
-        <v>52.62428283691406</v>
+        <v>52.62428665161133</v>
       </c>
       <c r="C1105" t="n">
-        <v>53.27664950938143</v>
+        <v>53.2766533713683</v>
       </c>
       <c r="D1105" t="n">
-        <v>52.62428283691406</v>
+        <v>52.62428665161133</v>
       </c>
       <c r="E1105" t="n">
-        <v>53.27664950938143</v>
+        <v>53.2766533713683</v>
       </c>
       <c r="F1105" t="n">
         <v>237</v>
@@ -22532,16 +22532,16 @@
         <v>42450</v>
       </c>
       <c r="B1106" t="n">
-        <v>52.84174728393555</v>
+        <v>52.84174346923828</v>
       </c>
       <c r="C1106" t="n">
-        <v>52.84174728393555</v>
+        <v>52.84174346923828</v>
       </c>
       <c r="D1106" t="n">
-        <v>52.62429168986402</v>
+        <v>52.62428789086508</v>
       </c>
       <c r="E1106" t="n">
-        <v>52.84174728393555</v>
+        <v>52.84174346923828</v>
       </c>
       <c r="F1106" t="n">
         <v>1897</v>
@@ -22572,16 +22572,16 @@
         <v>42459</v>
       </c>
       <c r="B1108" t="n">
-        <v>52.62428283691406</v>
+        <v>52.62428665161133</v>
       </c>
       <c r="C1108" t="n">
-        <v>52.62428283691406</v>
+        <v>52.62428665161133</v>
       </c>
       <c r="D1108" t="n">
-        <v>46.31806787727487</v>
+        <v>46.31807123483905</v>
       </c>
       <c r="E1108" t="n">
-        <v>46.31806787727487</v>
+        <v>46.31807123483905</v>
       </c>
       <c r="F1108" t="n">
         <v>315</v>
@@ -22652,16 +22652,16 @@
         <v>42473</v>
       </c>
       <c r="B1112" t="n">
-        <v>59.80032348632812</v>
+        <v>59.80032730102539</v>
       </c>
       <c r="C1112" t="n">
-        <v>59.80032348632812</v>
+        <v>59.80032730102539</v>
       </c>
       <c r="D1112" t="n">
-        <v>52.84174145162458</v>
+        <v>52.84174482242987</v>
       </c>
       <c r="E1112" t="n">
-        <v>52.84174145162458</v>
+        <v>52.84174482242987</v>
       </c>
       <c r="F1112" t="n">
         <v>992</v>
@@ -22752,16 +22752,16 @@
         <v>42488</v>
       </c>
       <c r="B1117" t="n">
-        <v>56.54997634887695</v>
+        <v>56.54997253417969</v>
       </c>
       <c r="C1117" t="n">
-        <v>57.63747509163461</v>
+        <v>57.63747120357784</v>
       </c>
       <c r="D1117" t="n">
-        <v>56.54997634887695</v>
+        <v>56.54997253417969</v>
       </c>
       <c r="E1117" t="n">
-        <v>57.63747509163461</v>
+        <v>57.63747120357784</v>
       </c>
       <c r="F1117" t="n">
         <v>96</v>
@@ -22772,16 +22772,16 @@
         <v>42489</v>
       </c>
       <c r="B1118" t="n">
-        <v>64.59748077392578</v>
+        <v>64.59747314453125</v>
       </c>
       <c r="C1118" t="n">
-        <v>64.59748077392578</v>
+        <v>64.59747314453125</v>
       </c>
       <c r="D1118" t="n">
-        <v>56.54998172587946</v>
+        <v>56.54997504694839</v>
       </c>
       <c r="E1118" t="n">
-        <v>57.63748057204093</v>
+        <v>57.63747376466898</v>
       </c>
       <c r="F1118" t="n">
         <v>128</v>
@@ -22872,16 +22872,16 @@
         <v>42501</v>
       </c>
       <c r="B1123" t="n">
-        <v>61.3349723815918</v>
+        <v>61.33496856689453</v>
       </c>
       <c r="C1123" t="n">
-        <v>64.81497224041225</v>
+        <v>64.81496820927816</v>
       </c>
       <c r="D1123" t="n">
-        <v>58.72497533239555</v>
+        <v>58.72497168002571</v>
       </c>
       <c r="E1123" t="n">
-        <v>58.72497533239555</v>
+        <v>58.72497168002571</v>
       </c>
       <c r="F1123" t="n">
         <v>192</v>
@@ -23072,16 +23072,16 @@
         <v>42521</v>
       </c>
       <c r="B1133" t="n">
-        <v>56.54997634887695</v>
+        <v>56.54997253417969</v>
       </c>
       <c r="C1133" t="n">
-        <v>56.54997634887695</v>
+        <v>56.54997253417969</v>
       </c>
       <c r="D1133" t="n">
-        <v>56.54997634887695</v>
+        <v>56.54997253417969</v>
       </c>
       <c r="E1133" t="n">
-        <v>56.54997634887695</v>
+        <v>56.54997253417969</v>
       </c>
       <c r="F1133" t="n">
         <v>22</v>
@@ -23112,16 +23112,16 @@
         <v>42523</v>
       </c>
       <c r="B1135" t="n">
-        <v>56.54997634887695</v>
+        <v>56.54997253417969</v>
       </c>
       <c r="C1135" t="n">
-        <v>56.54997634887695</v>
+        <v>56.54997253417969</v>
       </c>
       <c r="D1135" t="n">
-        <v>56.54997634887695</v>
+        <v>56.54997253417969</v>
       </c>
       <c r="E1135" t="n">
-        <v>56.54997634887695</v>
+        <v>56.54997253417969</v>
       </c>
       <c r="F1135" t="n">
         <v>41</v>
@@ -23132,16 +23132,16 @@
         <v>42530</v>
       </c>
       <c r="B1136" t="n">
-        <v>56.76747131347656</v>
+        <v>56.76747512817383</v>
       </c>
       <c r="C1136" t="n">
-        <v>56.76747131347656</v>
+        <v>56.76747512817383</v>
       </c>
       <c r="D1136" t="n">
-        <v>56.76747131347656</v>
+        <v>56.76747512817383</v>
       </c>
       <c r="E1136" t="n">
-        <v>56.76747131347656</v>
+        <v>56.76747512817383</v>
       </c>
       <c r="F1136" t="n">
         <v>9</v>
@@ -23152,16 +23152,16 @@
         <v>42534</v>
       </c>
       <c r="B1137" t="n">
-        <v>54.80997085571289</v>
+        <v>54.80997467041016</v>
       </c>
       <c r="C1137" t="n">
-        <v>54.80997085571289</v>
+        <v>54.80997467041016</v>
       </c>
       <c r="D1137" t="n">
-        <v>54.59247112188963</v>
+        <v>54.59247492144922</v>
       </c>
       <c r="E1137" t="n">
-        <v>54.59247112188963</v>
+        <v>54.59247492144922</v>
       </c>
       <c r="F1137" t="n">
         <v>169</v>
@@ -23172,16 +23172,16 @@
         <v>42538</v>
       </c>
       <c r="B1138" t="n">
-        <v>56.54997634887695</v>
+        <v>56.54997253417969</v>
       </c>
       <c r="C1138" t="n">
-        <v>57.20247559453154</v>
+        <v>57.20247173581858</v>
       </c>
       <c r="D1138" t="n">
-        <v>56.54997634887695</v>
+        <v>56.54997253417969</v>
       </c>
       <c r="E1138" t="n">
-        <v>57.20247559453154</v>
+        <v>57.20247173581858</v>
       </c>
       <c r="F1138" t="n">
         <v>27</v>
@@ -23192,16 +23192,16 @@
         <v>42541</v>
       </c>
       <c r="B1139" t="n">
-        <v>69.59996795654297</v>
+        <v>69.59996032714844</v>
       </c>
       <c r="C1139" t="n">
-        <v>70.2524710226232</v>
+        <v>70.25246332170272</v>
       </c>
       <c r="D1139" t="n">
-        <v>69.59996795654297</v>
+        <v>69.59996032714844</v>
       </c>
       <c r="E1139" t="n">
-        <v>69.59996795654297</v>
+        <v>69.59996032714844</v>
       </c>
       <c r="F1139" t="n">
         <v>429</v>
@@ -23212,16 +23212,16 @@
         <v>42542</v>
       </c>
       <c r="B1140" t="n">
-        <v>69.59996795654297</v>
+        <v>69.59996032714844</v>
       </c>
       <c r="C1140" t="n">
-        <v>69.59996795654297</v>
+        <v>69.59996032714844</v>
       </c>
       <c r="D1140" t="n">
-        <v>69.59996795654297</v>
+        <v>69.59996032714844</v>
       </c>
       <c r="E1140" t="n">
-        <v>69.59996795654297</v>
+        <v>69.59996032714844</v>
       </c>
       <c r="F1140" t="n">
         <v>196</v>
@@ -23292,16 +23292,16 @@
         <v>42549</v>
       </c>
       <c r="B1144" t="n">
-        <v>63.50997161865234</v>
+        <v>63.50996780395508</v>
       </c>
       <c r="C1144" t="n">
-        <v>68.29496605084024</v>
+        <v>68.29496194873448</v>
       </c>
       <c r="D1144" t="n">
-        <v>63.50997161865234</v>
+        <v>63.50996780395508</v>
       </c>
       <c r="E1144" t="n">
-        <v>68.29496605084024</v>
+        <v>68.29496194873448</v>
       </c>
       <c r="F1144" t="n">
         <v>13</v>
@@ -23352,16 +23352,16 @@
         <v>42556</v>
       </c>
       <c r="B1147" t="n">
-        <v>68.51246643066406</v>
+        <v>68.51247406005859</v>
       </c>
       <c r="C1147" t="n">
-        <v>68.51246643066406</v>
+        <v>68.51247406005859</v>
       </c>
       <c r="D1147" t="n">
-        <v>68.51246643066406</v>
+        <v>68.51247406005859</v>
       </c>
       <c r="E1147" t="n">
-        <v>68.51246643066406</v>
+        <v>68.51247406005859</v>
       </c>
       <c r="F1147" t="n">
         <v>9</v>
@@ -23372,16 +23372,16 @@
         <v>42557</v>
       </c>
       <c r="B1148" t="n">
-        <v>63.2924690246582</v>
+        <v>63.29247283935547</v>
       </c>
       <c r="C1148" t="n">
-        <v>68.72996245300497</v>
+        <v>68.72996659542513</v>
       </c>
       <c r="D1148" t="n">
-        <v>63.2924690246582</v>
+        <v>63.29247283935547</v>
       </c>
       <c r="E1148" t="n">
-        <v>68.72996245300497</v>
+        <v>68.72996659542513</v>
       </c>
       <c r="F1148" t="n">
         <v>27</v>
@@ -23432,16 +23432,16 @@
         <v>42562</v>
       </c>
       <c r="B1151" t="n">
-        <v>73.94997406005859</v>
+        <v>73.94996643066406</v>
       </c>
       <c r="C1151" t="n">
-        <v>78.08247343605805</v>
+        <v>78.08246538031491</v>
       </c>
       <c r="D1151" t="n">
-        <v>69.16497158829023</v>
+        <v>69.16496445256283</v>
       </c>
       <c r="E1151" t="n">
-        <v>69.16497158829023</v>
+        <v>69.16496445256283</v>
       </c>
       <c r="F1151" t="n">
         <v>105</v>
@@ -23572,16 +23572,16 @@
         <v>42571</v>
       </c>
       <c r="B1158" t="n">
-        <v>76.12496185302734</v>
+        <v>76.12496948242188</v>
       </c>
       <c r="C1158" t="n">
-        <v>76.12496185302734</v>
+        <v>76.12496948242188</v>
       </c>
       <c r="D1158" t="n">
-        <v>70.03496915319737</v>
+        <v>70.03497617224076</v>
       </c>
       <c r="E1158" t="n">
-        <v>76.12496185302734</v>
+        <v>76.12496948242188</v>
       </c>
       <c r="F1158" t="n">
         <v>68</v>
@@ -23592,16 +23592,16 @@
         <v>42572</v>
       </c>
       <c r="B1159" t="n">
-        <v>76.12496185302734</v>
+        <v>76.12496948242188</v>
       </c>
       <c r="C1159" t="n">
-        <v>78.29995924582376</v>
+        <v>78.29996709320085</v>
       </c>
       <c r="D1159" t="n">
-        <v>75.25496289590878</v>
+        <v>75.25497043811029</v>
       </c>
       <c r="E1159" t="n">
-        <v>78.29995924582376</v>
+        <v>78.29996709320085</v>
       </c>
       <c r="F1159" t="n">
         <v>82</v>
@@ -23612,16 +23612,16 @@
         <v>42573</v>
       </c>
       <c r="B1160" t="n">
-        <v>76.12496185302734</v>
+        <v>76.12496948242188</v>
       </c>
       <c r="C1160" t="n">
-        <v>76.12496185302734</v>
+        <v>76.12496948242188</v>
       </c>
       <c r="D1160" t="n">
-        <v>75.03745936340394</v>
+        <v>75.03746688380681</v>
       </c>
       <c r="E1160" t="n">
-        <v>75.03745936340394</v>
+        <v>75.03746688380681</v>
       </c>
       <c r="F1160" t="n">
         <v>68</v>
@@ -23632,16 +23632,16 @@
         <v>42576</v>
       </c>
       <c r="B1161" t="n">
-        <v>76.12496185302734</v>
+        <v>76.12496948242188</v>
       </c>
       <c r="C1161" t="n">
-        <v>76.12496185302734</v>
+        <v>76.12496948242188</v>
       </c>
       <c r="D1161" t="n">
-        <v>75.03745936340394</v>
+        <v>75.03746688380681</v>
       </c>
       <c r="E1161" t="n">
-        <v>75.03745936340394</v>
+        <v>75.03746688380681</v>
       </c>
       <c r="F1161" t="n">
         <v>105</v>
@@ -23652,16 +23652,16 @@
         <v>42577</v>
       </c>
       <c r="B1162" t="n">
-        <v>76.12496185302734</v>
+        <v>76.12496948242188</v>
       </c>
       <c r="C1162" t="n">
-        <v>76.12496185302734</v>
+        <v>76.12496948242188</v>
       </c>
       <c r="D1162" t="n">
-        <v>76.12496185302734</v>
+        <v>76.12496948242188</v>
       </c>
       <c r="E1162" t="n">
-        <v>76.12496185302734</v>
+        <v>76.12496948242188</v>
       </c>
       <c r="F1162" t="n">
         <v>27</v>
@@ -23712,16 +23712,16 @@
         <v>42580</v>
       </c>
       <c r="B1165" t="n">
-        <v>63.07497024536133</v>
+        <v>63.07496643066406</v>
       </c>
       <c r="C1165" t="n">
-        <v>63.07497024536133</v>
+        <v>63.07496643066406</v>
       </c>
       <c r="D1165" t="n">
-        <v>56.76747397947024</v>
+        <v>56.76747054624266</v>
       </c>
       <c r="E1165" t="n">
-        <v>62.20497128361431</v>
+        <v>62.20496752153352</v>
       </c>
       <c r="F1165" t="n">
         <v>548</v>
@@ -23772,16 +23772,16 @@
         <v>42585</v>
       </c>
       <c r="B1168" t="n">
-        <v>64.59748077392578</v>
+        <v>64.59747314453125</v>
       </c>
       <c r="C1168" t="n">
-        <v>64.59748077392578</v>
+        <v>64.59747314453125</v>
       </c>
       <c r="D1168" t="n">
-        <v>60.89997711052535</v>
+        <v>60.89996991783073</v>
       </c>
       <c r="E1168" t="n">
-        <v>63.07497859607401</v>
+        <v>63.07497114649717</v>
       </c>
       <c r="F1168" t="n">
         <v>155</v>
@@ -23852,16 +23852,16 @@
         <v>42592</v>
       </c>
       <c r="B1172" t="n">
-        <v>63.2924690246582</v>
+        <v>63.29247283935547</v>
       </c>
       <c r="C1172" t="n">
-        <v>63.2924690246582</v>
+        <v>63.29247283935547</v>
       </c>
       <c r="D1172" t="n">
-        <v>63.07496928752433</v>
+        <v>63.07497308911268</v>
       </c>
       <c r="E1172" t="n">
-        <v>63.2924690246582</v>
+        <v>63.29247283935547</v>
       </c>
       <c r="F1172" t="n">
         <v>210</v>
@@ -23892,16 +23892,16 @@
         <v>42594</v>
       </c>
       <c r="B1174" t="n">
-        <v>69.16496276855469</v>
+        <v>69.16497039794922</v>
       </c>
       <c r="C1174" t="n">
-        <v>69.16496276855469</v>
+        <v>69.16497039794922</v>
       </c>
       <c r="D1174" t="n">
-        <v>69.16496276855469</v>
+        <v>69.16497039794922</v>
       </c>
       <c r="E1174" t="n">
-        <v>69.16496276855469</v>
+        <v>69.16497039794922</v>
       </c>
       <c r="F1174" t="n">
         <v>22</v>
@@ -23912,16 +23912,16 @@
         <v>42597</v>
       </c>
       <c r="B1175" t="n">
-        <v>68.51246643066406</v>
+        <v>68.51247406005859</v>
       </c>
       <c r="C1175" t="n">
-        <v>68.51246643066406</v>
+        <v>68.51247406005859</v>
       </c>
       <c r="D1175" t="n">
-        <v>68.51246643066406</v>
+        <v>68.51247406005859</v>
       </c>
       <c r="E1175" t="n">
-        <v>68.51246643066406</v>
+        <v>68.51247406005859</v>
       </c>
       <c r="F1175" t="n">
         <v>50</v>
@@ -23952,16 +23952,16 @@
         <v>42599</v>
       </c>
       <c r="B1177" t="n">
-        <v>66.33747863769531</v>
+        <v>66.33747100830078</v>
       </c>
       <c r="C1177" t="n">
-        <v>66.33747863769531</v>
+        <v>66.33747100830078</v>
       </c>
       <c r="D1177" t="n">
-        <v>66.33747863769531</v>
+        <v>66.33747100830078</v>
       </c>
       <c r="E1177" t="n">
-        <v>66.33747863769531</v>
+        <v>66.33747100830078</v>
       </c>
       <c r="F1177" t="n">
         <v>45</v>
@@ -24052,16 +24052,16 @@
         <v>42606</v>
       </c>
       <c r="B1182" t="n">
-        <v>64.59748077392578</v>
+        <v>64.59747314453125</v>
       </c>
       <c r="C1182" t="n">
-        <v>65.24997628839695</v>
+        <v>65.24996858193833</v>
       </c>
       <c r="D1182" t="n">
-        <v>64.16247364900977</v>
+        <v>64.16246607099248</v>
       </c>
       <c r="E1182" t="n">
-        <v>64.16247364900977</v>
+        <v>64.16246607099248</v>
       </c>
       <c r="F1182" t="n">
         <v>169</v>
@@ -24072,16 +24072,16 @@
         <v>42607</v>
       </c>
       <c r="B1183" t="n">
-        <v>64.59748077392578</v>
+        <v>64.59747314453125</v>
       </c>
       <c r="C1183" t="n">
-        <v>65.24997628839695</v>
+        <v>65.24996858193833</v>
       </c>
       <c r="D1183" t="n">
-        <v>64.59748077392578</v>
+        <v>64.59747314453125</v>
       </c>
       <c r="E1183" t="n">
-        <v>65.24997628839695</v>
+        <v>65.24996858193833</v>
       </c>
       <c r="F1183" t="n">
         <v>132</v>
@@ -24092,16 +24092,16 @@
         <v>42608</v>
       </c>
       <c r="B1184" t="n">
-        <v>64.59748077392578</v>
+        <v>64.59747314453125</v>
       </c>
       <c r="C1184" t="n">
-        <v>65.24997628839695</v>
+        <v>65.24996858193833</v>
       </c>
       <c r="D1184" t="n">
-        <v>64.59748077392578</v>
+        <v>64.59747314453125</v>
       </c>
       <c r="E1184" t="n">
-        <v>65.24997628839695</v>
+        <v>65.24996858193833</v>
       </c>
       <c r="F1184" t="n">
         <v>416</v>
@@ -24112,16 +24112,16 @@
         <v>42611</v>
       </c>
       <c r="B1185" t="n">
-        <v>64.59748077392578</v>
+        <v>64.59747314453125</v>
       </c>
       <c r="C1185" t="n">
-        <v>64.59748077392578</v>
+        <v>64.59747314453125</v>
       </c>
       <c r="D1185" t="n">
-        <v>64.59748077392578</v>
+        <v>64.59747314453125</v>
       </c>
       <c r="E1185" t="n">
-        <v>64.59748077392578</v>
+        <v>64.59747314453125</v>
       </c>
       <c r="F1185" t="n">
         <v>82</v>
@@ -24192,16 +24192,16 @@
         <v>42615</v>
       </c>
       <c r="B1189" t="n">
-        <v>66.33747863769531</v>
+        <v>66.33747100830078</v>
       </c>
       <c r="C1189" t="n">
-        <v>66.33747863769531</v>
+        <v>66.33747100830078</v>
       </c>
       <c r="D1189" t="n">
-        <v>59.15997869796483</v>
+        <v>59.15997189404603</v>
       </c>
       <c r="E1189" t="n">
-        <v>59.15997869796483</v>
+        <v>59.15997189404603</v>
       </c>
       <c r="F1189" t="n">
         <v>160</v>
@@ -24272,16 +24272,16 @@
         <v>42625</v>
       </c>
       <c r="B1193" t="n">
-        <v>63.50997161865234</v>
+        <v>63.50996780395508</v>
       </c>
       <c r="C1193" t="n">
-        <v>63.50997161865234</v>
+        <v>63.50996780395508</v>
       </c>
       <c r="D1193" t="n">
-        <v>62.20497313714656</v>
+        <v>62.20496940083342</v>
       </c>
       <c r="E1193" t="n">
-        <v>62.63997263098182</v>
+        <v>62.63996886854064</v>
       </c>
       <c r="F1193" t="n">
         <v>32</v>
@@ -74172,19 +74172,39 @@
         <v>46314</v>
       </c>
       <c r="B3688" t="n">
-        <v>1.19</v>
+        <v>1.190000057220459</v>
       </c>
       <c r="C3688" t="n">
-        <v>1.21</v>
+        <v>1.210000038146973</v>
       </c>
       <c r="D3688" t="n">
-        <v>1.14</v>
+        <v>1.139999985694885</v>
       </c>
       <c r="E3688" t="n">
-        <v>1.17</v>
+        <v>1.169999957084656</v>
       </c>
       <c r="F3688" t="n">
         <v>9900600</v>
+      </c>
+    </row>
+    <row r="3689">
+      <c r="A3689" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B3689" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="C3689" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D3689" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E3689" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="F3689" t="n">
+        <v>24719200</v>
       </c>
     </row>
   </sheetData>
